--- a/uploads/curr.xlsx
+++ b/uploads/curr.xlsx
@@ -5,18 +5,33 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FF-PC06\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flexfitcom-my.sharepoint.com/personal/mont_flexfit_vn/Documents/MONT/Báo cáo doanh số/Báo cáo tiềm năng/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E98956E-499D-418D-B677-FE5E1D546F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{3AD2ED15-397E-4A34-ABEF-637B4DC470FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{715886A1-FC13-4E0D-B43F-CB09784FC502}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Danh sách dự kiến ký" sheetId="1" r:id="rId1"/>
+    <sheet name="Report" sheetId="6" r:id="rId1"/>
+    <sheet name="Danh sách dự kiến ký" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <definedNames>
+    <definedName name="Slicer_Trạng_thái">#N/A</definedName>
+  </definedNames>
+  <calcPr calcId="191028" calcOnSave="0"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId4"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -34,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="139">
   <si>
     <t>Phòng ban</t>
   </si>
@@ -42,6 +57,9 @@
     <t>Nhân viên</t>
   </si>
   <si>
+    <t xml:space="preserve"> Doanh số dự kiến ký</t>
+  </si>
+  <si>
     <t>BU 3</t>
   </si>
   <si>
@@ -79,6 +97,12 @@
   </si>
   <si>
     <t>Nguyễn Thanh Bình</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
   <si>
     <t>DANH SÁCH CÁC LEAD DỰ KIẾN KÝ THÁNG + TIỀM NĂNG</t>
@@ -97,6 +121,9 @@
     <t>Doanh số dự kiến ký</t>
   </si>
   <si>
+    <t>Margin dự kiến</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thời gian dự kiến ký </t>
   </si>
   <si>
@@ -118,13 +145,13 @@
     <t>I</t>
   </si>
   <si>
-    <t>Phong Vũ Phan Đăng Lưu</t>
+    <t>Khách sạn Đà Lạt</t>
   </si>
   <si>
     <t>anh Nam: 0912149609</t>
   </si>
   <si>
-    <t>12-15/06</t>
+    <t>Tháng 6</t>
   </si>
   <si>
     <t>Dự kiến ký tháng</t>
@@ -133,7 +160,7 @@
     <t>Customer</t>
   </si>
   <si>
-    <t>Đã gửi báo giá cho khách 2/6, đang chờ tài chính bên Phong Vũ duyệt</t>
+    <t xml:space="preserve">Đã gửi báo giá cho BU 1 gửi khách, đang chờ khách đánh giá và trao đổi. </t>
   </si>
   <si>
     <t>Phát sinh KS Phú Quốc</t>
@@ -143,39 +170,34 @@
 QS đang trình sếp Khôi Nguyên duyệt, dự kiến đầu tuần tới ký</t>
   </si>
   <si>
-    <t>Khách sạn Phú Quốc Chị Trang</t>
-  </si>
-  <si>
-    <t>Tháng 6</t>
-  </si>
-  <si>
-    <t>Khách đã có 3D, Đã gửi báo giá cho khách ngày 2/6
-Khách muốn giảm giá 15%, đang thương thảo giảm 8%
-Hai bên đang đàm phán, dự kiến sang tuần chốt ký</t>
+    <t>Phát sinh Netnam</t>
+  </si>
+  <si>
+    <t>22-24/06</t>
   </si>
   <si>
     <t>II</t>
   </si>
   <si>
-    <t>chị Linh (Nhà máy nước)</t>
-  </si>
-  <si>
-    <t>0909000156 - Chị Linh</t>
-  </si>
-  <si>
-    <t>Khách cũ giới thiệu</t>
-  </si>
-  <si>
-    <t>06/06 khách phản hồi đã ok về báo giá, sang tuần soạn hợp đồng gửi khách review và ký</t>
+    <t>Anh Thanh</t>
+  </si>
+  <si>
+    <t>Tháng 7</t>
+  </si>
+  <si>
+    <t>Tiềm năng</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>Khách đang làm thiết kế bên khác, đang chỉnh sửa 3D và thích sản phẩm thi công bên mình. Dự kiến tháng 7 hoàn thiện.</t>
   </si>
   <si>
     <t>anh Quyết</t>
   </si>
   <si>
-    <t>MKT</t>
-  </si>
-  <si>
-    <t>Đã qua khảo sát sơ bộ và đo đạc, CĐT đang bị chậm phần thô, chưa có trần và ốp lát và đang điều chỉnh phần thô, khách hẹn 2 tuần sau để xử lí phần thô. Dự kiến tuần 2 tháng 6 sẽ liên hệ lại</t>
+    <t>20/06 liên hệ lại khách. Khách vẫn đang triển khai chậm phần thô. Khách hẹn sẽ báo lại vì đang băn khoăn thiết kế phòng khách. Đã ok hỗ trợ khách thiết kế lại phòng khách để triển khai thi công.</t>
   </si>
   <si>
     <t>Khách sạn Hạ Long</t>
@@ -184,41 +206,34 @@
     <t>Partner</t>
   </si>
   <si>
-    <t>Đang chào thầu - đã gửi giá (Liên hệ cuối với Chị Dung bên GRD 25/5 CĐT đang yêu cầu làm rõ quy cách vật liệu và comment điều khoản song song)</t>
+    <t>Đang chỉnh sửa báo giá</t>
+  </si>
+  <si>
+    <t>Căn mẫu KS Hạ Long (Gói đồ rời)</t>
+  </si>
+  <si>
+    <t>Đang giai đoạn đàm phán về các điều khoản của hợp đồng.</t>
   </si>
   <si>
     <t>HK GLOBAL</t>
   </si>
   <si>
-    <t>Tháng 7</t>
-  </si>
-  <si>
-    <t>Tiềm năng</t>
-  </si>
-  <si>
     <t>Holding</t>
   </si>
   <si>
-    <t>Đang trao đổi, chào giá với CĐT, Đã gửi báo giá 2/6 cho chị Trang, Chờ phản hồi</t>
+    <t xml:space="preserve">Update 13/06 đang trao đổi tiến độ báo giá, thi công căn mẫu ngày 10/6. Dự kiến 15/06 kí thỏa thuận hợp tác HK và FFok </t>
   </si>
   <si>
     <t>Chị Huyền, Anh Trường</t>
   </si>
   <si>
-    <t>Đã qua khảo sát đo đạc cùng KH, đã gửi báo giá V1, Đang sửa báo giá V2 (chờ thầu báo lại)</t>
+    <t>Đã gửi báo giá ngày 11/6. Đang chờ khách tham khảo và phản hồi</t>
   </si>
   <si>
     <t>Chị Ngân</t>
   </si>
   <si>
-    <t>Đã qua khảo sát đo đạc. Đang lên báo giá và tư vấn dự kiến tuần 2 tháng 6 gửi</t>
-  </si>
-  <si>
-    <t>Khách sạn Hạ Long
-(Gói đồ rời)</t>
-  </si>
-  <si>
-    <t>Đang LV với Chị Dung bên GRD đã gửi và điều chỉnh BG lần 3 06/06</t>
+    <t>Đã qua khảo sát đo đạc. Đang lên báo giá và tư vấn dự kiến sang tuần gửi khách</t>
   </si>
   <si>
     <t>Chị Trường, Anh Giang</t>
@@ -227,17 +242,65 @@
     <t>WALK-IN</t>
   </si>
   <si>
-    <t>Đag triển khai TK 3D.</t>
-  </si>
-  <si>
-    <t>Vp AORA</t>
-  </si>
-  <si>
-    <t>Đang làm phương án concept. Dự kiến gửi concept cho KH 14/6.
-Dự kiến chốt thiết kế và chuyển đổi thi công 2 tỷ vào cuối tháng</t>
+    <t xml:space="preserve">Đã ký 3D, Đag triển khai TK 3D. </t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thanh</t>
+  </si>
+  <si>
+    <t>Chị Nguyệt Anh</t>
+  </si>
+  <si>
+    <t>Gửi phương án concept cho KH 10/6.
+Dự kiến chốt thiết kế và chuyển đổi thi công 400 tr vào cuối tháng</t>
+  </si>
+  <si>
+    <t>Vũ Ánh Dương</t>
+  </si>
+  <si>
+    <t>Chị Minh Thu</t>
+  </si>
+  <si>
+    <t>Khách đã có thiết kế 3D, hẹn khách đầu tuần tới ngày 22/06 gửi lại báo giá.</t>
+  </si>
+  <si>
+    <t>Chị Ngân Mỹ Đức</t>
+  </si>
+  <si>
+    <t>18/06 đã báo giá, chờ khách phản hồi</t>
+  </si>
+  <si>
+    <t>Anh Huy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã lên thiết kế 3D, gửi báo giá chờ khách phản hồi. </t>
+  </si>
+  <si>
+    <t>Đàm Mạnh Hải</t>
+  </si>
+  <si>
+    <t>Anh Tiến Anh</t>
+  </si>
+  <si>
+    <t>18/06 trao đổi với khách. Dự kiến ký thiết kế trước 13 triệu. Hẹn 23/06 phản hồi.</t>
+  </si>
+  <si>
+    <t>Chị Hồng</t>
+  </si>
+  <si>
+    <t>16/06 trao đổi với khách. Dự kiến ký thiết kế trước. Hẹn ngày 22/06 phản hồi chốt hoặc không.</t>
+  </si>
+  <si>
+    <t>Anh Dũng Tuấn - B2B - Văn phòng hạng sang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/06 Đang chào giá chủ đầu tư. Hẹn 23/06 gửi báo giá. </t>
   </si>
   <si>
     <t>III</t>
+  </si>
+  <si>
+    <t>Trường Ardyring Lào Cai</t>
   </si>
   <si>
     <t xml:space="preserve">Văn Phòng Tuyển Sinh Trường - tại Hà Nội 
@@ -245,10 +308,34 @@
 Chờ Phòng dự án trình Chủ tịch </t>
   </si>
   <si>
-    <t>Các lớp học khối trung học 
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Các lớp học khối trung học 
 ( đã gửi 3D, Báo giá cho CĐT ) 29/05
-còn 3 phòng chức năng khác đang chạy 3D: dự kiến 09/06 trả CĐT
+còn 3 phòng chức năng khác đang chạy 3D: dự kiến </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>15/06</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve"> trả CĐT
 Phòng DA trình chủ tịch phê duyệt )</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Căn mẫu Sunshine </t>
@@ -257,37 +344,131 @@
     <t>Làm việc qua Ms Huyền GRD</t>
   </si>
   <si>
-    <t>Phụ lục hợp đồng 01: 1.260.000.000 vnđ :( Ký HĐ+ Ck tiền) từ GRD
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">1/ Phụ lục hợp đồng 01: 1.260.000.000 vnđ :( Ký HĐ+ Ck tiền) từ GRD
 (GRD đã làm xong bảo lãnh với CĐT ) 
-Phụ lục hợp đồng 02: 1.000.000.000 vnđ : 10/06 ký phát sinh 
-CĐT đã chốt PA &amp; Speck vật liệu : 05/06/2026</t>
+chờ CĐT chuyển tiền &gt;&gt; thi công
+2/ Phụ lục hợp đồng 02: 1.000.000.000 vnđ : 12/06 đã gửi lại BOQ theo speck mới 
+CĐT đã chốt PA &amp; Speck vật liệu : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">12/06/2026
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Chờ CEO duyệt báo giá: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>17/06</t>
+    </r>
   </si>
   <si>
     <t>Đoàn Thị Điểm</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã chốt layout, Speck, 3D gửi CĐT : 10/06
-Khái toán: đã gửi CĐT đồng ý khái toán </t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">3D gửi CĐT : chốt ( 2 phòng : Thư viện, Tuyển sinh) 10.06
+3D phòng Hội trường gửi CDT 13/06
+Chờ CDT phê duyệt 3D: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">15/06
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">&gt;&gt; gửi phụ lục psinh : </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">17/06 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Thị Hằng </t>
+  </si>
+  <si>
+    <t>HASCO-
+ Deawoo Kim mã</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>1/ lên khái toán Fitout &amp; MEP cho CĐT : 15/06 Trả bài
+2/ 2D bên CĐT đang thuê tk, họ sẽ gửi lại để check và hoàn thiện báo giá 
+&gt;&gt; Đàm phán thi công Fitout &amp;MEP trước để kịp tiến độ bàn giao
+3/ Fur : chờ TK của cdt xong, gửi đầu bài để lên BOQ 
+&gt;&gt; chào thi công 
+(dự kiến : 800,000,000 Hoàn thiện)</t>
   </si>
   <si>
     <t>Anh Tùng</t>
   </si>
   <si>
-    <t>30/06</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã gửi Dự toán : 22/05
-CĐT đang hoàn thiện xây dựng </t>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">Đã gửi Dự toán : 22/05
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve">CĐT đang xây thô </t>
+    </r>
   </si>
   <si>
     <t>Anh Nghĩa S8 (Biệt thự Đà Nẵng)</t>
   </si>
   <si>
     <t>Khách hàng đã gửi 3D,.2D : 22/05
-Gửi Dự toán cho CĐT : 12/06/206</t>
+Gửi Dự toán cho CĐT : 19/06/206</t>
   </si>
   <si>
     <t>Khách sạn chị Trang HP</t>
@@ -295,13 +476,14 @@
   <si>
     <t>Khách hàng đã gửi 3D : Khu sảnh lobby, lễ tân &amp; Nhà Hàng 
 Đã gửi Khái Toán : 28/05
-điều chỉnh lại dự toán cân đối theo mức CĐT đầu tư 800 tr</t>
+điều chỉnh lại dự toán cân đối theo mức CĐT đầu tư 600 tr
+17/06</t>
   </si>
   <si>
     <t>Hóa dầu Quảng Ninh</t>
   </si>
   <si>
-    <t xml:space="preserve">BU1 &amp; BU2 &amp; BU3 </t>
+    <t>16/6 đi khảo sát, đang ra bản vẽ SOP và điều chỉnh lại báo giá gửi CĐT, bỏ hạng mục Thảm vì CĐT tự cung cấp</t>
   </si>
   <si>
     <t>Anh Trường (Long Biên)</t>
@@ -310,13 +492,13 @@
     <t>Facebook</t>
   </si>
   <si>
-    <t xml:space="preserve">Đang thiết kế 3D </t>
+    <t>đã gửi TK, chờ CĐT chốt, nếu khách hàng chốt sẽ chuyển BU1 Triển khai (CĐT đã đặt cọc tiền tk)</t>
   </si>
   <si>
     <t>Anh Vũ (Yên Hòa)</t>
   </si>
   <si>
-    <t>Đã khảo sát, đang lên thiết kế 3D</t>
+    <t>Đã khảo sát, đang chỉnh sửa lị thiết kế gửi khách</t>
   </si>
   <si>
     <t>IV</t>
@@ -325,7 +507,20 @@
     <t>Anh Phú The Charm</t>
   </si>
   <si>
-    <t>Đã ký HĐ khung, đang triển khai 3D, dự kiến cuối tháng 5 chuyển đổi thi công</t>
+    <t>Tuần 1 tháng 7</t>
+  </si>
+  <si>
+    <t>Đã ký HĐ khung, đang triển khai 3D, dự kiến đầu tháng 7 chuyển đổi thi công</t>
+  </si>
+  <si>
+    <t>Anh Minh</t>
+  </si>
+  <si>
+    <t>28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã ký HĐTK. KH đã chốt 3D. 
+KH đang cân đối giá </t>
   </si>
   <si>
     <t>Thiết kế nhà a Hân - Thái Nguyên</t>
@@ -334,7 +529,7 @@
     <t>Sale tự kiếm</t>
   </si>
   <si>
-    <t>Đang tư vấn thiết kế sơ bộ</t>
+    <t>Đang tư vấn thiết kế sơ bộ, khách chưa làm đk thủ tục chuyển nhượng đất</t>
   </si>
   <si>
     <t>Booyoung - Campuchia</t>
@@ -343,30 +538,29 @@
     <t>Đối tác</t>
   </si>
   <si>
-    <t>06/06 đã ok mẫu sơn, hàng hóa; CĐT yêu cầu điều chỉnh lại một chút kích thước.
-Sang tuần sẽ đẩy hợp đồng để ký kết</t>
+    <t>Đang triển khai Hợp đồng đặt hàng mẫu (lần 2) vs thầu mới</t>
   </si>
   <si>
     <t>Chị Trang Timecity</t>
   </si>
   <si>
-    <t>12/06/2026</t>
-  </si>
-  <si>
     <t>25/5 KH đã ký hợp đồng thiết kế
-Dự kiến ký thi công vào đầu tháng 6</t>
+Đã chốt 3D, đang điều chỉnh HSKT.</t>
   </si>
   <si>
     <t>Anh Ngọc</t>
   </si>
   <si>
-    <t>KH đang điều chỉnh lại Layout</t>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>Đã chốt 3D, đang triển khai HSKT</t>
   </si>
   <si>
     <t>HDB Thanh Trì</t>
   </si>
   <si>
-    <t>04/06 đã đi gặp CĐT (sếp Trung đi cùng)
+    <t>19/06 đã đi gặp CĐT (sếp Trung, sếp Thuân đi cùng)
 Đang điều chỉnh giá</t>
   </si>
   <si>
@@ -376,26 +570,16 @@
     <t>Tự kiếm</t>
   </si>
   <si>
-    <t>29/05/2026 đã vào gặp chủ đầu tư với sếp Trung và sếp Thuân
-07/06 gửi BOQ cho Ban Thư ký của Chủ Tịch để trình ký</t>
+    <t>20/06 đang làm việc lại về tiến độ phần thô. Tuần 4 tháng 6 họp trao đổi về Hợp đồng.</t>
   </si>
   <si>
     <t>Minh Châu</t>
   </si>
   <si>
-    <t>10/06/2026</t>
-  </si>
-  <si>
-    <t>Đang triển khai 3D</t>
-  </si>
-  <si>
-    <t>Chú Phước</t>
-  </si>
-  <si>
-    <t>25/06/2026</t>
-  </si>
-  <si>
-    <t>Khách đang xem dự thảo hợp đồng</t>
+    <t>29/06/2026</t>
+  </si>
+  <si>
+    <t>Đã chốt 3D, đang đợi ván nên lùi lịch ký PL Thi công đến cuối tháng 6</t>
   </si>
   <si>
     <t>Nội thất 328 căn Chung cư Ecopark Sông Lam</t>
@@ -410,13 +594,10 @@
     <t>Bệnh viện Thạch Thất</t>
   </si>
   <si>
-    <t>CĐT đã có bảng báo giá, Đang đàm phán hợp đồng và giá để chốt ký hợp đồng</t>
+    <t>Triển khai trước phần ép cọc.</t>
   </si>
   <si>
     <t>TỔNG</t>
-  </si>
-  <si>
-    <t>Trường Ardingly Lào Cai</t>
   </si>
 </sst>
 </file>
@@ -427,7 +608,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-1010000]d/m/yyyy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,8 +646,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,8 +677,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -631,11 +823,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -655,9 +862,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -679,6 +883,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -748,6 +964,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -760,10 +977,46 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -773,7 +1026,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="34">
     <dxf>
       <font>
         <b val="0"/>
@@ -959,6 +1212,41 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1213,6 +1501,132 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1226,16 +1640,947 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Trạng thái">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DEE8FFF-0354-321B-A094-F9A62611E93B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Trạng thái"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5705475" y="361950"/>
+              <a:ext cx="1828800" cy="2638425"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46179.745634143517" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="38" xr:uid="{3C70C7AF-468D-46B6-AC12-E9848BD45200}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table5"/>
+  </cacheSource>
+  <cacheFields count="12">
+    <cacheField name="STT" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="11"/>
+    </cacheField>
+    <cacheField name="Phòng ban" numFmtId="0">
+      <sharedItems count="7">
+        <s v="BU HCM"/>
+        <s v="BU 1"/>
+        <s v="BU 2"/>
+        <s v="BU 3"/>
+        <s v="TỔNG"/>
+        <s v="BU3" u="1"/>
+        <s v="BU1" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nhân viên" numFmtId="0">
+      <sharedItems containsBlank="1" count="27">
+        <m/>
+        <s v="Nguyễn Thanh Bình"/>
+        <s v="Hoàng Xuân Sơn"/>
+        <s v="Đinh Ngọc Thịnh"/>
+        <s v="Lê Thị Sao Mai"/>
+        <s v="Nguyễn Lâm Vũ"/>
+        <s v="Lê Thị Hằng"/>
+        <s v="Dương Xuân Thái"/>
+        <s v="Ngô Thanh Tùng"/>
+        <s v="Nguyễn Kiều Vân"/>
+        <s v="Chu Hoàng Nam" u="1"/>
+        <s v="Phạm Hoàng Giang" u="1"/>
+        <s v="Phạm Trường Giang" u="1"/>
+        <s v="Đỗ Đắc Long" u="1"/>
+        <s v="Trần Hán Triều" u="1"/>
+        <s v="Hồ Hằng" u="1"/>
+        <s v="Trần Thị Phương Thảo" u="1"/>
+        <s v="Vũ Ánh Dương" u="1"/>
+        <s v="Phạm Thanh Việt" u="1"/>
+        <s v="Nguyễn Thị Vân" u="1"/>
+        <s v="Đàm Bình Minh" u="1"/>
+        <s v="Nguyễn Ánh Dương" u="1"/>
+        <s v="Nguyễn Đắc Long" u="1"/>
+        <s v="Đặng Công Bình" u="1"/>
+        <s v="Nguyễn Kiều Vân " u="1"/>
+        <s v="Trần Tuấn Anh" u="1"/>
+        <s v="Phạm Nguyên Khánh" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Khách hàng" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Đầu mối làm việc_x000a_(SĐT)" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Doanh số dự kiến ký" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80000000" maxValue="356530000000"/>
+    </cacheField>
+    <cacheField name="Thời gian dự kiến ký " numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Trạng thái" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <m/>
+        <s v="Dự kiến ký tháng"/>
+        <s v="Tiềm năng"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Nguồn lead" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Mức độ tiềm năng" numFmtId="0">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.5" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Tình trạng chăm lead" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Đề xuất Hỗ trợ từ BGĐ" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1568755218"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="38">
+  <r>
+    <s v="I"/>
+    <x v="0"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <n v="1250000000"/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Phong Vũ Phan Đăng Lưu"/>
+    <s v="anh Nam: 0912149609"/>
+    <n v="150000000"/>
+    <s v="12-15/06"/>
+    <x v="1"/>
+    <s v="Customer"/>
+    <n v="0.8"/>
+    <s v="Đã gửi báo giá cho khách 2/6, đang chờ tài chính bên Phong Vũ duyệt"/>
+    <m/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Phát sinh KS Phú Quốc"/>
+    <m/>
+    <n v="400000000"/>
+    <s v="12-15/06"/>
+    <x v="1"/>
+    <s v="Customer"/>
+    <n v="0.7"/>
+    <s v="Gửi báo giá phát sinh ngày 23/05_x000a_QS đang trình sếp Khôi Nguyên duyệt, dự kiến đầu tuần tới ký"/>
+    <m/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <s v="Khách sạn Phú Quốc Chị Trang"/>
+    <m/>
+    <n v="700000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Customer"/>
+    <n v="0.7"/>
+    <s v="Khách đã có 3D, Đã gửi báo giá cho khách ngày 2/6_x000a_Khách muốn giảm giá 15%, đang thương thảo giảm 8%_x000a_Hai bên đang đàm phán, dự kiến sang tuần chốt ký"/>
+    <m/>
+  </r>
+  <r>
+    <s v="II"/>
+    <x v="1"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <n v="23990000000"/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="chị Linh (Nhà máy nước)"/>
+    <s v="0909000156 - Chị Linh"/>
+    <n v="2300000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Khách cũ giới thiệu"/>
+    <n v="0.8"/>
+    <s v="06/06 khách phản hồi đã ok về báo giá, sang tuần soạn hợp đồng gửi khách review và ký"/>
+    <m/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="anh Quyết"/>
+    <m/>
+    <n v="1000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.8"/>
+    <s v="Đã qua khảo sát sơ bộ và đo đạc, CĐT đang bị chậm phần thô, chưa có trần và ốp lát và đang điều chỉnh phần thô, khách hẹn 2 tuần sau để xử lí phần thô. Dự kiến tuần 2 tháng 6 sẽ liên hệ lại"/>
+    <m/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Khách sạn Hạ Long"/>
+    <m/>
+    <n v="7000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="0.7"/>
+    <s v="Đang chào thầu - đã gửi giá (Liên hệ cuối với Chị Dung bên GRD 25/5 CĐT đang yêu cầu làm rõ quy cách vật liệu và comment điều khoản song song)"/>
+    <m/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="HK GLOBAL"/>
+    <m/>
+    <n v="8000000000"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Holding"/>
+    <n v="0.5"/>
+    <s v="Đang trao đổi, chào giá với CĐT, Đã gửi báo giá 2/6 cho chị Trang, Chờ phản hồi"/>
+    <m/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="1"/>
+    <x v="2"/>
+    <s v="Chị Huyền, Anh Trường"/>
+    <m/>
+    <n v="2500000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="0.6"/>
+    <s v="Đã qua khảo sát đo đạc cùng KH, đã gửi báo giá V1, Đang sửa báo giá V2 (chờ thầu báo lại)"/>
+    <m/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Chị Ngân"/>
+    <m/>
+    <n v="500000000"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="MKT"/>
+    <n v="0.7"/>
+    <s v="Đã qua khảo sát đo đạc. Đang lên báo giá và tư vấn dự kiến tuần 2 tháng 6 gửi"/>
+    <m/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Khách sạn Hạ Long_x000a_(Gói đồ rời)"/>
+    <m/>
+    <n v="190000000"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Partner"/>
+    <n v="0.7"/>
+    <s v="Đang LV với Chị Dung bên GRD đã gửi và điều chỉnh BG lần 3 06/06"/>
+    <m/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="1"/>
+    <x v="4"/>
+    <s v="Chị Trường, Anh Giang"/>
+    <m/>
+    <n v="500000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="WALK-IN"/>
+    <n v="0.7"/>
+    <s v="Đag triển khai TK 3D."/>
+    <m/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="1"/>
+    <x v="5"/>
+    <s v="Vp AORA"/>
+    <m/>
+    <n v="2000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.6"/>
+    <s v="Đang làm phương án concept. Dự kiến gửi concept cho KH 14/6._x000a_Dự kiến chốt thiết kế và chuyển đổi thi công 2 tỷ vào cuối tháng"/>
+    <m/>
+  </r>
+  <r>
+    <s v="III"/>
+    <x v="2"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <n v="20450000000"/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Trường Ardyring Lào Cai"/>
+    <m/>
+    <n v="3000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="0.7"/>
+    <s v="Văn Phòng Tuyển Sinh Trường - tại Hà Nội _x000a_Gửi báo giá 06/06/2026_x000a_Chờ Phòng dự án trình Chủ tịch "/>
+    <m/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Trường Ardyring Lào Cai"/>
+    <m/>
+    <n v="2000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="0.7"/>
+    <s v="Các lớp học khối trung học _x000a_( đã gửi 3D, Báo giá cho CĐT ) 29/05_x000a_còn 3 phòng chức năng khác đang chạy 3D: dự kiến 09/06 trả CĐT_x000a_Phòng DA trình chủ tịch phê duyệt )"/>
+    <m/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Căn mẫu Sunshine "/>
+    <s v="Làm việc qua Ms Huyền GRD"/>
+    <n v="2100000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="0.9"/>
+    <s v="Phụ lục hợp đồng 01: 1.260.000.000 vnđ :( Ký HĐ+ Ck tiền) từ GRD_x000a_(GRD đã làm xong bảo lãnh với CĐT ) _x000a_Phụ lục hợp đồng 02: 1.000.000.000 vnđ : 10/06 ký phát sinh _x000a_CĐT đã chốt PA &amp; Speck vật liệu : 05/06/2026"/>
+    <m/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Đoàn Thị Điểm"/>
+    <m/>
+    <n v="600000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="1"/>
+    <s v="Đã chốt layout, Speck, 3D gửi CĐT : 10/06_x000a_Khái toán: đã gửi CĐT đồng ý khái toán "/>
+    <m/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Anh Tùng"/>
+    <m/>
+    <n v="2900000000"/>
+    <s v="30/06"/>
+    <x v="1"/>
+    <s v="Reference"/>
+    <n v="0.7"/>
+    <s v="Đã gửi Dự toán : 22/05_x000a_CĐT đang hoàn thiện xây dựng "/>
+    <m/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Anh Nghĩa S8 (Biệt thự Đà Nẵng)"/>
+    <m/>
+    <n v="500000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Partner"/>
+    <n v="0.7"/>
+    <s v="Khách hàng đã gửi 3D,.2D : 22/05_x000a_Gửi Dự toán cho CĐT : 12/06/206"/>
+    <m/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Khách sạn chị Trang HP"/>
+    <m/>
+    <n v="800000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Customer"/>
+    <n v="0.7"/>
+    <s v="Khách hàng đã gửi 3D : Khu sảnh lobby, lễ tân &amp; Nhà Hàng _x000a_Đã gửi Khái Toán : 28/05_x000a_điều chỉnh lại dự toán cân đối theo mức CĐT đầu tư 800 tr"/>
+    <m/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Hóa dầu Quảng Ninh"/>
+    <m/>
+    <n v="8000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Holding"/>
+    <n v="1"/>
+    <s v="BU1 &amp; BU2 &amp; BU3 "/>
+    <m/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Anh Trường (Long Biên)"/>
+    <m/>
+    <n v="250000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Facebook"/>
+    <n v="0.6"/>
+    <s v="Đang thiết kế 3D "/>
+    <m/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="2"/>
+    <x v="6"/>
+    <s v="Anh Vũ (Yên Hòa)"/>
+    <m/>
+    <n v="300000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Customer"/>
+    <n v="0.6"/>
+    <s v="Đã khảo sát, đang lên thiết kế 3D"/>
+    <m/>
+  </r>
+  <r>
+    <s v="IV"/>
+    <x v="3"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <n v="310840000000"/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+  <r>
+    <n v="1"/>
+    <x v="3"/>
+    <x v="7"/>
+    <s v="Anh Phú The Charm"/>
+    <m/>
+    <n v="300000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.9"/>
+    <s v="Đã ký HĐ khung, đang triển khai 3D, dự kiến cuối tháng 5 chuyển đổi thi công"/>
+    <m/>
+  </r>
+  <r>
+    <n v="2"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Thiết kế nhà a Hân - Thái Nguyên"/>
+    <m/>
+    <n v="80000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Sale tự kiếm"/>
+    <n v="0.7"/>
+    <s v="Đang tư vấn thiết kế sơ bộ"/>
+    <m/>
+  </r>
+  <r>
+    <n v="3"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Booyoung - Campuchia"/>
+    <m/>
+    <n v="30000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Đối tác"/>
+    <n v="0.8"/>
+    <s v="06/06 đã ok mẫu sơn, hàng hóa; CĐT yêu cầu điều chỉnh lại một chút kích thước._x000a_Sang tuần sẽ đẩy hợp đồng để ký kết"/>
+    <m/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="3"/>
+    <x v="9"/>
+    <s v="Chị Trang Timecity"/>
+    <m/>
+    <n v="95000000"/>
+    <s v="12/06/2026"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.6"/>
+    <s v="25/5 KH đã ký hợp đồng thiết kế_x000a_Dự kiến ký thi công vào đầu tháng 6"/>
+    <m/>
+  </r>
+  <r>
+    <n v="5"/>
+    <x v="3"/>
+    <x v="7"/>
+    <s v="Anh Ngọc"/>
+    <m/>
+    <n v="100000000"/>
+    <s v="12/06/2026"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.7"/>
+    <s v="KH đang điều chỉnh lại Layout"/>
+    <m/>
+  </r>
+  <r>
+    <n v="6"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="HDB Thanh Trì"/>
+    <m/>
+    <n v="60000000000"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Đối tác"/>
+    <n v="0.8"/>
+    <s v="04/06 đã đi gặp CĐT (sếp Trung đi cùng)_x000a_Đang điều chỉnh giá"/>
+    <m/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Cụm 36 Biệt thự Ecopark"/>
+    <m/>
+    <n v="60000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Tự kiếm"/>
+    <n v="0.8"/>
+    <s v="29/05/2026 đã vào gặp chủ đầu tư với sếp Trung và sếp Thuân_x000a_07/06 gửi BOQ cho Ban Thư ký của Chủ Tịch để trình ký"/>
+    <m/>
+  </r>
+  <r>
+    <n v="8"/>
+    <x v="3"/>
+    <x v="9"/>
+    <s v="Minh Châu"/>
+    <m/>
+    <n v="115000000"/>
+    <s v="10/06/2026"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.8"/>
+    <s v="Đang triển khai 3D"/>
+    <m/>
+  </r>
+  <r>
+    <n v="9"/>
+    <x v="3"/>
+    <x v="9"/>
+    <s v="Chú Phước"/>
+    <m/>
+    <n v="150000000"/>
+    <s v="25/06/2026"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.75"/>
+    <s v="Khách đang xem dự thảo hợp đồng"/>
+    <m/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Nội thất 328 căn Chung cư Ecopark Sông Lam"/>
+    <m/>
+    <n v="80000000000"/>
+    <s v="Tháng 8"/>
+    <x v="2"/>
+    <s v="Tự kiếm"/>
+    <n v="0.8"/>
+    <s v="29/05/2026 vào gặp chủ đầu tư với sếp Trung và sếp Thuân"/>
+    <m/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="3"/>
+    <x v="8"/>
+    <s v="Bệnh viện Thạch Thất"/>
+    <m/>
+    <n v="80000000000"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="Đối tác"/>
+    <n v="0.8"/>
+    <s v="CĐT đã có bảng báo giá, Đang đàm phán hợp đồng và giá để chốt ký hợp đồng"/>
+    <m/>
+  </r>
+  <r>
+    <m/>
+    <x v="4"/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <n v="356530000000"/>
+    <m/>
+    <x v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="B3:D17" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="12">
+    <pivotField compact="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" showAll="0" sortType="descending">
+      <items count="8">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item m="1" x="6"/>
+        <item x="4"/>
+        <item m="1" x="5"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" showAll="0" sortType="descending">
+      <items count="28">
+        <item m="1" x="10"/>
+        <item x="7"/>
+        <item m="1" x="20"/>
+        <item m="1" x="23"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item m="1" x="21"/>
+        <item m="1" x="22"/>
+        <item m="1" x="24"/>
+        <item x="5"/>
+        <item x="1"/>
+        <item m="1" x="11"/>
+        <item m="1" x="26"/>
+        <item m="1" x="14"/>
+        <item m="1" x="25"/>
+        <item m="1" x="16"/>
+        <item x="0"/>
+        <item m="1" x="15"/>
+        <item m="1" x="18"/>
+        <item m="1" x="17"/>
+        <item m="1" x="19"/>
+        <item m="1" x="12"/>
+        <item x="2"/>
+        <item m="1" x="13"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="1"/>
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="14">
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="24"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name=" Doanh số dự kiến ký" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="16">
+    <format dxfId="33">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="32">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="31">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Trạng_thái" xr10:uid="{E27EFB44-2110-49B9-A113-CD07E6F11170}" sourceName="Trạng thái">
+  <pivotTables>
+    <pivotTable tabId="6" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1568755218">
+      <items count="3">
+        <i x="1" s="1"/>
+        <i x="2"/>
+        <i x="0"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Trạng thái" xr10:uid="{9EDE91CF-C93F-4706-8AF0-91C683A56668}" cache="Slicer_Trạng_thái" caption="Trạng thái" rowHeight="228600"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:L41" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="A3:L41" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phòng ban" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Nhân viên" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Khách hàng" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{5682C788-4E13-4D00-AE71-99A0CE9107F4}" name="Đầu mối làm việc_x000a_(SĐT)" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{2CF83ECE-3CD3-48FD-8820-02DB8F62181B}" name="Doanh số dự kiến ký" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M48" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A3:M48" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phòng ban" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Nhân viên" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Khách hàng" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{5682C788-4E13-4D00-AE71-99A0CE9107F4}" name="Đầu mối làm việc_x000a_(SĐT)" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{2CF83ECE-3CD3-48FD-8820-02DB8F62181B}" name="Doanh số dự kiến ký" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{7162C4C5-A5FF-4141-BC6C-08637B66FEDE}" name="Margin dự kiến" dataDxfId="6"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Thời gian dự kiến ký " dataDxfId="5"/>
     <tableColumn id="11" xr3:uid="{758AB0AB-3A74-4F15-820C-C43EB7995AC2}" name="Trạng thái" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Nguồn lead" dataDxfId="3"/>
@@ -1509,1347 +2854,1898 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382285EE-A618-417D-9608-F4D64537AFD0}">
+  <dimension ref="B3:L42"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="8" max="8" width="18.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17">
+        <v>170840000000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="17">
+        <v>170080000000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B6" s="16"/>
+      <c r="C6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="17">
+        <v>400000000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="17">
+        <v>360000000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B8" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17">
+        <v>20450000000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B9" s="16"/>
+      <c r="C9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="17">
+        <v>20450000000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17">
+        <v>15300000000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B11" s="16"/>
+      <c r="C11" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="17">
+        <v>11800000000</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="17">
+        <v>2000000000</v>
+      </c>
+      <c r="G12" s="41"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="16"/>
+      <c r="C13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="17">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="17">
+        <v>500000000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17">
+        <v>1250000000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="17">
+        <v>1250000000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17">
+        <v>207840000000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H26" s="41"/>
+    </row>
+    <row r="42" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="19" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="23.125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="23.625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="24.875" style="19" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="22.75" style="19" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="25" customWidth="1"/>
-    <col min="8" max="8" width="19.75" style="19" customWidth="1"/>
-    <col min="9" max="9" width="23" style="19" customWidth="1"/>
-    <col min="10" max="10" width="16.625" style="19" customWidth="1"/>
-    <col min="11" max="11" width="53.125" style="19" customWidth="1"/>
-    <col min="12" max="12" width="24" style="37" customWidth="1"/>
-    <col min="13" max="16384" width="9.125" style="19"/>
+    <col min="1" max="1" width="9.125" style="22" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="23" customWidth="1"/>
+    <col min="3" max="3" width="23.125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="35.625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="24.875" style="22" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="22.75" style="22" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="47" customWidth="1"/>
+    <col min="8" max="8" width="15.875" style="28" customWidth="1"/>
+    <col min="9" max="9" width="23.375" style="22" customWidth="1"/>
+    <col min="10" max="10" width="23" style="22" customWidth="1"/>
+    <col min="11" max="11" width="16.625" style="22" customWidth="1"/>
+    <col min="12" max="12" width="85.25" style="22" customWidth="1"/>
+    <col min="13" max="13" width="24" style="40" customWidth="1"/>
+    <col min="14" max="16384" width="9.125" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
-      <c r="L1" s="44"/>
-    </row>
-    <row r="2" spans="1:14" ht="8.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="16" t="s">
+    <row r="1" spans="1:15" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+    </row>
+    <row r="2" spans="1:15" ht="8.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="17" t="s">
+      <c r="D3" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="E3" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="F3" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="G3" s="48" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="17" t="s">
+      <c r="H3" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="18" t="s">
+      <c r="I3" s="20" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="J3" s="20" t="s">
         <v>26</v>
       </c>
+      <c r="K3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="B4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9">
+        <v>14</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
         <f>+SUBTOTAL(9,F5:F7)</f>
-        <v>1250000000</v>
-      </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="6"/>
+        <v>2600000000</v>
+      </c>
+      <c r="G4" s="49"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="34"/>
-    </row>
-    <row r="5" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K4" s="6"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="37"/>
+    </row>
+    <row r="5" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="54" t="s">
+        <v>15</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2">
-        <v>150000000</v>
-      </c>
-      <c r="G5" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>2000000000</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="13">
+        <v>34</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="12">
         <v>0.8</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="35"/>
-    </row>
-    <row r="6" spans="1:14" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="38"/>
+    </row>
+    <row r="6" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C6" s="54" t="s">
+        <v>15</v>
+      </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
-        <v>400000000</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>500000000</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="13">
+        <v>34</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="12">
         <v>0.7</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="35"/>
-    </row>
-    <row r="7" spans="1:14" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="38"/>
+    </row>
+    <row r="7" spans="1:15" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C7" s="54" t="s">
+        <v>15</v>
+      </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>700000000</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>100000000</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>40</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="13">
+        <v>34</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="12">
         <v>0.7</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="35"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-    </row>
-    <row r="8" spans="1:14" s="23" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L7" s="1"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+    </row>
+    <row r="8" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9">
-        <f>+SUBTOTAL(9,F9:F17)</f>
-        <v>23990000000</v>
-      </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="C8" s="56"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
+        <f>+SUBTOTAL(9,F9:F23)</f>
+        <v>24253000000</v>
+      </c>
+      <c r="G8" s="51"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="34"/>
-    </row>
-    <row r="9" spans="1:14" s="24" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="37"/>
+    </row>
+    <row r="9" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
         <v>1</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="12" t="s">
         <v>9</v>
       </c>
+      <c r="C9" s="57" t="s">
+        <v>12</v>
+      </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E9" s="1"/>
       <c r="F9" s="2">
-        <v>2300000000</v>
-      </c>
-      <c r="G9" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>30</v>
+        <v>500000000</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-    </row>
-    <row r="10" spans="1:14" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
+        <v>44</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M9" s="38"/>
+      <c r="N9" s="25"/>
+    </row>
+    <row r="10" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="2">
         <v>1000000000</v>
       </c>
-      <c r="G10" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>30</v>
+      <c r="G10" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="12">
         <v>0.8</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="22"/>
-    </row>
-    <row r="11" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11">
+      <c r="L10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="38"/>
+      <c r="N10" s="25"/>
+    </row>
+    <row r="11" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10">
         <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="12" t="s">
         <v>9</v>
       </c>
+      <c r="C11" s="57" t="s">
+        <v>10</v>
+      </c>
       <c r="D11" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="2">
         <v>7000000000</v>
       </c>
-      <c r="G11" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>30</v>
+      <c r="G11" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="H11" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="13">
+        <v>44</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="12">
         <v>0.7</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="35"/>
-      <c r="M11" s="22"/>
-    </row>
-    <row r="12" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11">
+      <c r="L11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M11" s="38"/>
+      <c r="N11" s="25"/>
+    </row>
+    <row r="12" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10">
         <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="2">
-        <v>8000000000</v>
-      </c>
-      <c r="G12" s="38" t="s">
+        <v>900000000</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="K12" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="35"/>
-      <c r="M12" s="22"/>
-    </row>
-    <row r="13" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
+      <c r="M12" s="38"/>
+      <c r="N12" s="25"/>
+    </row>
+    <row r="13" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10">
         <v>5</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="C13" s="57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="2">
-        <v>2500000000</v>
-      </c>
-      <c r="G13" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>30</v>
+        <v>8000000000</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J13" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="K13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="22"/>
-    </row>
-    <row r="14" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11">
+      <c r="K13" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M13" s="38"/>
+      <c r="N13" s="25"/>
+    </row>
+    <row r="14" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
         <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>56</v>
+      <c r="D14" s="11" t="s">
+        <v>57</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="2">
-        <v>500000000</v>
-      </c>
-      <c r="G14" s="38" t="s">
+        <v>2500000000</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="35"/>
-      <c r="M14" s="22"/>
-    </row>
-    <row r="15" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11">
+      <c r="K14" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="38"/>
+      <c r="N14" s="25"/>
+    </row>
+    <row r="15" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
         <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="C15" s="57" t="s">
+        <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2">
-        <v>190000000</v>
-      </c>
-      <c r="G15" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>51</v>
+        <v>500000000</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="13">
+        <v>44</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K15" s="12">
         <v>0.7</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="22"/>
-    </row>
-    <row r="16" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11">
+      <c r="L15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M15" s="38"/>
+      <c r="N15" s="25"/>
+    </row>
+    <row r="16" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
         <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="C16" s="57" t="s">
+        <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="2">
         <v>500000000</v>
       </c>
-      <c r="G16" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>30</v>
+      <c r="G16" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J16" s="13">
+        <v>34</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K16" s="12">
         <v>0.7</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L16" s="35"/>
-      <c r="M16" s="22"/>
-    </row>
-    <row r="17" spans="1:14" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11">
+      <c r="L16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="38"/>
+      <c r="N16" s="25"/>
+    </row>
+    <row r="17" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
         <v>9</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2">
-        <v>2000000000</v>
-      </c>
-      <c r="G17" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>30</v>
+        <v>400000000</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H17" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J17" s="13">
+        <v>34</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="12">
         <v>0.6</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L17" s="35"/>
-      <c r="M17" s="22"/>
-    </row>
-    <row r="18" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9">
-        <f>+SUBTOTAL(9,F19:F28)</f>
-        <v>20450000000</v>
-      </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="34"/>
-    </row>
-    <row r="19" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3">
-        <v>1</v>
+      <c r="L17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M17" s="38"/>
+      <c r="N17" s="25"/>
+    </row>
+    <row r="18" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M18" s="38"/>
+      <c r="N18" s="25"/>
+    </row>
+    <row r="19" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>11</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C19" s="57" t="s">
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2">
-        <v>3000000000</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>30</v>
+        <v>83000000</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J19" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="K19" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="L19" s="35"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-    </row>
-    <row r="20" spans="1:14" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="3">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="38"/>
+      <c r="N19" s="25"/>
+    </row>
+    <row r="20" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
+        <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>67</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="2">
-        <v>2000000000</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>30</v>
+        <v>20000000</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J20" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="K20" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="L20" s="35"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-    </row>
-    <row r="21" spans="1:14" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3">
-        <v>3</v>
+        <v>34</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M20" s="38"/>
+      <c r="N20" s="25"/>
+    </row>
+    <row r="21" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10">
+        <v>13</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C21" s="57" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="1"/>
       <c r="F21" s="2">
-        <v>2100000000</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>30</v>
+        <v>300000000</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J21" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="K21" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="L21" s="35"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-    </row>
-    <row r="22" spans="1:14" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3">
-        <v>4</v>
+        <v>34</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="38"/>
+      <c r="N21" s="25"/>
+    </row>
+    <row r="22" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10">
+        <v>14</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>74</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="2">
-        <v>600000000</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>30</v>
+        <v>400000000</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H22" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J22" s="13">
-        <v>1</v>
-      </c>
-      <c r="K22" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="L22" s="35"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-    </row>
-    <row r="23" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="3">
-        <v>5</v>
+        <v>34</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22" s="38"/>
+      <c r="N22" s="25"/>
+    </row>
+    <row r="23" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="10">
+        <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>74</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="2">
-        <v>2900000000</v>
-      </c>
-      <c r="G23" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>30</v>
+        <v>2000000000</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="42" t="s">
+        <v>33</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J23" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L23" s="35"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-    </row>
-    <row r="24" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="3">
-        <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M23" s="38"/>
+      <c r="N23" s="25"/>
+    </row>
+    <row r="24" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="2">
-        <v>500000000</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J24" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L24" s="35"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-    </row>
-    <row r="25" spans="1:14" ht="87" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="56"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="8">
+        <f>+SUBTOTAL(9,F25:F35)</f>
+        <v>18550000000</v>
+      </c>
+      <c r="G24" s="51"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="37"/>
+    </row>
+    <row r="25" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>7</v>
+      <c r="C25" s="54" t="s">
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="2">
-        <v>800000000</v>
-      </c>
-      <c r="G25" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="13">
+        <v>4400000000</v>
+      </c>
+      <c r="G25" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" s="12">
         <v>0.7</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L25" s="35"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-    </row>
-    <row r="26" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L25" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="M25" s="38"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+    </row>
+    <row r="26" spans="1:15" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
+        <v>2</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="2">
-        <v>8000000000</v>
-      </c>
-      <c r="G26" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="13">
-        <v>1</v>
-      </c>
-      <c r="K26" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="L26" s="35"/>
-    </row>
-    <row r="27" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1200000000</v>
+      </c>
+      <c r="G26" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L26" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="M26" s="38"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+    </row>
+    <row r="27" spans="1:15" ht="126" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C27" s="54" t="s">
+        <v>8</v>
+      </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="F27" s="2">
-        <v>250000000</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="J27" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="L27" s="35"/>
-    </row>
-    <row r="28" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1300000000</v>
+      </c>
+      <c r="G27" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K27" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L27" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="M27" s="38"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+    </row>
+    <row r="28" spans="1:15" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="C28" s="54" t="s">
+        <v>8</v>
+      </c>
       <c r="D28" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="2">
-        <v>300000000</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L28" s="35"/>
-    </row>
-    <row r="29" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9">
-        <f>+SUBTOTAL(9,F30:F40)</f>
-        <v>310840000000</v>
-      </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="34"/>
-    </row>
-    <row r="30" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="11">
+        <v>800000000</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K28" s="12">
         <v>1</v>
       </c>
+      <c r="L28" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="M28" s="38"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+    </row>
+    <row r="29" spans="1:15" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
+        <v>5</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="2">
+        <v>1200000000</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="M29" s="38"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+    </row>
+    <row r="30" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
+        <v>6</v>
+      </c>
       <c r="B30" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="C30" s="54" t="s">
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="2">
-        <v>300000000</v>
-      </c>
-      <c r="G30" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="4" t="s">
+        <v>2900000000</v>
+      </c>
+      <c r="G30" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H30" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="J30" s="13">
-        <v>0.9</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L30" s="35"/>
-    </row>
-    <row r="31" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="11">
-        <v>2</v>
+      <c r="J30" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K30" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M30" s="38"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+    </row>
+    <row r="31" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>7</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="2">
-        <v>80000000</v>
-      </c>
-      <c r="G31" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>30</v>
+        <v>500000000</v>
+      </c>
+      <c r="G31" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="J31" s="13">
+        <v>44</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K31" s="12">
         <v>0.7</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L31" s="35"/>
-    </row>
-    <row r="32" spans="1:14" s="24" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M31" s="38"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+    </row>
+    <row r="32" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
+      </c>
+      <c r="C32" s="54" t="s">
+        <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="2">
-        <v>30000000000</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J32" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="L32" s="35"/>
-    </row>
-    <row r="33" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="11">
-        <v>4</v>
+        <v>800000000</v>
+      </c>
+      <c r="G32" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H32" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M32" s="38"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+    </row>
+    <row r="33" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>9</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C33" s="54" t="s">
+        <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="E33" s="1"/>
       <c r="F33" s="2">
-        <v>95000000</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>30</v>
+        <v>5000000000</v>
+      </c>
+      <c r="G33" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J33" s="13">
-        <v>0.6</v>
-      </c>
-      <c r="K33" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="L33" s="35"/>
-    </row>
-    <row r="34" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="11">
+      <c r="J33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K33" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L33" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="M33" s="38"/>
+    </row>
+    <row r="34" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>10</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="1"/>
+      <c r="F34" s="2">
+        <v>250000000</v>
+      </c>
+      <c r="G34" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H34" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="58" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K34" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="M34" s="38"/>
+    </row>
+    <row r="35" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>11</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="2">
+        <v>200000000</v>
+      </c>
+      <c r="G35" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M35" s="38"/>
+    </row>
+    <row r="36" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="56"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="8">
+        <f>+SUBTOTAL(9,F37:F47)</f>
+        <v>236820000000</v>
+      </c>
+      <c r="G36" s="51"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="37"/>
+    </row>
+    <row r="37" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E34" s="41"/>
-      <c r="F34" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="G34" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J34" s="13">
-        <v>0.7</v>
-      </c>
-      <c r="K34" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="L34" s="35"/>
-    </row>
-    <row r="35" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>6</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="41"/>
-      <c r="F35" s="2">
-        <v>60000000000</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J35" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="K35" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="L35" s="35"/>
-    </row>
-    <row r="36" spans="1:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11">
-        <v>7</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E36" s="41"/>
-      <c r="F36" s="2">
-        <v>60000000000</v>
-      </c>
-      <c r="G36" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J36" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="K36" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="L36" s="35"/>
-    </row>
-    <row r="37" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11">
-        <v>8</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>5</v>
-      </c>
       <c r="D37" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E37" s="41"/>
+        <v>108</v>
+      </c>
+      <c r="E37" s="1"/>
       <c r="F37" s="2">
-        <v>115000000</v>
-      </c>
-      <c r="G37" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>30</v>
+        <v>300000000</v>
+      </c>
+      <c r="G37" s="12">
+        <v>0.21</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>109</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J37" s="13">
+      <c r="J37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M37" s="38"/>
+    </row>
+    <row r="38" spans="1:13" s="23" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <f t="shared" ref="A38:A46" si="0">A37+1</f>
+        <v>2</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="52">
+        <v>130000000</v>
+      </c>
+      <c r="G38" s="12">
+        <v>0.22</v>
+      </c>
+      <c r="H38" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K38" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="L38" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="M38" s="53"/>
+    </row>
+    <row r="39" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="2">
+        <v>80000000</v>
+      </c>
+      <c r="G39" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H39" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="K39" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="M39" s="38"/>
+    </row>
+    <row r="40" spans="1:13" s="27" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="2">
+        <v>30000000000</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H40" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K40" s="12">
         <v>0.8</v>
       </c>
-      <c r="K37" s="40" t="s">
+      <c r="L40" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="M40" s="38"/>
+    </row>
+    <row r="41" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E41" s="45"/>
+      <c r="F41" s="2">
+        <v>95000000</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.23</v>
+      </c>
+      <c r="H41" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K41" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L41" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="M41" s="38"/>
+    </row>
+    <row r="42" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="45"/>
+      <c r="F42" s="2">
+        <v>100000000</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K42" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L42" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="M42" s="38"/>
+    </row>
+    <row r="43" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="45"/>
+      <c r="F43" s="2">
+        <v>60000000000</v>
+      </c>
+      <c r="G43" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K43" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L43" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="M43" s="38"/>
+    </row>
+    <row r="44" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E44" s="45"/>
+      <c r="F44" s="2">
+        <v>60000000000</v>
+      </c>
+      <c r="G44" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="H44" s="42" t="s">
         <v>109</v>
       </c>
-      <c r="L37" s="35"/>
-    </row>
-    <row r="38" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
+      <c r="I44" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K44" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L44" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="M44" s="38"/>
+    </row>
+    <row r="45" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" s="41"/>
-      <c r="F38" s="2">
-        <v>150000000</v>
-      </c>
-      <c r="G38" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="4" t="s">
+      <c r="B45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E45" s="45"/>
+      <c r="F45" s="2">
+        <v>115000000</v>
+      </c>
+      <c r="G45" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H45" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K45" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L45" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="M45" s="38"/>
+    </row>
+    <row r="46" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="45"/>
+      <c r="F46" s="2">
+        <v>80000000000</v>
+      </c>
+      <c r="G46" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="H46" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J38" s="13">
-        <v>0.75</v>
-      </c>
-      <c r="K38" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="L38" s="35"/>
-    </row>
-    <row r="39" spans="1:12" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11">
-        <v>10</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="12" t="s">
+      <c r="J46" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K46" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="M46" s="38"/>
+    </row>
+    <row r="47" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="10">
+        <v>11</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="41"/>
-      <c r="F39" s="2">
-        <v>80000000000</v>
-      </c>
-      <c r="G39" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J39" s="13">
+      <c r="C47" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="45"/>
+      <c r="F47" s="2">
+        <v>6000000000</v>
+      </c>
+      <c r="G47" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H47" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K47" s="12">
         <v>0.8</v>
       </c>
-      <c r="K39" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="L39" s="35"/>
-    </row>
-    <row r="40" spans="1:12" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11">
-        <v>11</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="41"/>
-      <c r="F40" s="2">
-        <v>80000000000</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="J40" s="13">
-        <v>0.8</v>
-      </c>
-      <c r="K40" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="L40" s="35"/>
-    </row>
-    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="27"/>
-      <c r="B41" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="31">
-        <f>SUBTOTAL(9,F4:F40)</f>
-        <v>356530000000</v>
-      </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="30"/>
-      <c r="L41" s="36"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F42" s="22"/>
-      <c r="G42" s="26"/>
-    </row>
-    <row r="43" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:12" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="L47" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="M47" s="38"/>
+    </row>
+    <row r="48" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="30"/>
+      <c r="B48" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="32"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="34">
+        <f>SUBTOTAL(9,F4:F47)</f>
+        <v>282223000000</v>
+      </c>
+      <c r="G48" s="50"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="39"/>
+    </row>
+    <row r="49" spans="6:8" x14ac:dyDescent="0.2">
+      <c r="F49" s="25"/>
+      <c r="H49" s="29"/>
+    </row>
+    <row r="50" spans="6:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="6:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="6:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/uploads/curr.xlsx
+++ b/uploads/curr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flexfitcom-my.sharepoint.com/personal/mont_flexfit_vn/Documents/MONT/Báo cáo doanh số/Báo cáo tiềm năng/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flexfitcom-my.sharepoint.com/personal/mont_flexfit_vn/Documents/MONT/Báo cáo doanh số/Báo cáo tiềm năng/Dữ liệu báo cáo tiềm năng/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3AD2ED15-397E-4A34-ABEF-637B4DC470FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{715886A1-FC13-4E0D-B43F-CB09784FC502}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{3A852FE8-40D6-450E-8607-96A050C672FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5E57DBA-443E-445B-B99D-B170A7FA527D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="Slicer_Trạng_thái">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028" calcOnSave="0"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="150">
   <si>
     <t>Phòng ban</t>
   </si>
@@ -69,34 +69,25 @@
     <t>Dương Xuân Thái</t>
   </si>
   <si>
-    <t>Nguyễn Kiều Vân</t>
+    <t>BU 1</t>
+  </si>
+  <si>
+    <t>Lê Thị Sao Mai</t>
+  </si>
+  <si>
+    <t>Hoàng Xuân Sơn</t>
+  </si>
+  <si>
+    <t>Đinh Ngọc Thịnh</t>
+  </si>
+  <si>
+    <t>Nguyễn Lâm Vũ</t>
   </si>
   <si>
     <t>BU 2</t>
   </si>
   <si>
     <t>Lê Thị Hằng</t>
-  </si>
-  <si>
-    <t>BU 1</t>
-  </si>
-  <si>
-    <t>Hoàng Xuân Sơn</t>
-  </si>
-  <si>
-    <t>Nguyễn Lâm Vũ</t>
-  </si>
-  <si>
-    <t>Đinh Ngọc Thịnh</t>
-  </si>
-  <si>
-    <t>Lê Thị Sao Mai</t>
-  </si>
-  <si>
-    <t>BU HCM</t>
-  </si>
-  <si>
-    <t>Nguyễn Thanh Bình</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -145,35 +136,62 @@
     <t>I</t>
   </si>
   <si>
+    <t>BU HCM</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Bình</t>
+  </si>
+  <si>
     <t>Khách sạn Đà Lạt</t>
   </si>
   <si>
     <t>anh Nam: 0912149609</t>
   </si>
   <si>
-    <t>Tháng 6</t>
+    <t>Tháng 9</t>
+  </si>
+  <si>
+    <t>Tiềm năng</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>CĐT đang thi công thô đến sàn tầng 3. Sếp bên CĐT đang đi TQ để khảo sát vật liệu, lựa chọn đồ rời 
+Sau khi sếp bên CĐT về và thống nhất định hướng triển khai thì sẽ liên hệ tao đổi lại</t>
+  </si>
+  <si>
+    <t>Phát sinh KS Phú Quốc</t>
+  </si>
+  <si>
+    <t>Tuần 1 tháng 7</t>
   </si>
   <si>
     <t>Dự kiến ký tháng</t>
   </si>
   <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã gửi báo giá cho BU 1 gửi khách, đang chờ khách đánh giá và trao đổi. </t>
-  </si>
-  <si>
-    <t>Phát sinh KS Phú Quốc</t>
-  </si>
-  <si>
-    <t>Gửi báo giá phát sinh ngày 23/05
-QS đang trình sếp Khôi Nguyên duyệt, dự kiến đầu tuần tới ký</t>
+    <t>QS đang trình sếp Khôi Nguyên duyệt, Cô Oanh đi công tác dự kiến tuần này sẽ phê duyệt</t>
   </si>
   <si>
     <t>Phát sinh Netnam</t>
   </si>
   <si>
-    <t>22-24/06</t>
+    <t>Đã gửi PL phát sinh cho CĐT, đang ký trong ngày 30/06/2026</t>
+  </si>
+  <si>
+    <t>Hồ Thị Thu Hằng</t>
+  </si>
+  <si>
+    <t>Chị Quyên Phú Mỹ Hưng</t>
+  </si>
+  <si>
+    <t>Tháng 7</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>3/7 gửi khách BOQ phần thô và NT</t>
   </si>
   <si>
     <t>II</t>
@@ -182,37 +200,23 @@
     <t>Anh Thanh</t>
   </si>
   <si>
-    <t>Tháng 7</t>
-  </si>
-  <si>
-    <t>Tiềm năng</t>
-  </si>
-  <si>
-    <t>MKT</t>
-  </si>
-  <si>
-    <t>Khách đang làm thiết kế bên khác, đang chỉnh sửa 3D và thích sản phẩm thi công bên mình. Dự kiến tháng 7 hoàn thiện.</t>
+    <t>Khách đang làm thiết kế bên khác, Đã gửi FF Ver1 ngày 1/7, dự kiến 3/7 gửi chào giá thi công</t>
   </si>
   <si>
     <t>anh Quyết</t>
   </si>
   <si>
-    <t>20/06 liên hệ lại khách. Khách vẫn đang triển khai chậm phần thô. Khách hẹn sẽ báo lại vì đang băn khoăn thiết kế phòng khách. Đã ok hỗ trợ khách thiết kế lại phòng khách để triển khai thi công.</t>
-  </si>
-  <si>
-    <t>Khách sạn Hạ Long</t>
+    <t>27/6 đã trao đổi liên hệ tư vấn với khách. khách đâng căn nhắc lại giá.
+1/7 gọi điện đề xuất cân đối giá, khách chưa nghe máy</t>
+  </si>
+  <si>
+    <t>Căn mẫu KS Hạ Long (Gói đồ rời)</t>
   </si>
   <si>
     <t>Partner</t>
   </si>
   <si>
-    <t>Đang chỉnh sửa báo giá</t>
-  </si>
-  <si>
-    <t>Căn mẫu KS Hạ Long (Gói đồ rời)</t>
-  </si>
-  <si>
-    <t>Đang giai đoạn đàm phán về các điều khoản của hợp đồng.</t>
+    <t>Đã gửi mail chào giá + điều khoản thương mại và tiến độ, chờ phản hồi</t>
   </si>
   <si>
     <t>HK GLOBAL</t>
@@ -221,19 +225,22 @@
     <t>Holding</t>
   </si>
   <si>
-    <t xml:space="preserve">Update 13/06 đang trao đổi tiến độ báo giá, thi công căn mẫu ngày 10/6. Dự kiến 15/06 kí thỏa thuận hợp tác HK và FFok </t>
+    <t>25/06 Đã gửi lại thông tin gói đồ rời. Phía C Trang bên HK chưa trả lời.</t>
   </si>
   <si>
     <t>Chị Huyền, Anh Trường</t>
   </si>
   <si>
-    <t>Đã gửi báo giá ngày 11/6. Đang chờ khách tham khảo và phản hồi</t>
+    <t>Đã gặp khách tối 26/6 trên VP FF cùng Thầu Thô để bảo vệ phương án BG. Khách có nhu cầu thiết kế lại toàn bộ trước khi thi công thô nên đang cân nhắc.</t>
   </si>
   <si>
     <t>Chị Ngân</t>
   </si>
   <si>
-    <t>Đã qua khảo sát đo đạc. Đang lên báo giá và tư vấn dự kiến sang tuần gửi khách</t>
+    <t>Khách đang chọn đơn vị thiết kế khác, FF chào giá thi công dự kiến cuối tháng 7</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thanh</t>
   </si>
   <si>
     <t>Chị Trường, Anh Giang</t>
@@ -242,17 +249,7 @@
     <t>WALK-IN</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã ký 3D, Đag triển khai TK 3D. </t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thanh</t>
-  </si>
-  <si>
-    <t>Chị Nguyệt Anh</t>
-  </si>
-  <si>
-    <t>Gửi phương án concept cho KH 10/6.
-Dự kiến chốt thiết kế và chuyển đổi thi công 400 tr vào cuối tháng</t>
+    <t>Đã gửi 3D ngày 26/6 khách comment chỉnh sửa màu sắc. Dự kiến tuần 2 tháng 7</t>
   </si>
   <si>
     <t>Vũ Ánh Dương</t>
@@ -261,19 +258,19 @@
     <t>Chị Minh Thu</t>
   </si>
   <si>
-    <t>Khách đã có thiết kế 3D, hẹn khách đầu tuần tới ngày 22/06 gửi lại báo giá.</t>
-  </si>
-  <si>
-    <t>Chị Ngân Mỹ Đức</t>
-  </si>
-  <si>
-    <t>18/06 đã báo giá, chờ khách phản hồi</t>
+    <t>Đã báo giá khách, Khách đang phản hồi giá cao. Đang tìm thầu để hạ giá.</t>
+  </si>
+  <si>
+    <t>Chị Ngân - Trần Phú</t>
+  </si>
+  <si>
+    <t>Đã báo giá, chốt spec, chốt thiết kế. Mời khách qua văn phòng ký hợp đồng (dự kiến ngày 3/7 hoặc ngày 10/7, khách sẽ cố gắng sắp xếp công việc và báo lại)</t>
   </si>
   <si>
     <t>Anh Huy</t>
   </si>
   <si>
-    <t xml:space="preserve">Đã lên thiết kế 3D, gửi báo giá chờ khách phản hồi. </t>
+    <t>Đã lên thiết kế 3D, gửi báo giá khách. Khách chưa nhận nhà và đang ở quê có việc gia đình chưa liên hệ lại được, nên báo lại sau khi lên HN sẽ trao đổi</t>
   </si>
   <si>
     <t>Đàm Mạnh Hải</t>
@@ -282,19 +279,68 @@
     <t>Anh Tiến Anh</t>
   </si>
   <si>
-    <t>18/06 trao đổi với khách. Dự kiến ký thiết kế trước 13 triệu. Hẹn 23/06 phản hồi.</t>
+    <t>Đã tư vấn phương án thiết kế và ngân sách đầu tư, khách đang bàn bạc lại với gia đình, hẹn 2/7 trao đổi lại</t>
   </si>
   <si>
     <t>Chị Hồng</t>
   </si>
   <si>
-    <t>16/06 trao đổi với khách. Dự kiến ký thiết kế trước. Hẹn ngày 22/06 phản hồi chốt hoặc không.</t>
+    <t>Khách đang công tác ở SG nên chờ về HN để trao đổi</t>
   </si>
   <si>
     <t>Anh Dũng Tuấn - B2B - Văn phòng hạng sang</t>
   </si>
   <si>
-    <t xml:space="preserve">19/06 Đang chào giá chủ đầu tư. Hẹn 23/06 gửi báo giá. </t>
+    <t>Đã gửi báo giá ngày 27/06. Đã gặp CĐT 29/06 sang trao đổi về Báo giá và Phương án Kĩ thuật + Spec cùng CĐT
+2/7 chốt spec, dự kiến giữa tháng tháng 7 ký HĐ</t>
+  </si>
+  <si>
+    <t>Anh Khiêm</t>
+  </si>
+  <si>
+    <t>Doanh số dự kiến 1 tỉ. Đơn BTB 10 căn hộ cho thuê. Triển khai TK trước căn mẫu. Công trình đang trong giai đoạn thi công ngăn tường xây thô</t>
+  </si>
+  <si>
+    <t>Anh Thành</t>
+  </si>
+  <si>
+    <t>Giới thiệu</t>
+  </si>
+  <si>
+    <t>27/6 Nhận thông tin gói thầu đồ rời của dự án Lumi. Dự kiến 30/6 gửi lại BOQ và hẹn CĐT để trao đổi</t>
+  </si>
+  <si>
+    <t>Anh Thức</t>
+  </si>
+  <si>
+    <t>Tháng 8</t>
+  </si>
+  <si>
+    <t>Đối tác</t>
+  </si>
+  <si>
+    <t>25/6 Đã gửi báo giá. CĐT đã ok báo giá dự kiến sau khi triển khai xong phần xây thô sẽ kí HĐTC</t>
+  </si>
+  <si>
+    <t>Anh Tuấn</t>
+  </si>
+  <si>
+    <t>Đang giai đoạn lên báo giá, dự kiến 6/7 gửi lại khách</t>
+  </si>
+  <si>
+    <t>KS Hải Phòng - Anh Phong</t>
+  </si>
+  <si>
+    <t>Quý 4</t>
+  </si>
+  <si>
+    <t>Anh Phong TVTK Raymond Đà Nẵng. Gói thầu bao gồm 1 căn mẫu, hạng mục thô và thiết bị. Dự Kiến Quý 4 triển khai. Dự kiến 3/7 gửi lại báo giá sơ bộ để chào thầu. Khách hàng đang hợp tác với FF ở dự án Phú Quốc.</t>
+  </si>
+  <si>
+    <t>Chị Điệp - HGAA</t>
+  </si>
+  <si>
+    <t>25/6 Gửi báo giá Ver1 review cho HGAA. Chờ thông tin phản hồi. Dự kiến 29/6 check phản hồi thông tin</t>
   </si>
   <si>
     <t>III</t>
@@ -305,37 +351,13 @@
   <si>
     <t xml:space="preserve">Văn Phòng Tuyển Sinh Trường - tại Hà Nội 
 Gửi báo giá 06/06/2026
-Chờ Phòng dự án trình Chủ tịch </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Các lớp học khối trung học 
+30/6 Lên làm việc với Chủ tịch </t>
+  </si>
+  <si>
+    <t>Các lớp học khối trung học 
 ( đã gửi 3D, Báo giá cho CĐT ) 29/05
-còn 3 phòng chức năng khác đang chạy 3D: dự kiến </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="13"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>15/06</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve"> trả CĐT
+còn 3 phòng chức năng khác đang chạy 3D 15/06 trả CĐT
 Phòng DA trình chủ tịch phê duyệt )</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">Căn mẫu Sunshine </t>
@@ -386,45 +408,10 @@
     <t>Đoàn Thị Điểm</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">3D gửi CĐT : chốt ( 2 phòng : Thư viện, Tuyển sinh) 10.06
+    <t xml:space="preserve">3D gửi CĐT : chốt ( 2 phòng : Thư viện, Tuyển sinh) 10.06
 3D phòng Hội trường gửi CDT 13/06
-Chờ CDT phê duyệt 3D: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">15/06
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">&gt;&gt; gửi phụ lục psinh : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">17/06 
-</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Lê Thị Hằng </t>
+Chờ CDT phê duyệt 3D: 15/06
+&gt;&gt; gửi phụ lục psinh : 17/06 </t>
   </si>
   <si>
     <t>HASCO-
@@ -437,9 +424,7 @@
     <t>1/ lên khái toán Fitout &amp; MEP cho CĐT : 15/06 Trả bài
 2/ 2D bên CĐT đang thuê tk, họ sẽ gửi lại để check và hoàn thiện báo giá 
 &gt;&gt; Đàm phán thi công Fitout &amp;MEP trước để kịp tiến độ bàn giao
-3/ Fur : chờ TK của cdt xong, gửi đầu bài để lên BOQ 
-&gt;&gt; chào thi công 
-(dự kiến : 800,000,000 Hoàn thiện)</t>
+3/ Fur : 26/6 họp CĐT, chỉnh sửa lại thiết kế một số khu vực</t>
   </si>
   <si>
     <t>Anh Tùng</t>
@@ -498,31 +483,12 @@
     <t>Anh Vũ (Yên Hòa)</t>
   </si>
   <si>
-    <t>Đã khảo sát, đang chỉnh sửa lị thiết kế gửi khách</t>
+    <t>Đã khảo sát, đang chỉnh sửa lại thiết kế gửi khách</t>
   </si>
   <si>
     <t>IV</t>
   </si>
   <si>
-    <t>Anh Phú The Charm</t>
-  </si>
-  <si>
-    <t>Tuần 1 tháng 7</t>
-  </si>
-  <si>
-    <t>Đã ký HĐ khung, đang triển khai 3D, dự kiến đầu tháng 7 chuyển đổi thi công</t>
-  </si>
-  <si>
-    <t>Anh Minh</t>
-  </si>
-  <si>
-    <t>28/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đã ký HĐTK. KH đã chốt 3D. 
-KH đang cân đối giá </t>
-  </si>
-  <si>
     <t>Thiết kế nhà a Hân - Thái Nguyên</t>
   </si>
   <si>
@@ -535,23 +501,26 @@
     <t>Booyoung - Campuchia</t>
   </si>
   <si>
-    <t>Đối tác</t>
-  </si>
-  <si>
     <t>Đang triển khai Hợp đồng đặt hàng mẫu (lần 2) vs thầu mới</t>
   </si>
   <si>
+    <t>Nguyễn Kiều Vân</t>
+  </si>
+  <si>
     <t>Chị Trang Timecity</t>
   </si>
   <si>
-    <t>25/5 KH đã ký hợp đồng thiết kế
+    <t>09/07/2026</t>
+  </si>
+  <si>
+    <t>KH đã ký hợp đồng thiết kế
 Đã chốt 3D, đang điều chỉnh HSKT.</t>
   </si>
   <si>
     <t>Anh Ngọc</t>
   </si>
   <si>
-    <t>26/06/2026</t>
+    <t>11/07/2026</t>
   </si>
   <si>
     <t>Đã chốt 3D, đang triển khai HSKT</t>
@@ -567,28 +536,35 @@
     <t>Cụm 36 Biệt thự Ecopark</t>
   </si>
   <si>
+    <t>Tuần 3 tháng 7</t>
+  </si>
+  <si>
     <t>Tự kiếm</t>
   </si>
   <si>
-    <t>20/06 đang làm việc lại về tiến độ phần thô. Tuần 4 tháng 6 họp trao đổi về Hợp đồng.</t>
-  </si>
-  <si>
-    <t>Minh Châu</t>
-  </si>
-  <si>
-    <t>29/06/2026</t>
-  </si>
-  <si>
-    <t>Đã chốt 3D, đang đợi ván nên lùi lịch ký PL Thi công đến cuối tháng 6</t>
+    <t>20/06 đang làm việc lại về tiến độ phần thô. 
+30/6 sang gặp CĐT để trao đổi về tiến độ tiếp theo</t>
+  </si>
+  <si>
+    <t>Anh Quân - Hà Nam</t>
+  </si>
+  <si>
+    <t>22/07/2026</t>
+  </si>
+  <si>
+    <t>Đã ký HDTK, đang điều chỉnh layout cải tạo.</t>
   </si>
   <si>
     <t>Nội thất 328 căn Chung cư Ecopark Sông Lam</t>
   </si>
   <si>
-    <t>Tháng 8</t>
-  </si>
-  <si>
     <t>29/05/2026 vào gặp chủ đầu tư với sếp Trung và sếp Thuân</t>
+  </si>
+  <si>
+    <t>Trường tiểu học Liên Hồng</t>
+  </si>
+  <si>
+    <t>Hai bên đang thỏa thuận lại điều khoản thanh toán hợp đồng (đợt kế toán chốt điều khoản).</t>
   </si>
   <si>
     <t>Bệnh viện Thạch Thất</t>
@@ -652,7 +628,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -680,6 +656,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -842,7 +824,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -880,9 +862,6 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" pivotButton="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -928,9 +907,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -945,9 +921,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -987,20 +960,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1018,6 +982,90 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1143,7 +1191,7 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1211,7 +1259,7 @@
         <name val="Times New Roman"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1246,7 +1294,7 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1720,37 +1768,42 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46179.745634143517" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="38" xr:uid="{3C70C7AF-468D-46B6-AC12-E9848BD45200}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46194.881354050929" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="45" xr:uid="{3C70C7AF-468D-46B6-AC12-E9848BD45200}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table5"/>
   </cacheSource>
-  <cacheFields count="12">
+  <cacheFields count="13">
     <cacheField name="STT" numFmtId="0">
-      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="11"/>
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="15"/>
     </cacheField>
     <cacheField name="Phòng ban" numFmtId="0">
-      <sharedItems count="7">
+      <sharedItems count="8">
         <s v="BU HCM"/>
         <s v="BU 1"/>
         <s v="BU 2"/>
         <s v="BU 3"/>
         <s v="TỔNG"/>
+        <s v="BU2" u="1"/>
         <s v="BU3" u="1"/>
         <s v="BU1" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Nhân viên" numFmtId="0">
-      <sharedItems containsBlank="1" count="27">
+      <sharedItems containsBlank="1" count="30">
         <m/>
         <s v="Nguyễn Thanh Bình"/>
+        <s v="Đinh Ngọc Thịnh"/>
         <s v="Hoàng Xuân Sơn"/>
-        <s v="Đinh Ngọc Thịnh"/>
         <s v="Lê Thị Sao Mai"/>
         <s v="Nguyễn Lâm Vũ"/>
+        <s v="Nguyễn Ngọc Thanh"/>
+        <s v="Vũ Ánh Dương"/>
+        <s v="Đàm Mạnh Hải"/>
         <s v="Lê Thị Hằng"/>
         <s v="Dương Xuân Thái"/>
         <s v="Ngô Thanh Tùng"/>
         <s v="Nguyễn Kiều Vân"/>
+        <s v="Lê Thị Hằng " u="1"/>
         <s v="Chu Hoàng Nam" u="1"/>
         <s v="Phạm Hoàng Giang" u="1"/>
         <s v="Phạm Trường Giang" u="1"/>
@@ -1758,7 +1811,6 @@
         <s v="Trần Hán Triều" u="1"/>
         <s v="Hồ Hằng" u="1"/>
         <s v="Trần Thị Phương Thảo" u="1"/>
-        <s v="Vũ Ánh Dương" u="1"/>
         <s v="Phạm Thanh Việt" u="1"/>
         <s v="Nguyễn Thị Vân" u="1"/>
         <s v="Đàm Bình Minh" u="1"/>
@@ -1777,7 +1829,10 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Doanh số dự kiến ký" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="80000000" maxValue="356530000000"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20000000" maxValue="282223000000"/>
+    </cacheField>
+    <cacheField name="Margin dự kiến" numFmtId="9">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.08" maxValue="0.3"/>
     </cacheField>
     <cacheField name="Thời gian dự kiến ký " numFmtId="0">
       <sharedItems containsBlank="1"/>
@@ -1796,7 +1851,7 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.5" maxValue="1"/>
     </cacheField>
     <cacheField name="Tình trạng chăm lead" numFmtId="0">
-      <sharedItems containsBlank="1"/>
+      <sharedItems containsBlank="1" longText="1"/>
     </cacheField>
     <cacheField name="Đề xuất Hỗ trợ từ BGĐ" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -1811,14 +1866,15 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="38">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="45">
   <r>
     <s v="I"/>
     <x v="0"/>
     <x v="0"/>
     <m/>
     <m/>
-    <n v="1250000000"/>
+    <n v="2600000000"/>
+    <m/>
     <m/>
     <x v="0"/>
     <m/>
@@ -1830,14 +1886,15 @@
     <n v="1"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="Phong Vũ Phan Đăng Lưu"/>
+    <s v="Khách sạn Đà Lạt"/>
     <s v="anh Nam: 0912149609"/>
-    <n v="150000000"/>
-    <s v="12-15/06"/>
+    <n v="2000000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Customer"/>
     <n v="0.8"/>
-    <s v="Đã gửi báo giá cho khách 2/6, đang chờ tài chính bên Phong Vũ duyệt"/>
+    <s v="Đã gửi báo giá cho BU 1 gửi khách, đang chờ khách đánh giá và trao đổi. "/>
     <m/>
   </r>
   <r>
@@ -1846,8 +1903,9 @@
     <x v="1"/>
     <s v="Phát sinh KS Phú Quốc"/>
     <m/>
-    <n v="400000000"/>
-    <s v="12-15/06"/>
+    <n v="500000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Customer"/>
     <n v="0.7"/>
@@ -1858,14 +1916,15 @@
     <n v="3"/>
     <x v="0"/>
     <x v="1"/>
-    <s v="Khách sạn Phú Quốc Chị Trang"/>
-    <m/>
-    <n v="700000000"/>
-    <s v="Tháng 6"/>
+    <s v="Phát sinh Netnam"/>
+    <m/>
+    <n v="100000000"/>
+    <n v="0.2"/>
+    <s v="22-24/06"/>
     <x v="1"/>
     <s v="Customer"/>
     <n v="0.7"/>
-    <s v="Khách đã có 3D, Đã gửi báo giá cho khách ngày 2/6_x000a_Khách muốn giảm giá 15%, đang thương thảo giảm 8%_x000a_Hai bên đang đàm phán, dự kiến sang tuần chốt ký"/>
+    <m/>
     <m/>
   </r>
   <r>
@@ -1874,7 +1933,8 @@
     <x v="0"/>
     <m/>
     <m/>
-    <n v="23990000000"/>
+    <n v="24253000000"/>
+    <m/>
     <m/>
     <x v="0"/>
     <m/>
@@ -1886,98 +1946,105 @@
     <n v="1"/>
     <x v="1"/>
     <x v="2"/>
-    <s v="chị Linh (Nhà máy nước)"/>
-    <s v="0909000156 - Chị Linh"/>
-    <n v="2300000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Khách cũ giới thiệu"/>
-    <n v="0.8"/>
-    <s v="06/06 khách phản hồi đã ok về báo giá, sang tuần soạn hợp đồng gửi khách review và ký"/>
+    <s v="Anh Thanh"/>
+    <m/>
+    <n v="500000000"/>
+    <n v="0.3"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="MKT"/>
+    <n v="0.6"/>
+    <s v="Khách đang làm thiết kế bên khác, đang chỉnh sửa 3D và thích sản phẩm thi công bên mình. Dự kiến tháng 7 hoàn thiện."/>
     <m/>
   </r>
   <r>
     <n v="2"/>
     <x v="1"/>
-    <x v="3"/>
+    <x v="2"/>
     <s v="anh Quyết"/>
     <m/>
     <n v="1000000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
+    <n v="0.25"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
     <s v="MKT"/>
     <n v="0.8"/>
-    <s v="Đã qua khảo sát sơ bộ và đo đạc, CĐT đang bị chậm phần thô, chưa có trần và ốp lát và đang điều chỉnh phần thô, khách hẹn 2 tuần sau để xử lí phần thô. Dự kiến tuần 2 tháng 6 sẽ liên hệ lại"/>
+    <s v="20/06 liên hệ lại khách. Khách vẫn đang triển khai chậm phần thô. Khách hẹn sẽ báo lại vì đang băn khoăn thiết kế phòng khách. Đã ok hỗ trợ khách thiết kế lại phòng khách để triển khai thi công."/>
     <m/>
   </r>
   <r>
     <n v="3"/>
     <x v="1"/>
+    <x v="3"/>
+    <s v="Khách sạn Hạ Long"/>
+    <m/>
+    <n v="7000000000"/>
+    <n v="0.15"/>
+    <s v="Tháng 7"/>
     <x v="2"/>
-    <s v="Khách sạn Hạ Long"/>
-    <m/>
-    <n v="7000000000"/>
+    <s v="Partner"/>
+    <n v="0.7"/>
+    <s v="Đang chỉnh sửa báo giá"/>
+    <m/>
+  </r>
+  <r>
+    <n v="4"/>
+    <x v="1"/>
+    <x v="3"/>
+    <s v="Căn mẫu KS Hạ Long (Gói đồ rời)"/>
+    <m/>
+    <n v="900000000"/>
+    <n v="0.2"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Partner"/>
     <n v="0.7"/>
-    <s v="Đang chào thầu - đã gửi giá (Liên hệ cuối với Chị Dung bên GRD 25/5 CĐT đang yêu cầu làm rõ quy cách vật liệu và comment điều khoản song song)"/>
+    <s v="Đang giai đoạn đàm phán về các điều khoản của hợp đồng."/>
     <m/>
   </r>
   <r>
-    <n v="4"/>
+    <n v="5"/>
     <x v="1"/>
     <x v="4"/>
     <s v="HK GLOBAL"/>
     <m/>
     <n v="8000000000"/>
+    <n v="0.15"/>
     <s v="Tháng 7"/>
     <x v="2"/>
     <s v="Holding"/>
     <n v="0.5"/>
-    <s v="Đang trao đổi, chào giá với CĐT, Đã gửi báo giá 2/6 cho chị Trang, Chờ phản hồi"/>
+    <s v="Update 13/06 đang trao đổi tiến độ báo giá, thi công căn mẫu ngày 10/6. Dự kiến 15/06 kí thỏa thuận hợp tác HK và FFok "/>
     <m/>
   </r>
   <r>
-    <n v="5"/>
+    <n v="6"/>
     <x v="1"/>
-    <x v="2"/>
+    <x v="3"/>
     <s v="Chị Huyền, Anh Trường"/>
     <m/>
     <n v="2500000000"/>
+    <n v="0.18"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Partner"/>
     <n v="0.6"/>
-    <s v="Đã qua khảo sát đo đạc cùng KH, đã gửi báo giá V1, Đang sửa báo giá V2 (chờ thầu báo lại)"/>
+    <s v="Đã gửi báo giá ngày 11/6. Đang chờ khách tham khảo và phản hồi"/>
     <m/>
   </r>
   <r>
-    <n v="6"/>
+    <n v="7"/>
     <x v="1"/>
     <x v="5"/>
     <s v="Chị Ngân"/>
     <m/>
     <n v="500000000"/>
+    <n v="0.2"/>
     <s v="Tháng 7"/>
     <x v="2"/>
     <s v="MKT"/>
     <n v="0.7"/>
-    <s v="Đã qua khảo sát đo đạc. Đang lên báo giá và tư vấn dự kiến tuần 2 tháng 6 gửi"/>
-    <m/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="1"/>
-    <x v="4"/>
-    <s v="Khách sạn Hạ Long_x000a_(Gói đồ rời)"/>
-    <m/>
-    <n v="190000000"/>
-    <s v="Tháng 7"/>
-    <x v="2"/>
-    <s v="Partner"/>
-    <n v="0.7"/>
-    <s v="Đang LV với Chị Dung bên GRD đã gửi và điều chỉnh BG lần 3 06/06"/>
+    <s v="Đã qua khảo sát đo đạc. Đang lên báo giá và tư vấn dự kiến sang tuần gửi khách"/>
     <m/>
   </r>
   <r>
@@ -1987,25 +2054,117 @@
     <s v="Chị Trường, Anh Giang"/>
     <m/>
     <n v="500000000"/>
+    <n v="0.2"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="WALK-IN"/>
     <n v="0.7"/>
-    <s v="Đag triển khai TK 3D."/>
+    <s v="Đã ký 3D, Đag triển khai TK 3D. "/>
     <m/>
   </r>
   <r>
     <n v="9"/>
     <x v="1"/>
-    <x v="5"/>
-    <s v="Vp AORA"/>
-    <m/>
-    <n v="2000000000"/>
+    <x v="6"/>
+    <s v="Chị Nguyệt Anh"/>
+    <m/>
+    <n v="400000000"/>
+    <n v="0.2"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="MKT"/>
     <n v="0.6"/>
-    <s v="Đang làm phương án concept. Dự kiến gửi concept cho KH 14/6._x000a_Dự kiến chốt thiết kế và chuyển đổi thi công 2 tỷ vào cuối tháng"/>
+    <s v="Gửi phương án concept cho KH 10/6._x000a_Dự kiến chốt thiết kế và chuyển đổi thi công 400 tr vào cuối tháng"/>
+    <m/>
+  </r>
+  <r>
+    <n v="10"/>
+    <x v="1"/>
+    <x v="7"/>
+    <s v="Chị Minh Thu"/>
+    <m/>
+    <n v="150000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.6"/>
+    <s v="Khách đã có thiết kế 3D, hẹn khách đầu tuần tới ngày 22/06 gửi lại báo giá."/>
+    <m/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="1"/>
+    <x v="7"/>
+    <s v="Chị Ngân Mỹ Đức"/>
+    <m/>
+    <n v="83000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.6"/>
+    <s v="18/06 đã báo giá, chờ khách phản hồi"/>
+    <m/>
+  </r>
+  <r>
+    <n v="12"/>
+    <x v="1"/>
+    <x v="7"/>
+    <s v="Anh Huy"/>
+    <m/>
+    <n v="20000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.6"/>
+    <s v="Đã lên thiết kế 3D, gửi báo giá chờ khách phản hồi. "/>
+    <m/>
+  </r>
+  <r>
+    <n v="13"/>
+    <x v="1"/>
+    <x v="8"/>
+    <s v="Anh Tiến Anh"/>
+    <m/>
+    <n v="300000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.8"/>
+    <s v="18/06 trao đổi với khách. Dự kiến ký thiết kế trước 13 triệu. Hẹn 23/06 phản hồi."/>
+    <m/>
+  </r>
+  <r>
+    <n v="14"/>
+    <x v="1"/>
+    <x v="8"/>
+    <s v="Chị Hồng"/>
+    <m/>
+    <n v="400000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.5"/>
+    <s v="16/06 trao đổi với khách. Dự kiến ký thiết kế trước. Hẹn ngày 22/06 phản hồi chốt hoặc không."/>
+    <m/>
+  </r>
+  <r>
+    <n v="15"/>
+    <x v="1"/>
+    <x v="8"/>
+    <s v="Anh Dũng Tuấn - B2B - Văn phòng hạng sang"/>
+    <m/>
+    <n v="2000000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 6"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.5"/>
+    <s v="19/06 Đang chào giá chủ đầu tư. Hẹn 23/06 gửi báo giá. "/>
     <m/>
   </r>
   <r>
@@ -2014,7 +2173,8 @@
     <x v="0"/>
     <m/>
     <m/>
-    <n v="20450000000"/>
+    <n v="18550000000"/>
+    <m/>
     <m/>
     <x v="0"/>
     <m/>
@@ -2025,10 +2185,11 @@
   <r>
     <n v="1"/>
     <x v="2"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Trường Ardyring Lào Cai"/>
     <m/>
-    <n v="3000000000"/>
+    <n v="4400000000"/>
+    <n v="0.25"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Partner"/>
@@ -2039,127 +2200,151 @@
   <r>
     <n v="2"/>
     <x v="2"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Trường Ardyring Lào Cai"/>
     <m/>
-    <n v="2000000000"/>
+    <n v="1200000000"/>
+    <n v="0.25"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Partner"/>
     <n v="0.7"/>
-    <s v="Các lớp học khối trung học _x000a_( đã gửi 3D, Báo giá cho CĐT ) 29/05_x000a_còn 3 phòng chức năng khác đang chạy 3D: dự kiến 09/06 trả CĐT_x000a_Phòng DA trình chủ tịch phê duyệt )"/>
+    <s v="Các lớp học khối trung học _x000a_( đã gửi 3D, Báo giá cho CĐT ) 29/05_x000a_còn 3 phòng chức năng khác đang chạy 3D: dự kiến 15/06 trả CĐT_x000a_Phòng DA trình chủ tịch phê duyệt )"/>
     <m/>
   </r>
   <r>
     <n v="3"/>
     <x v="2"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Căn mẫu Sunshine "/>
     <s v="Làm việc qua Ms Huyền GRD"/>
-    <n v="2100000000"/>
+    <n v="1300000000"/>
+    <n v="0.25"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Partner"/>
-    <n v="0.9"/>
-    <s v="Phụ lục hợp đồng 01: 1.260.000.000 vnđ :( Ký HĐ+ Ck tiền) từ GRD_x000a_(GRD đã làm xong bảo lãnh với CĐT ) _x000a_Phụ lục hợp đồng 02: 1.000.000.000 vnđ : 10/06 ký phát sinh _x000a_CĐT đã chốt PA &amp; Speck vật liệu : 05/06/2026"/>
+    <n v="0.7"/>
+    <s v="1/ Phụ lục hợp đồng 01: 1.260.000.000 vnđ :( Ký HĐ+ Ck tiền) từ GRD_x000a_(GRD đã làm xong bảo lãnh với CĐT ) _x000a_chờ CĐT chuyển tiền &gt;&gt; thi công_x000a_2/ Phụ lục hợp đồng 02: 1.000.000.000 vnđ : 12/06 đã gửi lại BOQ theo speck mới _x000a_CĐT đã chốt PA &amp; Speck vật liệu : 12/06/2026_x000a_Chờ CEO duyệt báo giá: 17/06"/>
     <m/>
   </r>
   <r>
     <n v="4"/>
     <x v="2"/>
-    <x v="6"/>
+    <x v="9"/>
     <s v="Đoàn Thị Điểm"/>
     <m/>
-    <n v="600000000"/>
+    <n v="800000000"/>
+    <n v="0.25"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Partner"/>
     <n v="1"/>
-    <s v="Đã chốt layout, Speck, 3D gửi CĐT : 10/06_x000a_Khái toán: đã gửi CĐT đồng ý khái toán "/>
+    <s v="3D gửi CĐT : chốt ( 2 phòng : Thư viện, Tuyển sinh) 10.06_x000a_3D phòng Hội trường gửi CDT 13/06_x000a_Chờ CDT phê duyệt 3D: 15/06_x000a_&gt;&gt; gửi phụ lục psinh : 17/06 _x000a_"/>
     <m/>
   </r>
   <r>
     <n v="5"/>
     <x v="2"/>
-    <x v="6"/>
-    <s v="Anh Tùng"/>
-    <m/>
-    <n v="2900000000"/>
-    <s v="30/06"/>
+    <x v="9"/>
+    <s v="HASCO-_x000a_ Deawoo Kim mã"/>
+    <m/>
+    <n v="1200000000"/>
+    <n v="0.25"/>
+    <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Reference"/>
-    <n v="0.7"/>
-    <s v="Đã gửi Dự toán : 22/05_x000a_CĐT đang hoàn thiện xây dựng "/>
+    <n v="0.5"/>
+    <s v="1/ lên khái toán Fitout &amp; MEP cho CĐT : 15/06 Trả bài_x000a_2/ 2D bên CĐT đang thuê tk, họ sẽ gửi lại để check và hoàn thiện báo giá _x000a_&gt;&gt; Đàm phán thi công Fitout &amp;MEP trước để kịp tiến độ bàn giao_x000a_3/ Fur : chờ TK của cdt xong, gửi đầu bài để lên BOQ _x000a_&gt;&gt; chào thi công _x000a_(dự kiến : 800,000,000 Hoàn thiện)"/>
     <m/>
   </r>
   <r>
     <n v="6"/>
     <x v="2"/>
-    <x v="6"/>
-    <s v="Anh Nghĩa S8 (Biệt thự Đà Nẵng)"/>
-    <m/>
-    <n v="500000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Partner"/>
-    <n v="0.7"/>
-    <s v="Khách hàng đã gửi 3D,.2D : 22/05_x000a_Gửi Dự toán cho CĐT : 12/06/206"/>
+    <x v="9"/>
+    <s v="Anh Tùng"/>
+    <m/>
+    <n v="2900000000"/>
+    <n v="0.25"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Reference"/>
+    <n v="0.5"/>
+    <s v="Đã gửi Dự toán : 22/05_x000a_CĐT đang xây thô "/>
     <m/>
   </r>
   <r>
     <n v="7"/>
     <x v="2"/>
-    <x v="6"/>
-    <s v="Khách sạn chị Trang HP"/>
-    <m/>
-    <n v="800000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Customer"/>
+    <x v="9"/>
+    <s v="Anh Nghĩa S8 (Biệt thự Đà Nẵng)"/>
+    <m/>
+    <n v="500000000"/>
+    <n v="0.25"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Partner"/>
     <n v="0.7"/>
-    <s v="Khách hàng đã gửi 3D : Khu sảnh lobby, lễ tân &amp; Nhà Hàng _x000a_Đã gửi Khái Toán : 28/05_x000a_điều chỉnh lại dự toán cân đối theo mức CĐT đầu tư 800 tr"/>
+    <s v="Khách hàng đã gửi 3D,.2D : 22/05_x000a_Gửi Dự toán cho CĐT : 19/06/206"/>
     <m/>
   </r>
   <r>
     <n v="8"/>
     <x v="2"/>
-    <x v="6"/>
-    <s v="Hóa dầu Quảng Ninh"/>
-    <m/>
-    <n v="8000000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Holding"/>
-    <n v="1"/>
-    <s v="BU1 &amp; BU2 &amp; BU3 "/>
+    <x v="9"/>
+    <s v="Khách sạn chị Trang HP"/>
+    <m/>
+    <n v="800000000"/>
+    <n v="0.25"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Customer"/>
+    <n v="0.5"/>
+    <s v="Khách hàng đã gửi 3D : Khu sảnh lobby, lễ tân &amp; Nhà Hàng _x000a_Đã gửi Khái Toán : 28/05_x000a_điều chỉnh lại dự toán cân đối theo mức CĐT đầu tư 600 tr_x000a_17/06"/>
     <m/>
   </r>
   <r>
     <n v="9"/>
     <x v="2"/>
-    <x v="6"/>
-    <s v="Anh Trường (Long Biên)"/>
-    <m/>
-    <n v="250000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Facebook"/>
-    <n v="0.6"/>
-    <s v="Đang thiết kế 3D "/>
+    <x v="9"/>
+    <s v="Hóa dầu Quảng Ninh"/>
+    <m/>
+    <n v="5000000000"/>
+    <n v="0.25"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Holding"/>
+    <n v="0.9"/>
+    <s v="16/6 đi khảo sát, đang ra bản vẽ SOP và điều chỉnh lại báo giá gửi CĐT, bỏ hạng mục Thảm vì CĐT tự cung cấp"/>
     <m/>
   </r>
   <r>
     <n v="10"/>
     <x v="2"/>
-    <x v="6"/>
+    <x v="9"/>
+    <s v="Anh Trường (Long Biên)"/>
+    <m/>
+    <n v="250000000"/>
+    <n v="0.25"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Facebook"/>
+    <n v="0.5"/>
+    <s v="đã gửi TK, chờ CĐT chốt, nếu khách hàng chốt sẽ chuyển BU1 Triển khai (CĐT đã đặt cọc tiền tk)"/>
+    <m/>
+  </r>
+  <r>
+    <n v="11"/>
+    <x v="2"/>
+    <x v="9"/>
     <s v="Anh Vũ (Yên Hòa)"/>
     <m/>
-    <n v="300000000"/>
+    <n v="200000000"/>
+    <n v="0.2"/>
     <s v="Tháng 6"/>
     <x v="1"/>
     <s v="Customer"/>
-    <n v="0.6"/>
-    <s v="Đã khảo sát, đang lên thiết kế 3D"/>
+    <n v="0.5"/>
+    <s v="Đã khảo sát, đang chỉnh sửa lị thiết kế gửi khách"/>
     <m/>
   </r>
   <r>
@@ -2168,7 +2353,8 @@
     <x v="0"/>
     <m/>
     <m/>
-    <n v="310840000000"/>
+    <n v="236820000000"/>
+    <m/>
     <m/>
     <x v="0"/>
     <m/>
@@ -2179,136 +2365,146 @@
   <r>
     <n v="1"/>
     <x v="3"/>
-    <x v="7"/>
+    <x v="10"/>
     <s v="Anh Phú The Charm"/>
     <m/>
     <n v="300000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
+    <n v="0.21"/>
+    <s v="Tuần 1 tháng 7"/>
+    <x v="2"/>
     <s v="MKT"/>
     <n v="0.9"/>
-    <s v="Đã ký HĐ khung, đang triển khai 3D, dự kiến cuối tháng 5 chuyển đổi thi công"/>
+    <s v="Đã ký HĐ khung, đang triển khai 3D, dự kiến đầu tháng 7 chuyển đổi thi công"/>
     <m/>
   </r>
   <r>
     <n v="2"/>
     <x v="3"/>
-    <x v="8"/>
-    <s v="Thiết kế nhà a Hân - Thái Nguyên"/>
-    <m/>
-    <n v="80000000"/>
-    <s v="Tháng 6"/>
+    <x v="10"/>
+    <s v="Anh Minh"/>
+    <m/>
+    <n v="130000000"/>
+    <n v="0.22"/>
+    <s v="28/06/2026"/>
     <x v="1"/>
-    <s v="Sale tự kiếm"/>
-    <n v="0.7"/>
-    <s v="Đang tư vấn thiết kế sơ bộ"/>
+    <s v="MKT"/>
+    <n v="0.85"/>
+    <s v="Đã ký HĐTK. KH đã chốt 3D. _x000a_KH đang cân đối giá "/>
     <m/>
   </r>
   <r>
     <n v="3"/>
     <x v="3"/>
-    <x v="8"/>
-    <s v="Booyoung - Campuchia"/>
-    <m/>
-    <n v="30000000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Đối tác"/>
-    <n v="0.8"/>
-    <s v="06/06 đã ok mẫu sơn, hàng hóa; CĐT yêu cầu điều chỉnh lại một chút kích thước._x000a_Sang tuần sẽ đẩy hợp đồng để ký kết"/>
+    <x v="11"/>
+    <s v="Thiết kế nhà a Hân - Thái Nguyên"/>
+    <m/>
+    <n v="80000000"/>
+    <n v="0.2"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Sale tự kiếm"/>
+    <n v="0.7"/>
+    <s v="Đang tư vấn thiết kế sơ bộ, khách chưa làm đk thủ tục chuyển nhượng đất"/>
     <m/>
   </r>
   <r>
     <n v="4"/>
     <x v="3"/>
-    <x v="9"/>
-    <s v="Chị Trang Timecity"/>
-    <m/>
-    <n v="95000000"/>
-    <s v="12/06/2026"/>
-    <x v="1"/>
-    <s v="MKT"/>
-    <n v="0.6"/>
-    <s v="25/5 KH đã ký hợp đồng thiết kế_x000a_Dự kiến ký thi công vào đầu tháng 6"/>
+    <x v="11"/>
+    <s v="Booyoung - Campuchia"/>
+    <m/>
+    <n v="30000000000"/>
+    <n v="0.18"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
+    <s v="Đối tác"/>
+    <n v="0.8"/>
+    <s v="Đang triển khai Hợp đồng đặt hàng mẫu (lần 2) vs thầu mới"/>
     <m/>
   </r>
   <r>
     <n v="5"/>
     <x v="3"/>
-    <x v="7"/>
-    <s v="Anh Ngọc"/>
-    <m/>
-    <n v="100000000"/>
-    <s v="12/06/2026"/>
+    <x v="12"/>
+    <s v="Chị Trang Timecity"/>
+    <m/>
+    <n v="95000000"/>
+    <n v="0.23"/>
+    <s v="28/06/2026"/>
     <x v="1"/>
     <s v="MKT"/>
-    <n v="0.7"/>
-    <s v="KH đang điều chỉnh lại Layout"/>
+    <n v="0.6"/>
+    <s v="25/5 KH đã ký hợp đồng thiết kế_x000a_Đã chốt 3D, đang điều chỉnh HSKT."/>
     <m/>
   </r>
   <r>
     <n v="6"/>
     <x v="3"/>
-    <x v="8"/>
+    <x v="10"/>
+    <s v="Anh Ngọc"/>
+    <m/>
+    <n v="100000000"/>
+    <n v="0.2"/>
+    <s v="26/06/2026"/>
+    <x v="1"/>
+    <s v="MKT"/>
+    <n v="0.7"/>
+    <s v="Đã chốt 3D, đang triển khai HSKT"/>
+    <m/>
+  </r>
+  <r>
+    <n v="7"/>
+    <x v="3"/>
+    <x v="11"/>
     <s v="HDB Thanh Trì"/>
     <m/>
     <n v="60000000000"/>
+    <n v="0.08"/>
     <s v="Tháng 7"/>
     <x v="2"/>
     <s v="Đối tác"/>
     <n v="0.8"/>
-    <s v="04/06 đã đi gặp CĐT (sếp Trung đi cùng)_x000a_Đang điều chỉnh giá"/>
-    <m/>
-  </r>
-  <r>
-    <n v="7"/>
-    <x v="3"/>
-    <x v="8"/>
-    <s v="Cụm 36 Biệt thự Ecopark"/>
-    <m/>
-    <n v="60000000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
-    <s v="Tự kiếm"/>
-    <n v="0.8"/>
-    <s v="29/05/2026 đã vào gặp chủ đầu tư với sếp Trung và sếp Thuân_x000a_07/06 gửi BOQ cho Ban Thư ký của Chủ Tịch để trình ký"/>
+    <s v="19/06 đã đi gặp CĐT (sếp Trung, sếp Thuân đi cùng)_x000a_Đang điều chỉnh giá"/>
     <m/>
   </r>
   <r>
     <n v="8"/>
     <x v="3"/>
-    <x v="9"/>
-    <s v="Minh Châu"/>
-    <m/>
-    <n v="115000000"/>
-    <s v="10/06/2026"/>
-    <x v="1"/>
-    <s v="MKT"/>
+    <x v="11"/>
+    <s v="Cụm 36 Biệt thự Ecopark"/>
+    <m/>
+    <n v="60000000000"/>
+    <n v="0.15"/>
+    <s v="Tuần 1 tháng 7"/>
+    <x v="2"/>
+    <s v="Tự kiếm"/>
     <n v="0.8"/>
-    <s v="Đang triển khai 3D"/>
+    <s v="20/06 đang làm việc lại về tiến độ phần thô. Tuần 4 tháng 6 họp trao đổi về Hợp đồng."/>
     <m/>
   </r>
   <r>
     <n v="9"/>
     <x v="3"/>
-    <x v="9"/>
-    <s v="Chú Phước"/>
-    <m/>
-    <n v="150000000"/>
-    <s v="25/06/2026"/>
+    <x v="12"/>
+    <s v="Minh Châu"/>
+    <m/>
+    <n v="115000000"/>
+    <n v="0.25"/>
+    <s v="29/06/2026"/>
     <x v="1"/>
     <s v="MKT"/>
-    <n v="0.75"/>
-    <s v="Khách đang xem dự thảo hợp đồng"/>
+    <n v="0.8"/>
+    <s v="Đã chốt 3D, đang đợi ván nên lùi lịch ký PL Thi công đến cuối tháng 6"/>
     <m/>
   </r>
   <r>
     <n v="10"/>
     <x v="3"/>
-    <x v="8"/>
+    <x v="11"/>
     <s v="Nội thất 328 căn Chung cư Ecopark Sông Lam"/>
     <m/>
     <n v="80000000000"/>
+    <n v="0.15"/>
     <s v="Tháng 8"/>
     <x v="2"/>
     <s v="Tự kiếm"/>
@@ -2319,15 +2515,16 @@
   <r>
     <n v="11"/>
     <x v="3"/>
-    <x v="8"/>
+    <x v="11"/>
     <s v="Bệnh viện Thạch Thất"/>
     <m/>
-    <n v="80000000000"/>
-    <s v="Tháng 6"/>
-    <x v="1"/>
+    <n v="6000000000"/>
+    <n v="0.08"/>
+    <s v="Tháng 7"/>
+    <x v="2"/>
     <s v="Đối tác"/>
     <n v="0.8"/>
-    <s v="CĐT đã có bảng báo giá, Đang đàm phán hợp đồng và giá để chốt ký hợp đồng"/>
+    <s v="Triển khai trước phần ép cọc."/>
     <m/>
   </r>
   <r>
@@ -2336,7 +2533,8 @@
     <x v="0"/>
     <m/>
     <m/>
-    <n v="356530000000"/>
+    <n v="282223000000"/>
+    <m/>
     <m/>
     <x v="0"/>
     <m/>
@@ -2348,18 +2546,19 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="B3:D17" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
-  <pivotFields count="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="B3:D14" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="13">
     <pivotField compact="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" showAll="0" sortType="descending">
-      <items count="8">
+      <items count="9">
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="0"/>
+        <item m="1" x="7"/>
+        <item x="4"/>
         <item m="1" x="6"/>
-        <item x="4"/>
         <item m="1" x="5"/>
         <item t="default"/>
       </items>
@@ -2374,34 +2573,37 @@
       </autoSortScope>
     </pivotField>
     <pivotField axis="axisRow" compact="0" showAll="0" sortType="descending">
-      <items count="28">
-        <item m="1" x="10"/>
-        <item x="7"/>
-        <item m="1" x="20"/>
+      <items count="31">
+        <item m="1" x="14"/>
+        <item x="10"/>
         <item m="1" x="23"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item m="1" x="21"/>
-        <item m="1" x="22"/>
+        <item m="1" x="26"/>
+        <item x="2"/>
+        <item x="11"/>
         <item m="1" x="24"/>
+        <item m="1" x="25"/>
+        <item m="1" x="27"/>
         <item x="5"/>
         <item x="1"/>
-        <item m="1" x="11"/>
-        <item m="1" x="26"/>
-        <item m="1" x="14"/>
-        <item m="1" x="25"/>
+        <item m="1" x="15"/>
+        <item m="1" x="29"/>
+        <item m="1" x="18"/>
+        <item m="1" x="28"/>
+        <item m="1" x="20"/>
+        <item x="0"/>
+        <item m="1" x="19"/>
+        <item m="1" x="21"/>
+        <item x="7"/>
+        <item m="1" x="22"/>
         <item m="1" x="16"/>
-        <item x="0"/>
-        <item m="1" x="15"/>
-        <item m="1" x="18"/>
+        <item x="3"/>
         <item m="1" x="17"/>
-        <item m="1" x="19"/>
-        <item m="1" x="12"/>
-        <item x="2"/>
+        <item x="9"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="6"/>
+        <item x="8"/>
         <item m="1" x="13"/>
-        <item x="6"/>
-        <item x="4"/>
-        <item x="9"/>
         <item t="default"/>
       </items>
       <autoSortScope>
@@ -2417,11 +2619,12 @@
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0">
       <items count="4">
-        <item x="1"/>
-        <item h="1" x="2"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
         <item h="1" x="0"/>
         <item t="default"/>
       </items>
@@ -2435,7 +2638,7 @@
     <field x="1"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="14">
+  <rowItems count="11">
     <i>
       <x v="2"/>
     </i>
@@ -2445,35 +2648,26 @@
     <i r="1">
       <x v="1"/>
     </i>
+    <i>
+      <x/>
+    </i>
     <i r="1">
-      <x v="26"/>
+      <x v="25"/>
+    </i>
+    <i r="1">
+      <x v="22"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i r="1">
       <x v="24"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="22"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
@@ -2555,8 +2749,8 @@
   <data>
     <tabular pivotCacheId="1568755218">
       <items count="3">
-        <i x="1" s="1"/>
-        <i x="2"/>
+        <i x="1"/>
+        <i x="2" s="1"/>
         <i x="0"/>
       </items>
     </tabular>
@@ -2571,8 +2765,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M48" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A3:M48" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A3:M52" xr:uid="{00000000-0009-0000-0100-000005000000}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="Facebook"/>
+        <filter val="MKT"/>
+        <filter val="WALK-IN"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="10">
+      <filters blank="1">
+        <filter val="100%"/>
+        <filter val="50%"/>
+        <filter val="60%"/>
+        <filter val="70%"/>
+        <filter val="80%"/>
+        <filter val="85%"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STT" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phòng ban" dataDxfId="11"/>
@@ -2866,149 +3078,122 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17">
-        <v>170840000000</v>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16">
+        <v>236380000000</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="16"/>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="17">
-        <v>170080000000</v>
+      <c r="D5" s="16">
+        <v>236080000000</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="15"/>
+      <c r="C6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="17">
-        <v>400000000</v>
+      <c r="D6" s="16">
+        <v>300000000</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="16"/>
-      <c r="C7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="17">
-        <v>360000000</v>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16">
+        <v>17000000000</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17">
-        <v>20450000000</v>
+      <c r="D8" s="16">
+        <v>8000000000</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="16"/>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="15"/>
+      <c r="C9" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="17">
-        <v>20450000000</v>
+      <c r="D9" s="16">
+        <v>7000000000</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15"/>
+      <c r="C10" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17">
-        <v>15300000000</v>
+      <c r="D10" s="16">
+        <v>1500000000</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="15"/>
+      <c r="C11" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="17">
-        <v>11800000000</v>
+      <c r="D11" s="16">
+        <v>500000000</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="16"/>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="17">
-        <v>2000000000</v>
-      </c>
-      <c r="G12" s="41"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16">
+        <v>9450000000</v>
+      </c>
+      <c r="G12" s="38"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="16"/>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="17">
-        <v>1000000000</v>
+      <c r="D13" s="16">
+        <v>9450000000</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="16"/>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="17">
-        <v>500000000</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17">
-        <v>1250000000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="17">
-        <v>1250000000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17">
-        <v>207840000000</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="H26" s="41"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16">
+        <v>262830000000</v>
+      </c>
+    </row>
+    <row r="26" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H26" s="38"/>
     </row>
     <row r="42" spans="12:12" x14ac:dyDescent="0.2">
       <c r="L42" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3026,121 +3211,125 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="22" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="23.125" style="22" customWidth="1"/>
-    <col min="4" max="4" width="35.625" style="22" customWidth="1"/>
-    <col min="5" max="5" width="24.875" style="22" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="22.75" style="22" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="47" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="28" customWidth="1"/>
-    <col min="9" max="9" width="23.375" style="22" customWidth="1"/>
+    <col min="1" max="1" width="9.125" style="21" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="22" customWidth="1"/>
+    <col min="3" max="3" width="23.125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="35.625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="24.875" style="21" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="22.75" style="21" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="60" customWidth="1"/>
+    <col min="8" max="8" width="15.875" style="22" customWidth="1"/>
+    <col min="9" max="9" width="23.375" style="21" customWidth="1"/>
     <col min="10" max="10" width="23" style="22" customWidth="1"/>
-    <col min="11" max="11" width="16.625" style="22" customWidth="1"/>
-    <col min="12" max="12" width="85.25" style="22" customWidth="1"/>
-    <col min="13" max="13" width="24" style="40" customWidth="1"/>
-    <col min="14" max="16384" width="9.125" style="22"/>
+    <col min="11" max="11" width="16.625" style="21" customWidth="1"/>
+    <col min="12" max="12" width="85.25" style="21" customWidth="1"/>
+    <col min="13" max="13" width="24" style="37" customWidth="1"/>
+    <col min="14" max="16384" width="9.125" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="82"/>
+      <c r="L1" s="82"/>
+      <c r="M1" s="82"/>
+    </row>
+    <row r="2" spans="1:15" ht="8.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G2" s="44"/>
+      <c r="H2" s="27"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="3" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-    </row>
-    <row r="2" spans="1:15" ht="8.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="20" t="s">
+      <c r="G3" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="H3" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="I3" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="48" t="s">
+      <c r="J3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="K3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="L3" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="M3" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="20" t="s">
+    </row>
+    <row r="4" spans="1:15" s="23" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="B4" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="M3" s="21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="8">
         <f>+SUBTOTAL(9,F5:F7)</f>
-        <v>2600000000</v>
-      </c>
-      <c r="G4" s="49"/>
-      <c r="H4" s="13"/>
+        <v>2700000000</v>
+      </c>
+      <c r="G4" s="46"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="7"/>
-      <c r="M4" s="37"/>
-    </row>
-    <row r="5" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M4" s="34"/>
+    </row>
+    <row r="5" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>15</v>
+        <v>28</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="F5" s="2">
         <v>2000000000</v>
@@ -3148,35 +3337,35 @@
       <c r="G5" s="12">
         <v>0.2</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="38"/>
-    </row>
-    <row r="6" spans="1:15" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M5" s="35"/>
+    </row>
+    <row r="6" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>15</v>
+        <v>28</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
@@ -3185,205 +3374,208 @@
       <c r="G6" s="12">
         <v>0.2</v>
       </c>
-      <c r="H6" s="42" t="s">
-        <v>33</v>
+      <c r="H6" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="K6" s="12">
         <v>0.7</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" s="38"/>
-    </row>
-    <row r="7" spans="1:15" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="M6" s="35"/>
+    </row>
+    <row r="7" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>15</v>
+        <v>28</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>100000000</v>
+        <v>200000000</v>
       </c>
       <c r="G7" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H7" s="42" t="s">
-        <v>40</v>
+        <v>0.19</v>
+      </c>
+      <c r="H7" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="K7" s="12">
         <v>0.7</v>
       </c>
-      <c r="L7" s="1"/>
-      <c r="M7" s="38"/>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-    </row>
-    <row r="8" spans="1:15" s="26" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="L7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="M7" s="35"/>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+    </row>
+    <row r="8" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.19</v>
+      </c>
+      <c r="H8" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="35"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+    </row>
+    <row r="9" spans="1:15" s="25" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="50"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
+        <f>+SUBTOTAL(9,F10:F28)</f>
+        <v>27693000000</v>
+      </c>
+      <c r="G9" s="46"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="34"/>
+    </row>
+    <row r="10" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="8">
-        <f>+SUBTOTAL(9,F9:F23)</f>
-        <v>24253000000</v>
-      </c>
-      <c r="G8" s="51"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="37"/>
-    </row>
-    <row r="9" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="57" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2">
-        <v>500000000</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.3</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M9" s="38"/>
-      <c r="N9" s="25"/>
-    </row>
-    <row r="10" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>12</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="2">
-        <v>1000000000</v>
+        <v>500000000</v>
       </c>
       <c r="G10" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H10" s="42" t="s">
-        <v>43</v>
+        <v>0.3</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>44</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>45</v>
       </c>
       <c r="K10" s="12">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="38"/>
-      <c r="N10" s="25"/>
-    </row>
-    <row r="11" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+      <c r="M10" s="35"/>
+      <c r="N10" s="24"/>
+    </row>
+    <row r="11" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="57" t="s">
-        <v>10</v>
-      </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="2">
-        <v>7000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G11" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>43</v>
+        <v>0.25</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>44</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K11" s="12">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M11" s="38"/>
-      <c r="N11" s="25"/>
-    </row>
-    <row r="12" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+      <c r="M11" s="35"/>
+      <c r="N11" s="24"/>
+    </row>
+    <row r="12" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="56">
         <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>52</v>
@@ -3395,36 +3587,36 @@
       <c r="G12" s="12">
         <v>0.2</v>
       </c>
-      <c r="H12" s="42" t="s">
-        <v>33</v>
+      <c r="H12" s="39" t="s">
+        <v>37</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K12" s="12">
         <v>0.7</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="38"/>
-      <c r="N12" s="25"/>
-    </row>
-    <row r="13" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10">
+        <v>54</v>
+      </c>
+      <c r="M12" s="35"/>
+      <c r="N12" s="24"/>
+    </row>
+    <row r="13" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="56">
         <v>5</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="57" t="s">
-        <v>13</v>
+        <v>6</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="2">
@@ -3433,36 +3625,36 @@
       <c r="G13" s="12">
         <v>0.15</v>
       </c>
-      <c r="H13" s="42" t="s">
-        <v>43</v>
+      <c r="H13" s="39" t="s">
+        <v>44</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K13" s="12">
         <v>0.5</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="M13" s="38"/>
-      <c r="N13" s="25"/>
-    </row>
-    <row r="14" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="M13" s="35"/>
+      <c r="N13" s="24"/>
+    </row>
+    <row r="14" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>8</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="2">
@@ -3471,36 +3663,36 @@
       <c r="G14" s="12">
         <v>0.18</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J14" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K14" s="12">
         <v>0.6</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="38"/>
-      <c r="N14" s="25"/>
-    </row>
-    <row r="15" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+      <c r="M14" s="35"/>
+      <c r="N14" s="24"/>
+    </row>
+    <row r="15" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="57" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2">
@@ -3509,11 +3701,11 @@
       <c r="G15" s="12">
         <v>0.2</v>
       </c>
-      <c r="H15" s="42" t="s">
-        <v>43</v>
+      <c r="H15" s="39" t="s">
+        <v>44</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>45</v>
@@ -3522,74 +3714,74 @@
         <v>0.7</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M15" s="38"/>
-      <c r="N15" s="25"/>
-    </row>
-    <row r="16" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10">
+        <v>61</v>
+      </c>
+      <c r="M15" s="35"/>
+      <c r="N15" s="24"/>
+    </row>
+    <row r="16" spans="1:15" s="72" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="73">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>61</v>
+      <c r="B16" s="64" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="66" t="s">
+        <v>63</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="2">
+      <c r="F16" s="67">
         <v>500000000</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="68">
         <v>0.2</v>
       </c>
-      <c r="H16" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K16" s="12">
+      <c r="H16" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="68">
         <v>0.7</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M16" s="38"/>
-      <c r="N16" s="25"/>
-    </row>
-    <row r="17" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L16" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="M16" s="70"/>
+      <c r="N16" s="71"/>
+    </row>
+    <row r="17" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="57" t="s">
-        <v>64</v>
+        <v>6</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>66</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2">
-        <v>400000000</v>
+        <v>150000000</v>
       </c>
       <c r="G17" s="12">
         <v>0.2</v>
       </c>
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>45</v>
@@ -3598,112 +3790,114 @@
         <v>0.6</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M17" s="35"/>
+      <c r="N17" s="24"/>
+    </row>
+    <row r="18" spans="1:15" s="72" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="63">
+        <f>A17+1</f>
+        <v>11</v>
+      </c>
+      <c r="B18" s="64" t="str">
+        <f>B17</f>
+        <v>BU 1</v>
+      </c>
+      <c r="C18" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="M17" s="38"/>
-      <c r="N17" s="25"/>
-    </row>
-    <row r="18" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10">
-        <v>10</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>68</v>
+      <c r="D18" s="66" t="s">
+        <v>69</v>
       </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="2">
-        <v>150000000</v>
-      </c>
-      <c r="G18" s="12">
+      <c r="F18" s="67">
+        <v>85000000</v>
+      </c>
+      <c r="G18" s="68">
         <v>0.2</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="68">
+        <v>0.9</v>
+      </c>
+      <c r="L18" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="M18" s="70"/>
+      <c r="N18" s="71"/>
+    </row>
+    <row r="19" spans="1:15" s="26" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="56">
+        <v>12</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="77">
+        <v>200000000</v>
+      </c>
+      <c r="G19" s="78">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="J19" s="53" t="s">
         <v>45</v>
       </c>
-      <c r="K18" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M18" s="38"/>
-      <c r="N18" s="25"/>
-    </row>
-    <row r="19" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10">
-        <v>11</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="2">
-        <v>83000000</v>
-      </c>
-      <c r="G19" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H19" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M19" s="38"/>
-      <c r="N19" s="25"/>
-    </row>
-    <row r="20" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K19" s="78">
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="M19" s="80"/>
+      <c r="N19" s="81"/>
+    </row>
+    <row r="20" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>72</v>
+        <v>6</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="2">
-        <v>20000000</v>
+        <v>300000000</v>
       </c>
       <c r="G20" s="12">
         <v>0.2</v>
       </c>
-      <c r="H20" s="42" t="s">
+      <c r="H20" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>45</v>
@@ -3712,1037 +3906,1202 @@
         <v>0.6</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20" s="35"/>
+      <c r="N20" s="24"/>
+    </row>
+    <row r="21" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10">
+        <v>14</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="M20" s="38"/>
-      <c r="N20" s="25"/>
-    </row>
-    <row r="21" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10">
-        <v>13</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>75</v>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="2">
-        <v>300000000</v>
+        <v>400000000</v>
       </c>
       <c r="G21" s="12">
         <v>0.2</v>
       </c>
-      <c r="H21" s="42" t="s">
+      <c r="H21" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>45</v>
       </c>
       <c r="K21" s="12">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M21" s="38"/>
-      <c r="N21" s="25"/>
-    </row>
-    <row r="22" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="M21" s="35"/>
+      <c r="N21" s="24"/>
+    </row>
+    <row r="22" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="57" t="s">
-        <v>74</v>
+        <v>6</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="2">
-        <v>400000000</v>
+        <v>7000000000</v>
       </c>
       <c r="G22" s="12">
         <v>0.2</v>
       </c>
-      <c r="H22" s="42" t="s">
+      <c r="H22" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>45</v>
       </c>
       <c r="K22" s="12">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M22" s="38"/>
-      <c r="N22" s="25"/>
-    </row>
-    <row r="23" spans="1:15" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="M22" s="35"/>
+      <c r="N22" s="24"/>
+    </row>
+    <row r="23" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="57" t="s">
-        <v>74</v>
+        <v>6</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="1"/>
+        <v>80</v>
+      </c>
+      <c r="E23" s="2">
+        <v>400000000</v>
+      </c>
       <c r="F23" s="2">
-        <v>2000000000</v>
+        <v>8000000</v>
       </c>
       <c r="G23" s="12">
         <v>0.2</v>
       </c>
-      <c r="H23" s="42" t="s">
+      <c r="H23" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>45</v>
       </c>
       <c r="K23" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M23" s="35"/>
+      <c r="N23" s="24"/>
+    </row>
+    <row r="24" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="10">
+        <v>17</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="12">
         <v>0.5</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M23" s="38"/>
-      <c r="N23" s="25"/>
-    </row>
-    <row r="24" spans="1:15" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="56"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8">
-        <f>+SUBTOTAL(9,F25:F35)</f>
-        <v>18550000000</v>
-      </c>
-      <c r="G24" s="51"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="37"/>
-    </row>
-    <row r="25" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>1</v>
+      <c r="L24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="M24" s="35"/>
+      <c r="N24" s="24"/>
+    </row>
+    <row r="25" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="10">
+        <v>16</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="51" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="1"/>
+        <v>85</v>
+      </c>
+      <c r="E25" s="2">
+        <v>250000000</v>
+      </c>
       <c r="F25" s="2">
-        <v>4400000000</v>
+        <v>250000000</v>
       </c>
       <c r="G25" s="12">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="58" t="s">
-        <v>34</v>
-      </c>
       <c r="J25" s="4" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="K25" s="12">
         <v>0.7</v>
       </c>
-      <c r="L25" s="44" t="s">
-        <v>83</v>
-      </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-    </row>
-    <row r="26" spans="1:15" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3">
-        <v>2</v>
+      <c r="L25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M25" s="35"/>
+      <c r="N25" s="24"/>
+    </row>
+    <row r="26" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10">
+        <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="51" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="1"/>
+        <v>89</v>
+      </c>
+      <c r="E26" s="2">
+        <v>400000000</v>
+      </c>
       <c r="F26" s="2">
-        <v>1200000000</v>
+        <v>900000000</v>
       </c>
       <c r="G26" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H26" s="4" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="H26" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="58" t="s">
-        <v>34</v>
-      </c>
       <c r="J26" s="4" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="K26" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L26" s="44" t="s">
-        <v>84</v>
-      </c>
-      <c r="M26" s="38"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-    </row>
-    <row r="27" spans="1:15" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3">
-        <v>3</v>
+        <v>0.6</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M26" s="35"/>
+      <c r="N26" s="24"/>
+    </row>
+    <row r="27" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="10">
+        <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="51" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="E27" s="2">
+        <v>400000000</v>
       </c>
       <c r="F27" s="2">
-        <v>1300000000</v>
+        <v>3000000000</v>
       </c>
       <c r="G27" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H27" s="4" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="H27" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="58" t="s">
-        <v>34</v>
-      </c>
       <c r="J27" s="4" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="K27" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L27" s="44" t="s">
+        <v>0.6</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M27" s="35"/>
+      <c r="N27" s="24"/>
+    </row>
+    <row r="28" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="10">
+        <v>20</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F28" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="G28" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H28" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="M27" s="38"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-    </row>
-    <row r="28" spans="1:15" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
-        <v>4</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="2">
-        <v>800000000</v>
-      </c>
-      <c r="G28" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I28" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="K28" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M28" s="35"/>
+      <c r="N28" s="24"/>
+    </row>
+    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="50"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="8">
+        <f>+SUBTOTAL(9,F30:F40)</f>
+        <v>20666000000</v>
+      </c>
+      <c r="G29" s="46"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="34"/>
+    </row>
+    <row r="30" spans="1:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>1</v>
       </c>
-      <c r="L28" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="M28" s="38"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-    </row>
-    <row r="29" spans="1:15" ht="134.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
-        <v>5</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="2">
-        <v>1200000000</v>
-      </c>
-      <c r="G29" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I29" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K29" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L29" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="M29" s="38"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-    </row>
-    <row r="30" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
-        <v>6</v>
-      </c>
       <c r="B30" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="54" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="2">
-        <v>2900000000</v>
+        <v>3800000000</v>
       </c>
       <c r="G30" s="12">
         <v>0.25</v>
       </c>
-      <c r="H30" s="42" t="s">
-        <v>43</v>
+      <c r="H30" s="57" t="s">
+        <v>44</v>
       </c>
       <c r="I30" s="58" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="K30" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="M30" s="38"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-    </row>
-    <row r="31" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+      <c r="L30" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="M30" s="35"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+    </row>
+    <row r="31" spans="1:15" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="2">
-        <v>500000000</v>
-      </c>
-      <c r="G31" s="12">
+        <v>1200000000</v>
+      </c>
+      <c r="G31" s="55">
         <v>0.25</v>
       </c>
-      <c r="H31" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I31" s="4" t="s">
+      <c r="H31" s="54" t="s">
         <v>44</v>
       </c>
+      <c r="I31" s="56" t="s">
+        <v>33</v>
+      </c>
       <c r="J31" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K31" s="12">
         <v>0.7</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="M31" s="38"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-    </row>
-    <row r="32" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L31" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+    </row>
+    <row r="32" spans="1:15" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="54" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="C32" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="1"/>
+        <v>100</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="F32" s="2">
-        <v>800000000</v>
+        <v>2400000000</v>
       </c>
       <c r="G32" s="12">
         <v>0.25</v>
       </c>
-      <c r="H32" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I32" s="58" t="s">
-        <v>44</v>
+      <c r="H32" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="18" t="s">
+        <v>38</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="K32" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="M32" s="38"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-    </row>
-    <row r="33" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+      <c r="L32" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="M32" s="35"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+    </row>
+    <row r="33" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="54" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="C33" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="2">
-        <v>5000000000</v>
+        <v>816000000</v>
       </c>
       <c r="G33" s="12">
         <v>0.25</v>
       </c>
-      <c r="H33" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>44</v>
+      <c r="H33" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="53" t="s">
+        <v>38</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K33" s="12">
         <v>0.9</v>
       </c>
-      <c r="L33" s="55" t="s">
-        <v>101</v>
-      </c>
-      <c r="M33" s="38"/>
-    </row>
-    <row r="34" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="L33" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+    </row>
+    <row r="34" spans="1:15" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="54" t="s">
-        <v>8</v>
+        <v>11</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>12</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="2">
-        <v>250000000</v>
+        <v>2800000000</v>
       </c>
       <c r="G34" s="12">
         <v>0.25</v>
       </c>
-      <c r="H34" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I34" s="58" t="s">
+      <c r="H34" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="I34" s="52" t="s">
+        <v>33</v>
+      </c>
       <c r="J34" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K34" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M34" s="38"/>
-    </row>
-    <row r="35" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0.7</v>
+      </c>
+      <c r="L34" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="M34" s="35"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+    </row>
+    <row r="35" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
+        <v>6</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="54" t="s">
-        <v>8</v>
+      <c r="C35" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="2">
-        <v>200000000</v>
+        <v>2900000000</v>
       </c>
       <c r="G35" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H35" s="42" t="s">
+        <v>0.25</v>
+      </c>
+      <c r="H35" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="I35" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>34</v>
-      </c>
       <c r="J35" s="4" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="K35" s="12">
         <v>0.5</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M35" s="38"/>
-    </row>
-    <row r="36" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="56"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8">
-        <f>+SUBTOTAL(9,F37:F47)</f>
-        <v>236820000000</v>
-      </c>
-      <c r="G36" s="51"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
-      <c r="K36" s="6"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="37"/>
-    </row>
-    <row r="37" spans="1:13" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10">
-        <v>1</v>
+        <v>109</v>
+      </c>
+      <c r="M35" s="35"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+    </row>
+    <row r="36" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>7</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" s="2">
+        <v>500000000</v>
+      </c>
+      <c r="G36" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H36" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K36" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M36" s="35"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+    </row>
+    <row r="37" spans="1:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>8</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="54" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="2">
-        <v>300000000</v>
+        <v>800000000</v>
       </c>
       <c r="G37" s="12">
-        <v>0.21</v>
-      </c>
-      <c r="H37" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="4" t="s">
+        <v>0.25</v>
+      </c>
+      <c r="H37" s="39" t="s">
         <v>44</v>
       </c>
+      <c r="I37" s="53" t="s">
+        <v>33</v>
+      </c>
       <c r="J37" s="4" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K37" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="M37" s="35"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+    </row>
+    <row r="38" spans="1:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>9</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="2">
+        <v>5000000000</v>
+      </c>
+      <c r="G38" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H38" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38" s="12">
         <v>0.9</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M37" s="38"/>
-    </row>
-    <row r="38" spans="1:13" s="23" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
-        <f t="shared" ref="A38:A46" si="0">A37+1</f>
+      <c r="L38" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="M38" s="35"/>
+    </row>
+    <row r="39" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>10</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" s="2">
+        <v>250000000</v>
+      </c>
+      <c r="G39" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H39" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I39" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K39" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M39" s="35"/>
+    </row>
+    <row r="40" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>11</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="2">
+        <v>200000000</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H40" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K40" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="M40" s="35"/>
+    </row>
+    <row r="41" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="50"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="8">
+        <f>+SUBTOTAL(9,F42:F51)</f>
+        <v>241085000000</v>
+      </c>
+      <c r="G41" s="46"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="34"/>
+    </row>
+    <row r="42" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="2">
+        <v>80000000</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H42" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K42" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M42" s="35"/>
+    </row>
+    <row r="43" spans="1:15" s="26" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <f t="shared" ref="A43:A51" si="0">A42+1</f>
         <v>2</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B43" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C38" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" s="4"/>
-      <c r="F38" s="52">
-        <v>130000000</v>
-      </c>
-      <c r="G38" s="12">
-        <v>0.22</v>
-      </c>
-      <c r="H38" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K38" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="L38" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="M38" s="53"/>
-    </row>
-    <row r="39" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
+      <c r="C43" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="2">
+        <v>30000000000</v>
+      </c>
+      <c r="G43" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H43" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K43" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M43" s="35"/>
+    </row>
+    <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B44" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C39" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" s="2">
-        <v>80000000</v>
-      </c>
-      <c r="G39" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H39" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="K39" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M39" s="38"/>
-    </row>
-    <row r="40" spans="1:13" s="27" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
+      <c r="C44" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="42"/>
+      <c r="F44" s="2">
+        <v>95000000</v>
+      </c>
+      <c r="G44" s="12">
+        <v>0.23</v>
+      </c>
+      <c r="H44" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K44" s="12">
+        <v>0.85</v>
+      </c>
+      <c r="L44" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="M44" s="35"/>
+    </row>
+    <row r="45" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B45" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C40" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E40" s="1"/>
-      <c r="F40" s="2">
-        <v>30000000000</v>
-      </c>
-      <c r="G40" s="12">
-        <v>0.18</v>
-      </c>
-      <c r="H40" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="K40" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="M40" s="38"/>
-    </row>
-    <row r="41" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
+      <c r="C45" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="42"/>
+      <c r="F45" s="2">
+        <v>110000000</v>
+      </c>
+      <c r="G45" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H45" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K45" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L45" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="M45" s="35"/>
+    </row>
+    <row r="46" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B46" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C41" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E41" s="45"/>
-      <c r="F41" s="2">
-        <v>95000000</v>
-      </c>
-      <c r="G41" s="12">
-        <v>0.23</v>
-      </c>
-      <c r="H41" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K41" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L41" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="M41" s="38"/>
-    </row>
-    <row r="42" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
+      <c r="C46" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="42"/>
+      <c r="F46" s="2">
+        <v>60000000000</v>
+      </c>
+      <c r="G46" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H46" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K46" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L46" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="M46" s="35"/>
+    </row>
+    <row r="47" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B47" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="57" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="2">
-        <v>100000000</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H42" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K42" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L42" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="M42" s="38"/>
-    </row>
-    <row r="43" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
+      <c r="C47" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="42"/>
+      <c r="F47" s="2">
+        <v>60000000000</v>
+      </c>
+      <c r="G47" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="H47" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="K47" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L47" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="M47" s="35"/>
+    </row>
+    <row r="48" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B48" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C43" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" s="45"/>
-      <c r="F43" s="2">
-        <v>60000000000</v>
-      </c>
-      <c r="G43" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="H43" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="K43" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="L43" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="M43" s="38"/>
-    </row>
-    <row r="44" spans="1:13" ht="67.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
+      <c r="C48" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E48" s="42"/>
+      <c r="F48" s="2">
+        <v>800000000</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.23</v>
+      </c>
+      <c r="H48" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K48" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L48" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="M48" s="35"/>
+    </row>
+    <row r="49" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B49" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C49" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="2">
-        <v>60000000000</v>
-      </c>
-      <c r="G44" s="12">
+      <c r="D49" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" s="42"/>
+      <c r="F49" s="2">
+        <v>80000000000</v>
+      </c>
+      <c r="G49" s="12">
         <v>0.15</v>
       </c>
-      <c r="H44" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K44" s="12">
+      <c r="H49" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="K49" s="12">
         <v>0.8</v>
       </c>
-      <c r="L44" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="M44" s="38"/>
-    </row>
-    <row r="45" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
+      <c r="L49" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="M49" s="35"/>
+    </row>
+    <row r="50" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B50" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="2">
-        <v>115000000</v>
-      </c>
-      <c r="G45" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H45" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="J45" s="4" t="s">
+      <c r="C50" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="42"/>
+      <c r="F50" s="47">
+        <v>4000000000</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H50" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J50" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="K45" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="L45" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="M45" s="38"/>
-    </row>
-    <row r="46" spans="1:13" ht="68.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
+      <c r="K50" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L50" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="M50" s="35"/>
+    </row>
+    <row r="51" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="57" t="s">
+      <c r="C51" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" s="45"/>
-      <c r="F46" s="2">
-        <v>80000000000</v>
-      </c>
-      <c r="G46" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="H46" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="I46" s="4" t="s">
+      <c r="D51" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E51" s="42"/>
+      <c r="F51" s="2">
+        <v>6000000000</v>
+      </c>
+      <c r="G51" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H51" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K46" s="12">
+      <c r="I51" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K51" s="12">
         <v>0.8</v>
       </c>
-      <c r="L46" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="M46" s="38"/>
-    </row>
-    <row r="47" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="10">
-        <v>11</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" s="45"/>
-      <c r="F47" s="2">
-        <v>6000000000</v>
-      </c>
-      <c r="G47" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="H47" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="K47" s="12">
-        <v>0.8</v>
-      </c>
-      <c r="L47" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="M47" s="38"/>
-    </row>
-    <row r="48" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="C48" s="32"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="34">
-        <f>SUBTOTAL(9,F4:F47)</f>
-        <v>282223000000</v>
-      </c>
-      <c r="G48" s="50"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="39"/>
-    </row>
-    <row r="49" spans="6:8" x14ac:dyDescent="0.2">
-      <c r="F49" s="25"/>
-      <c r="H49" s="29"/>
-    </row>
-    <row r="50" spans="6:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="6:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="6:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="L51" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="M51" s="35"/>
+    </row>
+    <row r="52" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="28"/>
+      <c r="B52" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="C52" s="30"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="32">
+        <f>SUBTOTAL(9,F4:F51)</f>
+        <v>292644000000</v>
+      </c>
+      <c r="G52" s="59"/>
+      <c r="H52" s="61"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="61"/>
+      <c r="K52" s="33"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="36"/>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F53" s="24"/>
+      <c r="H53" s="62"/>
+    </row>
+    <row r="54" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>

--- a/uploads/curr.xlsx
+++ b/uploads/curr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flexfitcom-my.sharepoint.com/personal/mont_flexfit_vn/Documents/MONT/Báo cáo doanh số/Báo cáo tiềm năng/Dữ liệu báo cáo tiềm năng/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{3A852FE8-40D6-450E-8607-96A050C672FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5E57DBA-443E-445B-B99D-B170A7FA527D}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{8A8335D2-215C-4E66-90FA-87646CF4424E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33394C9E-0A74-4CB6-B0BB-D2C47DE04C59}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,9 @@
   <definedNames>
     <definedName name="Slicer_Trạng_thái">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcOnSave="0"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="157">
   <si>
     <t>Phòng ban</t>
   </si>
@@ -161,10 +161,13 @@
 Sau khi sếp bên CĐT về và thống nhất định hướng triển khai thì sẽ liên hệ tao đổi lại</t>
   </si>
   <si>
+    <t>Ms Thuân</t>
+  </si>
+  <si>
     <t>Phát sinh KS Phú Quốc</t>
   </si>
   <si>
-    <t>Tuần 1 tháng 7</t>
+    <t>Tuần 2 tháng 7</t>
   </si>
   <si>
     <t>Dự kiến ký tháng</t>
@@ -173,10 +176,13 @@
     <t>QS đang trình sếp Khôi Nguyên duyệt, Cô Oanh đi công tác dự kiến tuần này sẽ phê duyệt</t>
   </si>
   <si>
-    <t>Phát sinh Netnam</t>
-  </si>
-  <si>
-    <t>Đã gửi PL phát sinh cho CĐT, đang ký trong ngày 30/06/2026</t>
+    <t>Ms Thuỷ</t>
+  </si>
+  <si>
+    <t>VP KNI</t>
+  </si>
+  <si>
+    <t>Đã gửi báo giá cho CĐT đang chờ CĐT phê duyệt</t>
   </si>
   <si>
     <t>Hồ Thị Thu Hằng</t>
@@ -191,7 +197,7 @@
     <t>MKT</t>
   </si>
   <si>
-    <t>3/7 gửi khách BOQ phần thô và NT</t>
+    <t>3/7 đã gửi khách BOQ phần thô và NT</t>
   </si>
   <si>
     <t>II</t>
@@ -200,14 +206,26 @@
     <t>Anh Thanh</t>
   </si>
   <si>
-    <t>Khách đang làm thiết kế bên khác, Đã gửi FF Ver1 ngày 1/7, dự kiến 3/7 gửi chào giá thi công</t>
+    <t>Khách đang làm thiết kế bên khác, Đã gửi FF Ver1 ngày 1/7
+Dự kiến 7/7 gửi báo giá</t>
   </si>
   <si>
     <t>anh Quyết</t>
   </si>
   <si>
-    <t>27/6 đã trao đổi liên hệ tư vấn với khách. khách đâng căn nhắc lại giá.
-1/7 gọi điện đề xuất cân đối giá, khách chưa nghe máy</t>
+    <t>3/7 gọi điện khách, khách đang hoàn thiện thô và yêu cầu chỉnh sửa lại 3D</t>
+  </si>
+  <si>
+    <t>Anh Phong</t>
+  </si>
+  <si>
+    <t>Đã khảo sát và khách ok làm thiết kế trước. Đang lên dự toán để khách nắm được giá thi công. Hẹn thứ 2 ký</t>
+  </si>
+  <si>
+    <t>Anh Thành</t>
+  </si>
+  <si>
+    <t>Khách thích sản phẩm của FF, sale đã dẫn khách đi tham quan công trình thực tế. Đang băn khoăn giá, sale đang hỗ trợ vì vượt ngân sách do thi công cả thô bị cao. Sale đang báo 520 triệu. Khách đang có 400 triệu. Đang đề xuất phương án thay đổi vật liệu</t>
   </si>
   <si>
     <t>Căn mẫu KS Hạ Long (Gói đồ rời)</t>
@@ -216,7 +234,7 @@
     <t>Partner</t>
   </si>
   <si>
-    <t>Đã gửi mail chào giá + điều khoản thương mại và tiến độ, chờ phản hồi</t>
+    <t>2/7 Đã gửi mail chào giá + điều khoản thương mại và tiến độ, chờ phản hồi</t>
   </si>
   <si>
     <t>HK GLOBAL</t>
@@ -225,13 +243,22 @@
     <t>Holding</t>
   </si>
   <si>
-    <t>25/06 Đã gửi lại thông tin gói đồ rời. Phía C Trang bên HK chưa trả lời.</t>
+    <t>25/06 Đã gửi lại thông tin gói đồ rời
+2/7 CĐT đã gửi lại HĐNT; 3/7 FF gửi lại, đợi phản hồi
+4/7 đang sửa lại báo giá và hẹn 6/7 gửi lại</t>
+  </si>
+  <si>
+    <t>Mr Trung</t>
   </si>
   <si>
     <t>Chị Huyền, Anh Trường</t>
   </si>
   <si>
-    <t>Đã gặp khách tối 26/6 trên VP FF cùng Thầu Thô để bảo vệ phương án BG. Khách có nhu cầu thiết kế lại toàn bộ trước khi thi công thô nên đang cân nhắc.</t>
+    <t>Tháng 8</t>
+  </si>
+  <si>
+    <t>Đã báo giá thô nhưng không phù hợp với ngân sách của khách
+Chiều 4/7 hẹn khách để trao đổi phần HĐTK (65tr) ký trước tháng này</t>
   </si>
   <si>
     <t>Chị Ngân</t>
@@ -249,7 +276,7 @@
     <t>WALK-IN</t>
   </si>
   <si>
-    <t>Đã gửi 3D ngày 26/6 khách comment chỉnh sửa màu sắc. Dự kiến tuần 2 tháng 7</t>
+    <t>04/07 đã chốt 3D, dự kiến sang tuần kí thi công</t>
   </si>
   <si>
     <t>Vũ Ánh Dương</t>
@@ -264,7 +291,7 @@
     <t>Chị Ngân - Trần Phú</t>
   </si>
   <si>
-    <t>Đã báo giá, chốt spec, chốt thiết kế. Mời khách qua văn phòng ký hợp đồng (dự kiến ngày 3/7 hoặc ngày 10/7, khách sẽ cố gắng sắp xếp công việc và báo lại)</t>
+    <t>Đã báo giá, chốt spec, chốt thiết kế. Mời khách qua văn phòng ký hợp đồng (dự kiến ngày 10/7, khách sẽ cố gắng sắp xếp công việc và báo lại)</t>
   </si>
   <si>
     <t>Anh Huy</t>
@@ -273,13 +300,13 @@
     <t>Đã lên thiết kế 3D, gửi báo giá khách. Khách chưa nhận nhà và đang ở quê có việc gia đình chưa liên hệ lại được, nên báo lại sau khi lên HN sẽ trao đổi</t>
   </si>
   <si>
-    <t>Đàm Mạnh Hải</t>
+    <t>Đàm Minh Hải</t>
   </si>
   <si>
     <t>Anh Tiến Anh</t>
   </si>
   <si>
-    <t>Đã tư vấn phương án thiết kế và ngân sách đầu tư, khách đang bàn bạc lại với gia đình, hẹn 2/7 trao đổi lại</t>
+    <t xml:space="preserve">Đã tư vấn phương án thiết kế và ngân sách đầu tư, khách đang bàn bạc lại với gia đình </t>
   </si>
   <si>
     <t>Chị Hồng</t>
@@ -288,44 +315,51 @@
     <t>Khách đang công tác ở SG nên chờ về HN để trao đổi</t>
   </si>
   <si>
+    <t>Anh Quân</t>
+  </si>
+  <si>
+    <t>Zalo</t>
+  </si>
+  <si>
+    <t>4/7 chốt layout 2D, dự kiến 15/07 kí HĐTC</t>
+  </si>
+  <si>
     <t>Anh Dũng Tuấn - B2B - Văn phòng hạng sang</t>
   </si>
   <si>
     <t>Đã gửi báo giá ngày 27/06. Đã gặp CĐT 29/06 sang trao đổi về Báo giá và Phương án Kĩ thuật + Spec cùng CĐT
-2/7 chốt spec, dự kiến giữa tháng tháng 7 ký HĐ</t>
+Đang điều chỉnh lại Spec</t>
   </si>
   <si>
     <t>Anh Khiêm</t>
   </si>
   <si>
-    <t>Doanh số dự kiến 1 tỉ. Đơn BTB 10 căn hộ cho thuê. Triển khai TK trước căn mẫu. Công trình đang trong giai đoạn thi công ngăn tường xây thô</t>
-  </si>
-  <si>
-    <t>Anh Thành</t>
+    <t>Doanh số dự kiến 1 tỉ. Đơn B2B 10 căn hộ cho thuê. Triển khai TK trước căn mẫu. Công trình đang trong giai đoạn thi công ngăn tường xây thô</t>
   </si>
   <si>
     <t>Giới thiệu</t>
   </si>
   <si>
-    <t>27/6 Nhận thông tin gói thầu đồ rời của dự án Lumi. Dự kiến 30/6 gửi lại BOQ và hẹn CĐT để trao đổi</t>
+    <t>27/6 Nhận thông tin gói thầu đồ rời của dự án Lumi. 30/6 đã gửi lại BOQ và hẹn CĐT để trao đổi
+3/7 khách phản hồi giá cao, đang tìm thêm thầu báo giá</t>
   </si>
   <si>
     <t>Anh Thức</t>
   </si>
   <si>
-    <t>Tháng 8</t>
+    <t>Tháng 10</t>
   </si>
   <si>
     <t>Đối tác</t>
   </si>
   <si>
-    <t>25/6 Đã gửi báo giá. CĐT đã ok báo giá dự kiến sau khi triển khai xong phần xây thô sẽ kí HĐTC</t>
+    <t>2/7 Đã gửi báo giá V2. CĐT đã ok báo giá, dự kiến sau khi khách triển khai xong phần xây thô sẽ kí HĐTC nội thất</t>
   </si>
   <si>
     <t>Anh Tuấn</t>
   </si>
   <si>
-    <t>Đang giai đoạn lên báo giá, dự kiến 6/7 gửi lại khách</t>
+    <t>Khách đã gửi báo giá 1 bên khác, dự kiến 8/7 sẽ gửi lại báo giá của FF cho khách</t>
   </si>
   <si>
     <t>KS Hải Phòng - Anh Phong</t>
@@ -334,30 +368,34 @@
     <t>Quý 4</t>
   </si>
   <si>
-    <t>Anh Phong TVTK Raymond Đà Nẵng. Gói thầu bao gồm 1 căn mẫu, hạng mục thô và thiết bị. Dự Kiến Quý 4 triển khai. Dự kiến 3/7 gửi lại báo giá sơ bộ để chào thầu. Khách hàng đang hợp tác với FF ở dự án Phú Quốc.</t>
+    <t>Anh Phong TVTK Raymond Đà Nẵng. Gói thầu bao gồm 1 căn mẫu, hạng mục thô và thiết bị. Dự Kiến Quý 4 triển khai. 
+02/07 đã gửi lại báo giá sơ bộ để chào thầu. Khách hàng đang hợp tác với FF ở dự án Phú Quốc.
+03/07 khách gửi lại Spec, đang cập nhật lại báo giá</t>
   </si>
   <si>
     <t>Chị Điệp - HGAA</t>
   </si>
   <si>
-    <t>25/6 Gửi báo giá Ver1 review cho HGAA. Chờ thông tin phản hồi. Dự kiến 29/6 check phản hồi thông tin</t>
+    <t>2/7 gửi lại báo giá V2, khách đang review</t>
   </si>
   <si>
     <t>III</t>
   </si>
   <si>
-    <t>Trường Ardyring Lào Cai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Văn Phòng Tuyển Sinh Trường - tại Hà Nội 
-Gửi báo giá 06/06/2026
-30/6 Lên làm việc với Chủ tịch </t>
-  </si>
-  <si>
-    <t>Các lớp học khối trung học 
-( đã gửi 3D, Báo giá cho CĐT ) 29/05
+    <t>Văn Phòng Tuyển Sinh Trường - tại Hà Nội  (Trường Ardyring Lào Cai)</t>
+  </si>
+  <si>
+    <t>Gửi báo giá 06/06/2026
+30/6 Lên làm việc với Chủ tịch =&gt; 2/7 đã gửi lại dự toán, CĐT đang review</t>
+  </si>
+  <si>
+    <t>Các lớp học khối trung học (Trường Ardyring Lào Cai)</t>
+  </si>
+  <si>
+    <t>Đã gửi 3D, Báo giá cho CĐT  29/05
 còn 3 phòng chức năng khác đang chạy 3D 15/06 trả CĐT
-Phòng DA trình chủ tịch phê duyệt )</t>
+Phòng DA trình chủ tịch phê duyệt )
+2/7 họp yêu cầu chạy lại 3D theo yêu cầu của cô chủ tịch để thi công gấp</t>
   </si>
   <si>
     <t xml:space="preserve">Căn mẫu Sunshine </t>
@@ -366,52 +404,18 @@
     <t>Làm việc qua Ms Huyền GRD</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">1/ Phụ lục hợp đồng 01: 1.260.000.000 vnđ :( Ký HĐ+ Ck tiền) từ GRD
-(GRD đã làm xong bảo lãnh với CĐT ) 
-chờ CĐT chuyển tiền &gt;&gt; thi công
-2/ Phụ lục hợp đồng 02: 1.000.000.000 vnđ : 12/06 đã gửi lại BOQ theo speck mới 
-CĐT đã chốt PA &amp; Speck vật liệu : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">12/06/2026
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t xml:space="preserve">Chờ CEO duyệt báo giá: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Times New Roman"/>
-      </rPr>
-      <t>17/06</t>
-    </r>
+    <t>+ Trúng thầu cả 2 phụ lục : tổng giá trị 2 Phụ lục là 2.4 tỷ ( MG &gt;25%)
++ Bên Tập đoàn Sunshine đã ký hợp đồng với GRD : phụ lục 1: từ ngày 21.05, và GRD đã làm bảo lãnh ngân hàng 01.06
+  nhưng đến hiện tại Sunshine vẫn chưa tạm ứng cho bên GRD ( cho dù Phòng mua &amp; Phòng thi công đã thông báo là trong tuần này vừa sẽ tạm ứng)
+&gt;&gt; 02.07: GRD thông báo hủy hợp đồng với Sunshine - vì sợ sau sẽ khó lấy tiền dc
++Sếp Trung sẽ trao đổi lại với chị Vân xem ntn, rồi quyết định</t>
   </si>
   <si>
     <t>Đoàn Thị Điểm</t>
   </si>
   <si>
-    <t xml:space="preserve">3D gửi CĐT : chốt ( 2 phòng : Thư viện, Tuyển sinh) 10.06
-3D phòng Hội trường gửi CDT 13/06
-Chờ CDT phê duyệt 3D: 15/06
-&gt;&gt; gửi phụ lục psinh : 17/06 </t>
+    <t>Gửi phụ lục psinh : 17/06 
+Dự kiến 6/7 ký</t>
   </si>
   <si>
     <t>HASCO-
@@ -421,10 +425,8 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>1/ lên khái toán Fitout &amp; MEP cho CĐT : 15/06 Trả bài
-2/ 2D bên CĐT đang thuê tk, họ sẽ gửi lại để check và hoàn thiện báo giá 
-&gt;&gt; Đàm phán thi công Fitout &amp;MEP trước để kịp tiến độ bàn giao
-3/ Fur : 26/6 họp CĐT, chỉnh sửa lại thiết kế một số khu vực</t>
+    <t>2/7 đã ký PL 1 2,4 tỷ trước VAT =&gt; đang thi công
+6/7 gửi PLPS 02 + 03</t>
   </si>
   <si>
     <t>Anh Tùng</t>
@@ -449,41 +451,18 @@
     </r>
   </si>
   <si>
-    <t>Anh Nghĩa S8 (Biệt thự Đà Nẵng)</t>
-  </si>
-  <si>
-    <t>Khách hàng đã gửi 3D,.2D : 22/05
-Gửi Dự toán cho CĐT : 19/06/206</t>
-  </si>
-  <si>
-    <t>Khách sạn chị Trang HP</t>
-  </si>
-  <si>
-    <t>Khách hàng đã gửi 3D : Khu sảnh lobby, lễ tân &amp; Nhà Hàng 
-Đã gửi Khái Toán : 28/05
-điều chỉnh lại dự toán cân đối theo mức CĐT đầu tư 600 tr
-17/06</t>
-  </si>
-  <si>
     <t>Hóa dầu Quảng Ninh</t>
   </si>
   <si>
-    <t>16/6 đi khảo sát, đang ra bản vẽ SOP và điều chỉnh lại báo giá gửi CĐT, bỏ hạng mục Thảm vì CĐT tự cung cấp</t>
-  </si>
-  <si>
-    <t>Anh Trường (Long Biên)</t>
-  </si>
-  <si>
-    <t>Facebook</t>
-  </si>
-  <si>
-    <t>đã gửi TK, chờ CĐT chốt, nếu khách hàng chốt sẽ chuyển BU1 Triển khai (CĐT đã đặt cọc tiền tk)</t>
+    <t>16/6 đi khảo sát, đang ra bản vẽ SOP và điều chỉnh lại báo giá gửi CĐT, bỏ hạng mục Thảm vì CĐT tự cung cấp
+5/7 gửi dự toán, dự kiến sang tuần ký</t>
   </si>
   <si>
     <t>Anh Vũ (Yên Hòa)</t>
   </si>
   <si>
-    <t>Đã khảo sát, đang chỉnh sửa lại thiết kế gửi khách</t>
+    <t>Đã khảo sát, đang chỉnh sửa lại thiết kế gửi khách
+Sang tuần sẽ pass lại cho BU4</t>
   </si>
   <si>
     <t>IV</t>
@@ -501,7 +480,8 @@
     <t>Booyoung - Campuchia</t>
   </si>
   <si>
-    <t>Đang triển khai Hợp đồng đặt hàng mẫu (lần 2) vs thầu mới</t>
+    <t>Đang triển khai Hợp đồng đặt hàng mẫu (lần 2) vs thầu mới
+03/07 CĐT qua E2 check hàng mẫu, dự kiến 7/7 chủ tịch Hàn Quốc bay sang check ver 2</t>
   </si>
   <si>
     <t>Nguyễn Kiều Vân</t>
@@ -517,13 +497,22 @@
 Đã chốt 3D, đang điều chỉnh HSKT.</t>
   </si>
   <si>
+    <t>Anh Dũng -Trung Văn</t>
+  </si>
+  <si>
+    <t>KH đã có 3D, cần triển khai thi công. Đang cân nhắc về điều khoản thanh toán.</t>
+  </si>
+  <si>
     <t>Anh Ngọc</t>
   </si>
   <si>
-    <t>11/07/2026</t>
-  </si>
-  <si>
-    <t>Đã chốt 3D, đang triển khai HSKT</t>
+    <t>02/7 đã gửi báo giá cho khách, khách bổ sung thêm một số hạng mục =&gt; đang điều chỉnh lại báo giá, sang tuần gửi lại khách</t>
+  </si>
+  <si>
+    <t>Anh Minh</t>
+  </si>
+  <si>
+    <t>Khách yêu cầu đổi cốt rẻ hơn, đã gửi báo giá ngày 2/7, đợi khách phản hồi</t>
   </si>
   <si>
     <t>HDB Thanh Trì</t>
@@ -543,7 +532,7 @@
   </si>
   <si>
     <t>20/06 đang làm việc lại về tiến độ phần thô. 
-30/6 sang gặp CĐT để trao đổi về tiến độ tiếp theo</t>
+30/6 sang gặp CĐT =&gt; chỉnh sửa lại phần kiến trức căn mẫu, dự kiến giữa tháng 7 duyệt</t>
   </si>
   <si>
     <t>Anh Quân - Hà Nam</t>
@@ -552,25 +541,25 @@
     <t>22/07/2026</t>
   </si>
   <si>
-    <t>Đã ký HDTK, đang điều chỉnh layout cải tạo.</t>
+    <t>Đã chốt 3D, đang đợi ván nên lùi lịch ký PL Thi công</t>
   </si>
   <si>
     <t>Nội thất 328 căn Chung cư Ecopark Sông Lam</t>
   </si>
   <si>
-    <t>29/05/2026 vào gặp chủ đầu tư với sếp Trung và sếp Thuân</t>
+    <t>29/05/2026 vào gặp chủ đầu tư với sếp Trung và sếp Thuân. Đang tạm pouse</t>
   </si>
   <si>
     <t>Trường tiểu học Liên Hồng</t>
   </si>
   <si>
-    <t>Hai bên đang thỏa thuận lại điều khoản thanh toán hợp đồng (đợt kế toán chốt điều khoản).</t>
+    <t>Hai bên đang thỏa thuận lại điều khoản thanh toán hợp đồng (đợi kế toán chốt điều khoản).</t>
   </si>
   <si>
     <t>Bệnh viện Thạch Thất</t>
   </si>
   <si>
-    <t>Triển khai trước phần ép cọc.</t>
+    <t>CĐT gửi báo giá thi công, FF đang check với thầu xem vào được ko</t>
   </si>
   <si>
     <t>TỔNG</t>
@@ -666,7 +655,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -820,11 +809,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -995,9 +1004,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1028,9 +1034,6 @@
     <xf numFmtId="9" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1065,6 +1068,57 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2546,7 +2600,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B3:D14" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="13">
     <pivotField compact="0" showAll="0"/>
@@ -2765,8 +2819,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A3:M52" xr:uid="{00000000-0009-0000-0100-000005000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M54" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A3:M54" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="9">
       <filters>
         <filter val="Facebook"/>
@@ -3211,7 +3265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O58"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.125" style="21" customWidth="1"/>
@@ -3220,7 +3274,7 @@
     <col min="4" max="4" width="35.625" style="21" customWidth="1"/>
     <col min="5" max="5" width="24.875" style="21" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="22.75" style="21" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="60" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="59" customWidth="1"/>
     <col min="8" max="8" width="15.875" style="22" customWidth="1"/>
     <col min="9" max="9" width="23.375" style="21" customWidth="1"/>
     <col min="10" max="10" width="23" style="22" customWidth="1"/>
@@ -3231,21 +3285,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
     </row>
     <row r="2" spans="1:15" ht="8.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G2" s="44"/>
@@ -3304,8 +3358,8 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="8">
-        <f>+SUBTOTAL(9,F5:F7)</f>
-        <v>2700000000</v>
+        <f>+SUBTOTAL(9,F5:F8)</f>
+        <v>3800000000</v>
       </c>
       <c r="G4" s="46"/>
       <c r="H4" s="6"/>
@@ -3352,7 +3406,9 @@
       <c r="L5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="35"/>
+      <c r="M5" s="35" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -3365,7 +3421,7 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
@@ -3375,10 +3431,10 @@
         <v>0.2</v>
       </c>
       <c r="H6" s="39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>34</v>
@@ -3387,9 +3443,11 @@
         <v>0.7</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="M6" s="35"/>
+        <v>40</v>
+      </c>
+      <c r="M6" s="35" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="7" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
@@ -3402,20 +3460,20 @@
         <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>200000000</v>
+        <v>800000000</v>
       </c>
       <c r="G7" s="12">
         <v>0.19</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>34</v>
@@ -3424,9 +3482,11 @@
         <v>0.7</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="35"/>
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
     </row>
@@ -3438,10 +3498,10 @@
         <v>28</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="2">
@@ -3451,27 +3511,29 @@
         <v>0.19</v>
       </c>
       <c r="H8" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K8" s="12">
         <v>0.6</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="M8" s="35"/>
+        <v>48</v>
+      </c>
+      <c r="M8" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N8" s="26"/>
       <c r="O8" s="26"/>
     </row>
     <row r="9" spans="1:15" s="25" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>6</v>
@@ -3480,8 +3542,8 @@
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="8">
-        <f>+SUBTOTAL(9,F10:F28)</f>
-        <v>27693000000</v>
+        <f>+SUBTOTAL(9,F10:F31)</f>
+        <v>26813000000</v>
       </c>
       <c r="G9" s="46"/>
       <c r="H9" s="40"/>
@@ -3502,7 +3564,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="2">
@@ -3512,21 +3574,23 @@
         <v>0.3</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K10" s="12">
         <v>0.6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="M10" s="35"/>
+        <v>51</v>
+      </c>
+      <c r="M10" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N10" s="24"/>
     </row>
     <row r="11" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -3540,7 +3604,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="2">
@@ -3550,92 +3614,98 @@
         <v>0.25</v>
       </c>
       <c r="H11" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K11" s="12">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M11" s="35"/>
+        <v>53</v>
+      </c>
+      <c r="M11" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N11" s="24"/>
     </row>
-    <row r="12" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="56">
-        <v>4</v>
+    <row r="12" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>54</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1000000000</v>
+      </c>
       <c r="F12" s="2">
-        <v>900000000</v>
+        <v>120000000</v>
       </c>
       <c r="G12" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H12" s="39" t="s">
-        <v>37</v>
+        <v>0.3</v>
+      </c>
+      <c r="H12" s="39">
+        <v>46209</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="K12" s="12">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M12" s="35"/>
       <c r="N12" s="24"/>
     </row>
-    <row r="13" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="56">
-        <v>5</v>
+    <row r="13" spans="1:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>3</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>56</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1000000000</v>
+      </c>
       <c r="F13" s="2">
-        <v>8000000000</v>
+        <v>400000000</v>
       </c>
       <c r="G13" s="12">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="K13" s="12">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>57</v>
@@ -3643,9 +3713,9 @@
       <c r="M13" s="35"/>
       <c r="N13" s="24"/>
     </row>
-    <row r="14" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10">
-        <v>6</v>
+    <row r="14" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="56">
+        <v>4</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>6</v>
@@ -3653,423 +3723,437 @@
       <c r="C14" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="2">
-        <v>2500000000</v>
+        <v>900000000</v>
       </c>
       <c r="G14" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K14" s="12">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M14" s="35"/>
+        <v>60</v>
+      </c>
+      <c r="M14" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N14" s="24"/>
     </row>
-    <row r="15" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10">
-        <v>7</v>
+    <row r="15" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="56">
+        <v>5</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2">
-        <v>500000000</v>
+        <v>8000000000</v>
       </c>
       <c r="G15" s="12">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="K15" s="12">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M15" s="35"/>
+        <v>63</v>
+      </c>
+      <c r="M15" s="35" t="s">
+        <v>64</v>
+      </c>
       <c r="N15" s="24"/>
     </row>
-    <row r="16" spans="1:15" s="72" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="73">
+    <row r="16" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="66" t="s">
-        <v>63</v>
+      <c r="D16" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="67">
-        <v>500000000</v>
-      </c>
-      <c r="G16" s="68">
-        <v>0.2</v>
-      </c>
-      <c r="H16" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="I16" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="J16" s="64" t="s">
-        <v>64</v>
-      </c>
-      <c r="K16" s="68">
-        <v>0.7</v>
-      </c>
-      <c r="L16" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="71"/>
-    </row>
-    <row r="17" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F16" s="2">
+        <v>600000000</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.18</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="K16" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" s="24"/>
+    </row>
+    <row r="17" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2">
-        <v>150000000</v>
+        <v>500000000</v>
       </c>
       <c r="G17" s="12">
         <v>0.2</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K17" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M17" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" s="24"/>
+    </row>
+    <row r="18" spans="1:14" s="70" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="71">
+        <v>8</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="72" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="66">
+        <v>500000000</v>
+      </c>
+      <c r="G18" s="67">
+        <v>0.2</v>
+      </c>
+      <c r="H18" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="63" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="67">
+        <v>0.7</v>
+      </c>
+      <c r="L18" s="65" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="N18" s="69"/>
+    </row>
+    <row r="19" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" s="12">
         <v>0.6</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M17" s="35"/>
-      <c r="N17" s="24"/>
-    </row>
-    <row r="18" spans="1:15" s="72" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="63">
-        <f>A17+1</f>
+      <c r="L19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M19" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" s="24"/>
+    </row>
+    <row r="20" spans="1:14" s="70" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="62">
+        <f>A19+1</f>
         <v>11</v>
       </c>
-      <c r="B18" s="64" t="str">
-        <f>B17</f>
+      <c r="B20" s="63" t="str">
+        <f>B19</f>
         <v>BU 1</v>
       </c>
-      <c r="C18" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="67">
+      <c r="C20" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="66">
         <v>85000000</v>
       </c>
-      <c r="G18" s="68">
+      <c r="G20" s="67">
         <v>0.2</v>
       </c>
-      <c r="H18" s="69" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="K18" s="68">
+      <c r="H20" s="63" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="J20" s="63" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="67">
         <v>0.9</v>
       </c>
-      <c r="L18" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="M18" s="70"/>
-      <c r="N18" s="71"/>
-    </row>
-    <row r="19" spans="1:15" s="26" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="56">
+      <c r="L20" s="65" t="s">
+        <v>78</v>
+      </c>
+      <c r="M20" s="68"/>
+      <c r="N20" s="69"/>
+    </row>
+    <row r="21" spans="1:14" s="26" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="56">
         <v>12</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B21" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="77">
+      <c r="C21" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="75">
         <v>200000000</v>
       </c>
-      <c r="G19" s="78">
+      <c r="G21" s="76">
         <v>0.2</v>
       </c>
-      <c r="H19" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="53" t="s">
+      <c r="H21" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="J19" s="53" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="78">
+      <c r="J21" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="K21" s="76">
         <v>0.7</v>
       </c>
-      <c r="L19" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="81"/>
-    </row>
-    <row r="20" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10">
+      <c r="L21" s="74" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="79"/>
+    </row>
+    <row r="22" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10">
         <v>13</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="2">
-        <v>300000000</v>
-      </c>
-      <c r="G20" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K20" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="M20" s="35"/>
-      <c r="N20" s="24"/>
-    </row>
-    <row r="21" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10">
-        <v>14</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="2">
-        <v>400000000</v>
-      </c>
-      <c r="G21" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K21" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M21" s="35"/>
-      <c r="N21" s="24"/>
-    </row>
-    <row r="22" spans="1:15" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
-        <v>15</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="2">
-        <v>7000000000</v>
+        <v>300000000</v>
       </c>
       <c r="G22" s="12">
         <v>0.2</v>
       </c>
       <c r="H22" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K22" s="12">
         <v>0.6</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M22" s="35"/>
+        <v>83</v>
+      </c>
+      <c r="M22" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N22" s="24"/>
     </row>
-    <row r="23" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="2">
+        <v>84</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" s="2">
         <v>400000000</v>
-      </c>
-      <c r="F23" s="2">
-        <v>8000000</v>
       </c>
       <c r="G23" s="12">
         <v>0.2</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K23" s="12">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M23" s="35"/>
+        <v>85</v>
+      </c>
+      <c r="M23" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N23" s="24"/>
     </row>
-    <row r="24" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="2">
-        <v>400000000</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="E24" s="1"/>
       <c r="F24" s="2">
-        <v>1000000000</v>
+        <v>500000000</v>
       </c>
       <c r="G24" s="12">
         <v>0.2</v>
       </c>
       <c r="H24" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K24" s="12">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="M24" s="35"/>
       <c r="N24" s="24"/>
     </row>
-    <row r="25" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>6</v>
@@ -4078,38 +4162,38 @@
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="2">
-        <v>250000000</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="E25" s="1"/>
       <c r="F25" s="2">
-        <v>250000000</v>
+        <v>7000000000</v>
       </c>
       <c r="G25" s="12">
         <v>0.2</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>86</v>
+      <c r="H25" s="39" t="s">
+        <v>46</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K25" s="12">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="M25" s="35"/>
+        <v>90</v>
+      </c>
+      <c r="M25" s="35" t="s">
+        <v>64</v>
+      </c>
       <c r="N25" s="24"/>
     </row>
-    <row r="26" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>6</v>
@@ -4118,38 +4202,40 @@
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2">
         <v>400000000</v>
       </c>
       <c r="F26" s="2">
-        <v>900000000</v>
+        <v>8000000</v>
       </c>
       <c r="G26" s="12">
         <v>0.2</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M26" s="35"/>
+        <v>92</v>
+      </c>
+      <c r="M26" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N26" s="24"/>
     </row>
-    <row r="27" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>6</v>
@@ -4158,38 +4244,40 @@
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="E27" s="2">
         <v>400000000</v>
       </c>
       <c r="F27" s="2">
-        <v>3000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G27" s="12">
         <v>0.2</v>
       </c>
       <c r="H27" s="39" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K27" s="12">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M27" s="35"/>
+        <v>94</v>
+      </c>
+      <c r="M27" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N27" s="24"/>
     </row>
-    <row r="28" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
@@ -4198,257 +4286,266 @@
         <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E28" s="2">
-        <v>400000000</v>
+        <v>250000000</v>
       </c>
       <c r="F28" s="2">
-        <v>500000000</v>
+        <v>250000000</v>
       </c>
       <c r="G28" s="12">
         <v>0.2</v>
       </c>
-      <c r="H28" s="39" t="s">
-        <v>92</v>
+      <c r="H28" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K28" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M28" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="24"/>
+    </row>
+    <row r="29" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>18</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E29" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F29" s="2">
+        <v>900000000</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H29" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K29" s="12">
         <v>0.6</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="M28" s="35"/>
-      <c r="N28" s="24"/>
-    </row>
-    <row r="29" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="L29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M29" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="N29" s="24"/>
+    </row>
+    <row r="30" spans="1:14" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>19</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F30" s="2">
+        <v>3000000000</v>
+      </c>
+      <c r="G30" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H30" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K30" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M30" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N30" s="24"/>
+    </row>
+    <row r="31" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="81">
+        <v>20</v>
+      </c>
+      <c r="B31" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F31" s="83">
+        <v>500000000</v>
+      </c>
+      <c r="G31" s="84">
+        <v>0.2</v>
+      </c>
+      <c r="H31" s="85" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="J31" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="K31" s="84">
+        <v>0.6</v>
+      </c>
+      <c r="L31" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="M31" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="N31" s="24"/>
+    </row>
+    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8">
-        <f>+SUBTOTAL(9,F30:F40)</f>
-        <v>20666000000</v>
-      </c>
-      <c r="G29" s="46"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="34"/>
-    </row>
-    <row r="30" spans="1:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="3">
+      <c r="C32" s="50"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="8">
+        <f>+SUBTOTAL(9,F33:F40)</f>
+        <v>21800000000</v>
+      </c>
+      <c r="G32" s="46"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="34"/>
+    </row>
+    <row r="33" spans="1:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="87">
         <v>1</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B33" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C33" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="2">
-        <v>3800000000</v>
-      </c>
-      <c r="G30" s="12">
+      <c r="D33" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="89">
+        <v>3900000000</v>
+      </c>
+      <c r="G33" s="90">
         <v>0.25</v>
       </c>
-      <c r="H30" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="I30" s="58" t="s">
+      <c r="H33" s="91" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K30" s="12">
+      <c r="J33" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="K33" s="90">
         <v>0.7</v>
       </c>
-      <c r="L30" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="M30" s="35"/>
-      <c r="N30" s="26"/>
-      <c r="O30" s="26"/>
-    </row>
-    <row r="31" spans="1:15" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>2</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="2">
-        <v>1200000000</v>
-      </c>
-      <c r="G31" s="55">
-        <v>0.25</v>
-      </c>
-      <c r="H31" s="54" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K31" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L31" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="26"/>
-      <c r="O31" s="26"/>
-    </row>
-    <row r="32" spans="1:15" ht="107.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>3</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="2">
-        <v>2400000000</v>
-      </c>
-      <c r="G32" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K32" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L32" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="M32" s="35"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-    </row>
-    <row r="33" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>4</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="2">
-        <v>816000000</v>
-      </c>
-      <c r="G33" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I33" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="L33" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="M33" s="35"/>
+      <c r="L33" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="M33" s="94"/>
       <c r="N33" s="26"/>
       <c r="O33" s="26"/>
     </row>
-    <row r="34" spans="1:15" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>105</v>
+      <c r="D34" s="41" t="s">
+        <v>109</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="2">
-        <v>2800000000</v>
-      </c>
-      <c r="G34" s="12">
+        <v>3500000000</v>
+      </c>
+      <c r="G34" s="55">
         <v>0.25</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I34" s="52" t="s">
+      <c r="H34" s="54" t="s">
+        <v>46</v>
+      </c>
+      <c r="I34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="K34" s="12">
         <v>0.7</v>
       </c>
-      <c r="L34" s="41" t="s">
-        <v>107</v>
+      <c r="L34" s="96" t="s">
+        <v>110</v>
       </c>
       <c r="M34" s="35"/>
       <c r="N34" s="26"/>
       <c r="O34" s="26"/>
     </row>
-    <row r="35" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" ht="131.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>11</v>
@@ -4457,37 +4554,39 @@
         <v>12</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="1"/>
+        <v>111</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="F35" s="2">
-        <v>2900000000</v>
+        <v>2400000000</v>
       </c>
       <c r="G35" s="12">
         <v>0.25</v>
       </c>
-      <c r="H35" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="I35" s="53" t="s">
+      <c r="H35" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="18" t="s">
         <v>33</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="K35" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>109</v>
+        <v>0.7</v>
+      </c>
+      <c r="L35" s="41" t="s">
+        <v>113</v>
       </c>
       <c r="M35" s="35"/>
       <c r="N35" s="26"/>
       <c r="O35" s="26"/>
     </row>
-    <row r="36" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>11</v>
@@ -4496,76 +4595,76 @@
         <v>12</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="2">
-        <v>500000000</v>
+        <v>1300000000</v>
       </c>
       <c r="G36" s="12">
         <v>0.25</v>
       </c>
-      <c r="H36" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>33</v>
+      <c r="H36" s="95">
+        <v>46209</v>
+      </c>
+      <c r="I36" s="53" t="s">
+        <v>39</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="K36" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>111</v>
+        <v>0.9</v>
+      </c>
+      <c r="L36" s="41" t="s">
+        <v>115</v>
       </c>
       <c r="M36" s="35"/>
       <c r="N36" s="26"/>
       <c r="O36" s="26"/>
     </row>
-    <row r="37" spans="1:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="51" t="s">
         <v>12</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="2">
-        <v>800000000</v>
+        <v>2600000000</v>
       </c>
       <c r="G37" s="12">
         <v>0.25</v>
       </c>
-      <c r="H37" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I37" s="53" t="s">
+      <c r="H37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I37" s="52" t="s">
         <v>33</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>34</v>
+        <v>117</v>
       </c>
       <c r="K37" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>113</v>
+        <v>0.7</v>
+      </c>
+      <c r="L37" s="41" t="s">
+        <v>118</v>
       </c>
       <c r="M37" s="35"/>
       <c r="N37" s="26"/>
       <c r="O37" s="26"/>
     </row>
-    <row r="38" spans="1:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>11</v>
@@ -4574,35 +4673,37 @@
         <v>12</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="2">
-        <v>5000000000</v>
+        <v>2900000000</v>
       </c>
       <c r="G38" s="12">
         <v>0.25</v>
       </c>
       <c r="H38" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I38" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I38" s="53" t="s">
         <v>33</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>56</v>
+        <v>117</v>
       </c>
       <c r="K38" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="L38" s="49" t="s">
-        <v>115</v>
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="M38" s="35"/>
-    </row>
-    <row r="39" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+    </row>
+    <row r="39" spans="1:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>11</v>
@@ -4611,29 +4712,29 @@
         <v>12</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="2">
-        <v>250000000</v>
+        <v>5000000000</v>
       </c>
       <c r="G39" s="12">
         <v>0.25</v>
       </c>
       <c r="H39" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="I39" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="K39" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>118</v>
+        <v>0.9</v>
+      </c>
+      <c r="L39" s="49" t="s">
+        <v>122</v>
       </c>
       <c r="M39" s="35"/>
     </row>
@@ -4648,7 +4749,7 @@
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="2">
@@ -4658,7 +4759,7 @@
         <v>0.2</v>
       </c>
       <c r="H40" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I40" s="52" t="s">
         <v>33</v>
@@ -4670,13 +4771,13 @@
         <v>0.5</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M40" s="35"/>
     </row>
     <row r="41" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>3</v>
@@ -4685,8 +4786,8 @@
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="8">
-        <f>+SUBTOTAL(9,F42:F51)</f>
-        <v>241085000000</v>
+        <f>+SUBTOTAL(9,F42:F53)</f>
+        <v>222325000000</v>
       </c>
       <c r="G41" s="46"/>
       <c r="H41" s="6"/>
@@ -4707,7 +4808,7 @@
         <v>4</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="2">
@@ -4717,25 +4818,25 @@
         <v>0.2</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K42" s="12">
         <v>0.7</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M42" s="35"/>
     </row>
-    <row r="43" spans="1:15" s="26" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" s="26" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
-        <f t="shared" ref="A43:A51" si="0">A42+1</f>
+        <f>A42+1</f>
         <v>2</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -4745,7 +4846,7 @@
         <v>4</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="2">
@@ -4755,35 +4856,35 @@
         <v>0.18</v>
       </c>
       <c r="H43" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K43" s="12">
         <v>0.8</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="M43" s="35"/>
     </row>
     <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
-        <f t="shared" si="0"/>
+        <f>A43+1</f>
         <v>3</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="51" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="E44" s="42"/>
       <c r="F44" s="2">
@@ -4793,178 +4894,175 @@
         <v>0.23</v>
       </c>
       <c r="H44" s="43" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K44" s="12">
         <v>0.85</v>
       </c>
       <c r="L44" s="41" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M44" s="35"/>
     </row>
-    <row r="45" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
-        <f t="shared" si="0"/>
+        <f>A44+1</f>
         <v>4</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="51" t="s">
-        <v>5</v>
+        <v>131</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E45" s="42"/>
       <c r="F45" s="2">
-        <v>110000000</v>
+        <v>1100000000</v>
       </c>
       <c r="G45" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H45" s="43" t="s">
-        <v>132</v>
+        <v>0.23</v>
+      </c>
+      <c r="H45" s="43">
+        <v>46213</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K45" s="12">
         <v>0.7</v>
       </c>
       <c r="L45" s="41" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M45" s="35"/>
     </row>
     <row r="46" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A46" si="0">A45+1</f>
         <v>5</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E46" s="42"/>
       <c r="F46" s="2">
-        <v>60000000000</v>
+        <v>110000000</v>
       </c>
       <c r="G46" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="H46" s="39" t="s">
-        <v>86</v>
+        <v>0.2</v>
+      </c>
+      <c r="H46" s="43">
+        <v>46213</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="K46" s="12">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L46" s="41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M46" s="35"/>
     </row>
-    <row r="47" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
+    <row r="47" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="3"/>
       <c r="B47" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E47" s="42"/>
       <c r="F47" s="2">
-        <v>60000000000</v>
+        <v>140000000</v>
       </c>
       <c r="G47" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>137</v>
+        <v>0.2</v>
+      </c>
+      <c r="H47" s="43" t="s">
+        <v>66</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="K47" s="12">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M47" s="35"/>
     </row>
-    <row r="48" spans="1:15" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f>A46+1</f>
+        <v>6</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>127</v>
+        <v>4</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E48" s="42"/>
       <c r="F48" s="2">
-        <v>800000000</v>
+        <v>60000000000</v>
       </c>
       <c r="G48" s="12">
-        <v>0.23</v>
-      </c>
-      <c r="H48" s="43" t="s">
-        <v>141</v>
+        <v>0.08</v>
+      </c>
+      <c r="H48" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="K48" s="12">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="L48" s="41" t="s">
         <v>142</v>
       </c>
       <c r="M48" s="35"/>
     </row>
-    <row r="49" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <f>A48+1</f>
+        <v>7</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>3</v>
@@ -4977,70 +5075,70 @@
       </c>
       <c r="E49" s="42"/>
       <c r="F49" s="2">
-        <v>80000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="G49" s="12">
         <v>0.15</v>
       </c>
       <c r="H49" s="39" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="K49" s="12">
         <v>0.8</v>
       </c>
       <c r="L49" s="41" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M49" s="35"/>
     </row>
-    <row r="50" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <f>A49+1</f>
+        <v>8</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E50" s="42"/>
-      <c r="F50" s="47">
-        <v>4000000000</v>
+      <c r="F50" s="2">
+        <v>800000000</v>
       </c>
       <c r="G50" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="H50" s="39" t="s">
-        <v>37</v>
+        <v>0.23</v>
+      </c>
+      <c r="H50" s="43" t="s">
+        <v>148</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K50" s="12">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L50" s="41" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M50" s="35"/>
     </row>
-    <row r="51" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f>A50+1</f>
+        <v>9</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>3</v>
@@ -5049,59 +5147,135 @@
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E51" s="42"/>
       <c r="F51" s="2">
-        <v>6000000000</v>
+        <v>60000000000</v>
       </c>
       <c r="G51" s="12">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H51" s="39" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="K51" s="12">
         <v>0.8</v>
       </c>
       <c r="L51" s="41" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M51" s="35"/>
     </row>
-    <row r="52" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="28"/>
-      <c r="B52" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="C52" s="30"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="32">
-        <f>SUBTOTAL(9,F4:F51)</f>
-        <v>292644000000</v>
-      </c>
-      <c r="G52" s="59"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="61"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="31"/>
-      <c r="M52" s="36"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F53" s="24"/>
-      <c r="H53" s="62"/>
-    </row>
-    <row r="54" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <f>A51+1</f>
+        <v>10</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" s="42"/>
+      <c r="F52" s="47">
+        <v>4000000000</v>
+      </c>
+      <c r="G52" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H52" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K52" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L52" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="M52" s="35"/>
+    </row>
+    <row r="53" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3">
+        <f>A52+1</f>
+        <v>11</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E53" s="42"/>
+      <c r="F53" s="2">
+        <v>6000000000</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H53" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="K53" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L53" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="M53" s="35"/>
+    </row>
+    <row r="54" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" s="30"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="32">
+        <f>SUBTOTAL(9,F4:F53)</f>
+        <v>274738000000</v>
+      </c>
+      <c r="G54" s="58"/>
+      <c r="H54" s="60"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="60"/>
+      <c r="K54" s="33"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="36"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="F55" s="24"/>
+      <c r="H55" s="61"/>
+    </row>
+    <row r="56" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>

--- a/uploads/curr.xlsx
+++ b/uploads/curr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://flexfitcom-my.sharepoint.com/personal/mont_flexfit_vn/Documents/MONT/Báo cáo doanh số/Báo cáo tiềm năng/Dữ liệu báo cáo tiềm năng/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FF-PC06\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{8A8335D2-215C-4E66-90FA-87646CF4424E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33394C9E-0A74-4CB6-B0BB-D2C47DE04C59}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47812530-ADCF-4A1D-8B7D-A9F356A5003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="6" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191028" calcOnSave="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="17" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -42,6 +42,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -49,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="161">
   <si>
     <t>Phòng ban</t>
   </si>
@@ -182,13 +184,16 @@
     <t>VP KNI</t>
   </si>
   <si>
+    <t>Tuần 3 tháng 7</t>
+  </si>
+  <si>
     <t>Đã gửi báo giá cho CĐT đang chờ CĐT phê duyệt</t>
   </si>
   <si>
-    <t>Hồ Thị Thu Hằng</t>
-  </si>
-  <si>
-    <t>Chị Quyên Phú Mỹ Hưng</t>
+    <t>II</t>
+  </si>
+  <si>
+    <t>Anh Thanh</t>
   </si>
   <si>
     <t>Tháng 7</t>
@@ -197,29 +202,23 @@
     <t>MKT</t>
   </si>
   <si>
-    <t>3/7 đã gửi khách BOQ phần thô và NT</t>
-  </si>
-  <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>Anh Thanh</t>
-  </si>
-  <si>
     <t>Khách đang làm thiết kế bên khác, Đã gửi FF Ver1 ngày 1/7
-Dự kiến 7/7 gửi báo giá</t>
+Dự kiến 09/7 gửi báo giá</t>
   </si>
   <si>
     <t>anh Quyết</t>
   </si>
   <si>
-    <t>3/7 gọi điện khách, khách đang hoàn thiện thô và yêu cầu chỉnh sửa lại 3D</t>
+    <t>Tháng 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/7 gọi điện khách, khách đang hoàn thiện thô và yêu cầu chỉnh sửa lại 3D phòng khách </t>
   </si>
   <si>
     <t>Anh Phong</t>
   </si>
   <si>
-    <t>Đã khảo sát và khách ok làm thiết kế trước. Đang lên dự toán để khách nắm được giá thi công. Hẹn thứ 2 ký</t>
+    <t>06/07 Đã ký HĐTK, đang triển khai thiết kế</t>
   </si>
   <si>
     <t>Anh Thành</t>
@@ -254,9 +253,6 @@
     <t>Chị Huyền, Anh Trường</t>
   </si>
   <si>
-    <t>Tháng 8</t>
-  </si>
-  <si>
     <t>Đã báo giá thô nhưng không phù hợp với ngân sách của khách
 Chiều 4/7 hẹn khách để trao đổi phần HĐTK (65tr) ký trước tháng này</t>
   </si>
@@ -267,6 +263,36 @@
     <t>Khách đang chọn đơn vị thiết kế khác, FF chào giá thi công dự kiến cuối tháng 7</t>
   </si>
   <si>
+    <t>Quách Tuấn Anh</t>
+  </si>
+  <si>
+    <t>Khách kí thiết kế 2 phòng ngủ dự kiến chuyển đổi thi công trong tháng 7</t>
+  </si>
+  <si>
+    <t>Chị Thương Anh Thụy</t>
+  </si>
+  <si>
+    <t>Khách đã kí thiết kế, trình 3D ver 3 vào 3/7 để chốt chuyển đổi sang thi công</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Vững</t>
+  </si>
+  <si>
+    <t>Đã tư vấn báo giá về thiết kế và khách hẹn nhận nhà qua khảo sát ký hợp đồng</t>
+  </si>
+  <si>
+    <t>Hà Thị Kim Cúc</t>
+  </si>
+  <si>
+    <t>Đã gửi báo giá cho khách PA 1 vào ngày 1/7, KH đã hoàn thiện xong phần thô đang lựa chọn đơn vị nt</t>
+  </si>
+  <si>
+    <t>Giang Lê Thắng</t>
+  </si>
+  <si>
+    <t>Đã đi khảo sát cho KH ngày 19/6 và báo giá sơ bộ - khách đang mổ tay nên chưa phản hồi chốt về HĐTK. 3/7 Đã liên hệ khách nhưng khách vẫn đang nhập viện mổ</t>
+  </si>
+  <si>
     <t>Nguyễn Ngọc Thanh</t>
   </si>
   <si>
@@ -312,7 +338,7 @@
     <t>Chị Hồng</t>
   </si>
   <si>
-    <t>Khách đang công tác ở SG nên chờ về HN để trao đổi</t>
+    <t>Khách đang công tác ở SG nên chờ về HN để trao đổi. Khách đang lăn tăn về chỗ ở trong thời gian thi công</t>
   </si>
   <si>
     <t>Anh Quân</t>
@@ -382,20 +408,13 @@
     <t>III</t>
   </si>
   <si>
-    <t>Văn Phòng Tuyển Sinh Trường - tại Hà Nội  (Trường Ardyring Lào Cai)</t>
-  </si>
-  <si>
-    <t>Gửi báo giá 06/06/2026
-30/6 Lên làm việc với Chủ tịch =&gt; 2/7 đã gửi lại dự toán, CĐT đang review</t>
-  </si>
-  <si>
     <t>Các lớp học khối trung học (Trường Ardyring Lào Cai)</t>
   </si>
   <si>
     <t>Đã gửi 3D, Báo giá cho CĐT  29/05
 còn 3 phòng chức năng khác đang chạy 3D 15/06 trả CĐT
-Phòng DA trình chủ tịch phê duyệt )
-2/7 họp yêu cầu chạy lại 3D theo yêu cầu của cô chủ tịch để thi công gấp</t>
+Phòng DA trình chủ tịch phê duyệt)
+7/7 đã gửi 3D V2 của CĐT sau khi họp ngày 2/7</t>
   </si>
   <si>
     <t xml:space="preserve">Căn mẫu Sunshine </t>
@@ -411,22 +430,19 @@
 +Sếp Trung sẽ trao đổi lại với chị Vân xem ntn, rồi quyết định</t>
   </si>
   <si>
-    <t>Đoàn Thị Điểm</t>
-  </si>
-  <si>
-    <t>Gửi phụ lục psinh : 17/06 
-Dự kiến 6/7 ký</t>
-  </si>
-  <si>
-    <t>HASCO-
- Deawoo Kim mã</t>
+    <t>Đoàn Thị Điểm Phòng - Mỹ Đình</t>
+  </si>
+  <si>
+    <t>Nội thất phòng tiếp đón phụ huynh và bục sân khấu ngoài trời</t>
+  </si>
+  <si>
+    <t>Văn Phòng HASCO - DEAHAN 360 Kim Mã - PL02 + PL03</t>
   </si>
   <si>
     <t>Reference</t>
   </si>
   <si>
-    <t>2/7 đã ký PL 1 2,4 tỷ trước VAT =&gt; đang thi công
-6/7 gửi PLPS 02 + 03</t>
+    <t>Phòng cháy, nội thất đồ rời, Fitout, MEP</t>
   </si>
   <si>
     <t>Anh Tùng</t>
@@ -455,14 +471,19 @@
   </si>
   <si>
     <t>16/6 đi khảo sát, đang ra bản vẽ SOP và điều chỉnh lại báo giá gửi CĐT, bỏ hạng mục Thảm vì CĐT tự cung cấp
-5/7 gửi dự toán, dự kiến sang tuần ký</t>
+5/7 gửi dự toán, CĐT đang review Spec vật liệu, dự kiến sang tuần ký</t>
+  </si>
+  <si>
+    <t>Văn Phòng Tòa nhà số 10 Trần Hưng Đạo</t>
+  </si>
+  <si>
+    <t>08/07 Đã gửi khái toán cho CĐT, đợi mở thầu</t>
   </si>
   <si>
     <t>Anh Vũ (Yên Hòa)</t>
   </si>
   <si>
-    <t>Đã khảo sát, đang chỉnh sửa lại thiết kế gửi khách
-Sang tuần sẽ pass lại cho BU4</t>
+    <t>Đã khảo sát, đang chỉnh sửa lại thiết kế gửi khách</t>
   </si>
   <si>
     <t>IV</t>
@@ -477,30 +498,20 @@
     <t>Đang tư vấn thiết kế sơ bộ, khách chưa làm đk thủ tục chuyển nhượng đất</t>
   </si>
   <si>
-    <t>Booyoung - Campuchia</t>
-  </si>
-  <si>
-    <t>Đang triển khai Hợp đồng đặt hàng mẫu (lần 2) vs thầu mới
-03/07 CĐT qua E2 check hàng mẫu, dự kiến 7/7 chủ tịch Hàn Quốc bay sang check ver 2</t>
-  </si>
-  <si>
     <t>Nguyễn Kiều Vân</t>
   </si>
   <si>
     <t>Chị Trang Timecity</t>
   </si>
   <si>
-    <t>09/07/2026</t>
-  </si>
-  <si>
     <t>KH đã ký hợp đồng thiết kế
-Đã chốt 3D, đang điều chỉnh HSKT.</t>
+Đã chốt 3D, đang điều chỉnh HSKT và đợi khách chốt lại các hạng mục sẽ làm</t>
   </si>
   <si>
     <t>Anh Dũng -Trung Văn</t>
   </si>
   <si>
-    <t>KH đã có 3D, cần triển khai thi công. Đang cân nhắc về điều khoản thanh toán.</t>
+    <t>KH đã có 3D, cần triển khai thi công. Đang cân nhắc về điều khoản thanh toán và cân nhắc làm thêm một số hạng mục</t>
   </si>
   <si>
     <t>Anh Ngọc</t>
@@ -525,9 +536,6 @@
     <t>Cụm 36 Biệt thự Ecopark</t>
   </si>
   <si>
-    <t>Tuần 3 tháng 7</t>
-  </si>
-  <si>
     <t>Tự kiếm</t>
   </si>
   <si>
@@ -553,7 +561,7 @@
     <t>Trường tiểu học Liên Hồng</t>
   </si>
   <si>
-    <t>Hai bên đang thỏa thuận lại điều khoản thanh toán hợp đồng (đợi kế toán chốt điều khoản).</t>
+    <t>08/07 sang gặp CĐT để trao đổi trực tiếp về hợp đồng</t>
   </si>
   <si>
     <t>Bệnh viện Thạch Thất</t>
@@ -573,11 +581,11 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-1010000]d/m/yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="163"/>
       <scheme val="minor"/>
@@ -617,7 +625,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,18 +652,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -809,31 +811,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -986,67 +968,55 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1070,10 +1040,7 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1091,35 +1058,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1536,6 +1491,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1569,13 +1531,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1602,36 +1557,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -1728,6 +1653,36 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2600,7 +2555,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{939B5B98-2060-4E95-B025-03590078A4D8}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="B3:D14" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="13">
     <pivotField compact="0" showAll="0"/>
@@ -2734,52 +2689,52 @@
     <dataField name=" Doanh số dự kiến ký" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="33">
+    <format dxfId="18">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="25">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="29">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
     <format dxfId="31">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="32">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="29">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="27">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="26">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="25">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="24">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="23">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="22">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-    <format dxfId="21">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="20">
-      <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="19">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
-    </format>
-    <format dxfId="18">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -2819,8 +2774,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M54" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
-  <autoFilter ref="A3:M54" xr:uid="{00000000-0009-0000-0100-000005000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table5" displayName="Table5" ref="A3:M57" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" headerRowBorderDxfId="14" tableBorderDxfId="15" totalsRowBorderDxfId="13">
+  <autoFilter ref="A3:M57" xr:uid="{00000000-0009-0000-0100-000005000000}">
     <filterColumn colId="9">
       <filters>
         <filter val="Facebook"/>
@@ -3122,16 +3077,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382285EE-A618-417D-9608-F4D64537AFD0}">
   <dimension ref="B3:L42"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="12.875" customWidth="1"/>
-    <col min="3" max="3" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="7" max="7" width="15.875" customWidth="1"/>
-    <col min="8" max="8" width="18.625" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:7" ht="15" customHeight="1">
       <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
@@ -3142,7 +3097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:7">
       <c r="B4" s="15" t="s">
         <v>3</v>
       </c>
@@ -3151,7 +3106,7 @@
         <v>236380000000</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:7">
       <c r="B5" s="15"/>
       <c r="C5" s="15" t="s">
         <v>4</v>
@@ -3160,7 +3115,7 @@
         <v>236080000000</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:7">
       <c r="B6" s="15"/>
       <c r="C6" s="15" t="s">
         <v>5</v>
@@ -3169,7 +3124,7 @@
         <v>300000000</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:7">
       <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
@@ -3178,7 +3133,7 @@
         <v>17000000000</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:7">
       <c r="B8" s="15"/>
       <c r="C8" s="15" t="s">
         <v>7</v>
@@ -3187,7 +3142,7 @@
         <v>8000000000</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:7">
       <c r="B9" s="15"/>
       <c r="C9" s="15" t="s">
         <v>8</v>
@@ -3196,7 +3151,7 @@
         <v>7000000000</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:7">
       <c r="B10" s="15"/>
       <c r="C10" s="15" t="s">
         <v>9</v>
@@ -3205,7 +3160,7 @@
         <v>1500000000</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:7">
       <c r="B11" s="15"/>
       <c r="C11" s="15" t="s">
         <v>10</v>
@@ -3214,7 +3169,7 @@
         <v>500000000</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:7">
       <c r="B12" s="15" t="s">
         <v>11</v>
       </c>
@@ -3224,7 +3179,7 @@
       </c>
       <c r="G12" s="38"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:7">
       <c r="B13" s="15"/>
       <c r="C13" s="15" t="s">
         <v>12</v>
@@ -3233,7 +3188,7 @@
         <v>9450000000</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:7">
       <c r="B14" s="15" t="s">
         <v>13</v>
       </c>
@@ -3242,10 +3197,10 @@
         <v>262830000000</v>
       </c>
     </row>
-    <row r="26" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="8:8">
       <c r="H26" s="38"/>
     </row>
-    <row r="42" spans="12:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="12:12">
       <c r="L42" t="s">
         <v>14</v>
       </c>
@@ -3265,48 +3220,48 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O58"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O61"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9.125" style="21" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="22" customWidth="1"/>
-    <col min="3" max="3" width="23.125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="35.625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="24.875" style="21" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="22.75" style="21" customWidth="1"/>
-    <col min="7" max="7" width="18.875" style="59" customWidth="1"/>
-    <col min="8" max="8" width="15.875" style="22" customWidth="1"/>
-    <col min="9" max="9" width="23.375" style="21" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" style="21" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" style="21" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" style="57" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="22" customWidth="1"/>
+    <col min="9" max="9" width="23.42578125" style="21" customWidth="1"/>
     <col min="10" max="10" width="23" style="22" customWidth="1"/>
-    <col min="11" max="11" width="16.625" style="21" customWidth="1"/>
-    <col min="12" max="12" width="85.25" style="21" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" style="21" customWidth="1"/>
+    <col min="12" max="12" width="85.28515625" style="21" customWidth="1"/>
     <col min="13" max="13" width="24" style="37" customWidth="1"/>
-    <col min="14" max="16384" width="9.125" style="21"/>
+    <col min="14" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:15" ht="33.75" hidden="1" customHeight="1">
+      <c r="A1" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-    </row>
-    <row r="2" spans="1:15" ht="8.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+    </row>
+    <row r="2" spans="1:15" ht="8.25" hidden="1" customHeight="1">
       <c r="G2" s="44"/>
       <c r="H2" s="27"/>
       <c r="J2" s="21"/>
     </row>
-    <row r="3" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="54" customHeight="1">
       <c r="A3" s="17" t="s">
         <v>16</v>
       </c>
@@ -3347,7 +3302,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="23" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" s="23" customFormat="1" ht="22.5" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>27</v>
       </c>
@@ -3358,8 +3313,8 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="8">
-        <f>+SUBTOTAL(9,F5:F8)</f>
-        <v>3800000000</v>
+        <f>+SUBTOTAL(9,F5:F7)</f>
+        <v>3300000000</v>
       </c>
       <c r="G4" s="46"/>
       <c r="H4" s="6"/>
@@ -3369,7 +3324,7 @@
       <c r="L4" s="7"/>
       <c r="M4" s="34"/>
     </row>
-    <row r="5" spans="1:15" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="59.25" customHeight="1">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -3410,7 +3365,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="40.5" customHeight="1">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -3449,7 +3404,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="40.5" customHeight="1">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -3470,7 +3425,7 @@
         <v>0.19</v>
       </c>
       <c r="H7" s="39" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>39</v>
@@ -3482,7 +3437,7 @@
         <v>0.7</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M7" s="35" t="s">
         <v>41</v>
@@ -3490,72 +3445,72 @@
       <c r="N7" s="26"/>
       <c r="O7" s="26"/>
     </row>
-    <row r="8" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="1" t="s">
+    <row r="8" spans="1:15" s="25" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2">
+      <c r="B8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="50"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
+        <f>+SUBTOTAL(9,F9:F35)</f>
+        <v>28233000000</v>
+      </c>
+      <c r="G8" s="46"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="34"/>
+    </row>
+    <row r="9" spans="1:15" ht="40.5" customHeight="1">
+      <c r="A9" s="10">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2">
         <v>500000000</v>
       </c>
-      <c r="G8" s="12">
-        <v>0.19</v>
-      </c>
-      <c r="H8" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="G9" s="12">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="12">
+      <c r="I9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="12">
         <v>0.6</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="35" t="s">
+      <c r="L9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="N8" s="26"/>
-      <c r="O8" s="26"/>
-    </row>
-    <row r="9" spans="1:15" s="25" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8">
-        <f>+SUBTOTAL(9,F10:F31)</f>
-        <v>26813000000</v>
-      </c>
-      <c r="G9" s="46"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="34"/>
-    </row>
-    <row r="10" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N9" s="24"/>
+    </row>
+    <row r="10" spans="1:15" ht="36" customHeight="1">
       <c r="A10" s="10">
-        <v>1</v>
+        <f>+A9+1</f>
+        <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>6</v>
@@ -3568,34 +3523,35 @@
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="2">
-        <v>500000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G10" s="12">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="39" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" s="12">
         <v>0.6</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M10" s="35" t="s">
         <v>41</v>
       </c>
       <c r="N10" s="24"/>
     </row>
-    <row r="11" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="36" customHeight="1">
       <c r="A11" s="10">
-        <v>2</v>
+        <f t="shared" ref="A11:A35" si="0">+A10+1</f>
+        <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>6</v>
@@ -3604,38 +3560,39 @@
         <v>9</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1000000000</v>
+      </c>
       <c r="F11" s="2">
-        <v>1000000000</v>
+        <v>120000000</v>
       </c>
       <c r="G11" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>46</v>
+        <v>0.3</v>
+      </c>
+      <c r="H11" s="39">
+        <v>46219</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" s="12">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="35" t="s">
-        <v>41</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="M11" s="35"/>
       <c r="N11" s="24"/>
     </row>
-    <row r="12" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <v>3</v>
+    <row r="12" spans="1:15" ht="75.75" customHeight="1">
+      <c r="A12" s="10">
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>6</v>
@@ -3644,186 +3601,190 @@
         <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2">
         <v>1000000000</v>
       </c>
       <c r="F12" s="2">
-        <v>120000000</v>
+        <v>400000000</v>
       </c>
       <c r="G12" s="12">
         <v>0.3</v>
       </c>
-      <c r="H12" s="39">
-        <v>46209</v>
+      <c r="H12" s="39" t="s">
+        <v>47</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>39</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" s="12">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M12" s="35"/>
       <c r="N12" s="24"/>
     </row>
-    <row r="13" spans="1:15" ht="75.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>3</v>
+    <row r="13" spans="1:15" ht="39" customHeight="1">
+      <c r="A13" s="10">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1000000000</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E13" s="1"/>
       <c r="F13" s="2">
-        <v>400000000</v>
+        <v>900000000</v>
       </c>
       <c r="G13" s="12">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="K13" s="12">
         <v>0.7</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M13" s="35"/>
+        <v>59</v>
+      </c>
+      <c r="M13" s="35" t="s">
+        <v>41</v>
+      </c>
       <c r="N13" s="24"/>
     </row>
-    <row r="14" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="56">
-        <v>4</v>
+    <row r="14" spans="1:15" ht="62.25" customHeight="1">
+      <c r="A14" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="2">
-        <v>900000000</v>
+        <v>8000000000</v>
       </c>
       <c r="G14" s="12">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K14" s="12">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="N14" s="24"/>
     </row>
-    <row r="15" spans="1:15" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="56">
-        <v>5</v>
+    <row r="15" spans="1:15" ht="51" customHeight="1">
+      <c r="A15" s="10">
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>61</v>
+        <v>8</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="2">
-        <v>8000000000</v>
+        <v>600000000</v>
       </c>
       <c r="G15" s="12">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H15" s="39" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K15" s="12">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M15" s="35" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="N15" s="24"/>
     </row>
-    <row r="16" spans="1:15" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="27.75" customHeight="1">
       <c r="A16" s="10">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>65</v>
+        <v>10</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="2">
-        <v>600000000</v>
+        <v>500000000</v>
       </c>
       <c r="G16" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H16" s="39" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K16" s="12">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>67</v>
@@ -3833,9 +3794,10 @@
       </c>
       <c r="N16" s="24"/>
     </row>
-    <row r="17" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="27.75" customHeight="1">
       <c r="A17" s="10">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>6</v>
@@ -3848,19 +3810,19 @@
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="2">
-        <v>500000000</v>
+        <v>100000000</v>
       </c>
       <c r="G17" s="12">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H17" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K17" s="12">
         <v>0.7</v>
@@ -3868,458 +3830,453 @@
       <c r="L17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="M17" s="35" t="s">
-        <v>41</v>
-      </c>
+      <c r="M17" s="35"/>
       <c r="N17" s="24"/>
     </row>
-    <row r="18" spans="1:14" s="70" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="71">
-        <v>8</v>
-      </c>
-      <c r="B18" s="63" t="s">
+    <row r="18" spans="1:14" ht="27.75" customHeight="1">
+      <c r="A18" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="C18" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="65" t="s">
+      <c r="E18" s="1"/>
+      <c r="F18" s="2">
+        <v>150000000</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="66">
-        <v>500000000</v>
-      </c>
-      <c r="G18" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="H18" s="80" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="63" t="s">
-        <v>39</v>
-      </c>
-      <c r="J18" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="K18" s="67">
-        <v>0.7</v>
-      </c>
-      <c r="L18" s="65" t="s">
-        <v>73</v>
-      </c>
-      <c r="M18" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="N18" s="69"/>
-    </row>
-    <row r="19" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M18" s="35"/>
+      <c r="N18" s="24"/>
+    </row>
+    <row r="19" spans="1:14" ht="27.75" customHeight="1">
       <c r="A19" s="10">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="2">
-        <v>150000000</v>
+        <v>320000000</v>
       </c>
       <c r="G19" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K19" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M19" s="35"/>
+      <c r="N19" s="24"/>
+    </row>
+    <row r="20" spans="1:14" ht="36.75" customHeight="1">
+      <c r="A20" s="10">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="2">
+        <v>650000000</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20" s="35"/>
+      <c r="N20" s="24"/>
+    </row>
+    <row r="21" spans="1:14" ht="48" customHeight="1">
+      <c r="A21" s="10">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" s="2">
+        <v>200000000</v>
+      </c>
+      <c r="G21" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K21" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="35"/>
+      <c r="N21" s="24"/>
+    </row>
+    <row r="22" spans="1:14" s="67" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A22" s="10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="62" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="63">
+        <v>500000000</v>
+      </c>
+      <c r="G22" s="64">
         <v>0.2</v>
       </c>
-      <c r="H19" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K19" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="35" t="s">
+      <c r="H22" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="J22" s="60" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" s="64">
+        <v>0.7</v>
+      </c>
+      <c r="L22" s="62" t="s">
+        <v>81</v>
+      </c>
+      <c r="M22" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="N19" s="24"/>
-    </row>
-    <row r="20" spans="1:14" s="70" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="62">
-        <f>A19+1</f>
-        <v>11</v>
-      </c>
-      <c r="B20" s="63" t="str">
-        <f>B19</f>
-        <v>BU 1</v>
-      </c>
-      <c r="C20" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="65" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="66">
-        <v>85000000</v>
-      </c>
-      <c r="G20" s="67">
-        <v>0.2</v>
-      </c>
-      <c r="H20" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="J20" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="K20" s="67">
-        <v>0.9</v>
-      </c>
-      <c r="L20" s="65" t="s">
-        <v>78</v>
-      </c>
-      <c r="M20" s="68"/>
-      <c r="N20" s="69"/>
-    </row>
-    <row r="21" spans="1:14" s="26" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="56">
-        <v>12</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="D21" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="75">
-        <v>200000000</v>
-      </c>
-      <c r="G21" s="76">
-        <v>0.2</v>
-      </c>
-      <c r="H21" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="I21" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="K21" s="76">
-        <v>0.7</v>
-      </c>
-      <c r="L21" s="74" t="s">
-        <v>80</v>
-      </c>
-      <c r="M21" s="78" t="s">
-        <v>41</v>
-      </c>
-      <c r="N21" s="79"/>
-    </row>
-    <row r="22" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10">
-        <v>13</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="2">
-        <v>300000000</v>
-      </c>
-      <c r="G22" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H22" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K22" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M22" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" s="24"/>
-    </row>
-    <row r="23" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N22" s="66"/>
+    </row>
+    <row r="23" spans="1:14" ht="38.25" customHeight="1">
       <c r="A23" s="10">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="2">
-        <v>400000000</v>
+        <v>150000000</v>
       </c>
       <c r="G23" s="12">
         <v>0.2</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" s="12">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M23" s="35" t="s">
         <v>41</v>
       </c>
       <c r="N23" s="24"/>
     </row>
-    <row r="24" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" s="67" customFormat="1" ht="38.25" customHeight="1">
       <c r="A24" s="10">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="s">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B24" s="60" t="str">
+        <f>B23</f>
+        <v>BU 1</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="63">
+        <v>85000000</v>
+      </c>
+      <c r="G24" s="64">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="K24" s="64">
+        <v>0.9</v>
+      </c>
+      <c r="L24" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="M24" s="65"/>
+      <c r="N24" s="66"/>
+    </row>
+    <row r="25" spans="1:14" s="26" customFormat="1" ht="42" customHeight="1">
+      <c r="A25" s="10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B25" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="2">
-        <v>500000000</v>
-      </c>
-      <c r="G24" s="12">
+      <c r="C25" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="70" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="71">
+        <v>200000000</v>
+      </c>
+      <c r="G25" s="72">
         <v>0.2</v>
       </c>
-      <c r="H24" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="K24" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="L24" s="1" t="s">
+      <c r="H25" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="72">
+        <v>0.7</v>
+      </c>
+      <c r="L25" s="70" t="s">
         <v>88</v>
       </c>
-      <c r="M24" s="35"/>
-      <c r="N24" s="24"/>
-    </row>
-    <row r="25" spans="1:14" ht="58.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10">
-        <v>15</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="2">
-        <v>7000000000</v>
-      </c>
-      <c r="G25" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K25" s="12">
-        <v>0.6</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M25" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="N25" s="24"/>
-    </row>
-    <row r="26" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M25" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="N25" s="75"/>
+    </row>
+    <row r="26" spans="1:14" ht="37.5" customHeight="1">
       <c r="A26" s="10">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="2">
-        <v>400000000</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" s="1"/>
       <c r="F26" s="2">
-        <v>8000000</v>
+        <v>300000000</v>
       </c>
       <c r="G26" s="12">
         <v>0.2</v>
       </c>
       <c r="H26" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K26" s="12">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M26" s="35" t="s">
         <v>41</v>
       </c>
       <c r="N26" s="24"/>
     </row>
-    <row r="27" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" ht="37.5" customHeight="1">
       <c r="A27" s="10">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="2">
+        <v>92</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="2">
         <v>400000000</v>
-      </c>
-      <c r="F27" s="2">
-        <v>1000000000</v>
       </c>
       <c r="G27" s="12">
         <v>0.2</v>
       </c>
       <c r="H27" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J27" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K27" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="K27" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="M27" s="35" t="s">
         <v>41</v>
       </c>
       <c r="N27" s="24"/>
     </row>
-    <row r="28" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="37.5" customHeight="1">
       <c r="A28" s="10">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="2">
-        <v>250000000</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="E28" s="1"/>
       <c r="F28" s="2">
-        <v>250000000</v>
+        <v>500000000</v>
       </c>
       <c r="G28" s="12">
         <v>0.2</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K28" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I28" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K28" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M28" s="35" t="s">
-        <v>41</v>
-      </c>
+      <c r="M28" s="35"/>
       <c r="N28" s="24"/>
     </row>
-    <row r="29" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="58.5" customHeight="1">
       <c r="A29" s="10">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>6</v>
@@ -4328,40 +4285,39 @@
         <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E29" s="2">
-        <v>400000000</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="E29" s="1"/>
       <c r="F29" s="2">
-        <v>900000000</v>
+        <v>7000000000</v>
       </c>
       <c r="G29" s="12">
         <v>0.2</v>
       </c>
       <c r="H29" s="39" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K29" s="12">
         <v>0.6</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M29" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N29" s="24"/>
     </row>
-    <row r="30" spans="1:14" ht="87.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="39.75" customHeight="1">
       <c r="A30" s="10">
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>6</v>
@@ -4370,301 +4326,317 @@
         <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E30" s="2">
         <v>400000000</v>
       </c>
       <c r="F30" s="2">
-        <v>3000000000</v>
+        <v>8000000</v>
       </c>
       <c r="G30" s="12">
         <v>0.2</v>
       </c>
       <c r="H30" s="39" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K30" s="12">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="M30" s="35" t="s">
         <v>41</v>
       </c>
       <c r="N30" s="24"/>
     </row>
-    <row r="31" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="81">
-        <v>20</v>
-      </c>
-      <c r="B31" s="57" t="s">
+    <row r="31" spans="1:14" ht="51" customHeight="1">
+      <c r="A31" s="10">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="C31" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="42" t="s">
-        <v>104</v>
+      <c r="D31" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E31" s="2">
         <v>400000000</v>
       </c>
-      <c r="F31" s="83">
-        <v>500000000</v>
-      </c>
-      <c r="G31" s="84">
+      <c r="F31" s="2">
+        <v>1000000000</v>
+      </c>
+      <c r="G31" s="12">
         <v>0.2</v>
       </c>
-      <c r="H31" s="85" t="s">
+      <c r="H31" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="K31" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I31" s="57" t="s">
+      <c r="M31" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N31" s="24"/>
+    </row>
+    <row r="32" spans="1:14" ht="39.75" customHeight="1">
+      <c r="A32" s="10">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" s="2">
+        <v>250000000</v>
+      </c>
+      <c r="F32" s="2">
+        <v>250000000</v>
+      </c>
+      <c r="G32" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J31" s="57" t="s">
-        <v>97</v>
-      </c>
-      <c r="K31" s="84">
+      <c r="J32" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K32" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="M32" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N32" s="24"/>
+    </row>
+    <row r="33" spans="1:15" ht="39.75" customHeight="1">
+      <c r="A33" s="10">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F33" s="2">
+        <v>900000000</v>
+      </c>
+      <c r="G33" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H33" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K33" s="12">
         <v>0.6</v>
       </c>
-      <c r="L31" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="M31" s="86" t="s">
-        <v>41</v>
-      </c>
-      <c r="N31" s="24"/>
-    </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="50"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8">
-        <f>+SUBTOTAL(9,F33:F40)</f>
-        <v>21800000000</v>
-      </c>
-      <c r="G32" s="46"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="34"/>
-    </row>
-    <row r="33" spans="1:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="87">
-        <v>1</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="89">
-        <v>3900000000</v>
-      </c>
-      <c r="G33" s="90">
-        <v>0.25</v>
-      </c>
-      <c r="H33" s="91" t="s">
-        <v>46</v>
-      </c>
-      <c r="I33" s="92" t="s">
-        <v>33</v>
-      </c>
-      <c r="J33" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="K33" s="90">
-        <v>0.7</v>
-      </c>
-      <c r="L33" s="93" t="s">
+      <c r="L33" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="M33" s="94"/>
-      <c r="N33" s="26"/>
-      <c r="O33" s="26"/>
-    </row>
-    <row r="34" spans="1:15" ht="94.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
-        <v>2</v>
+      <c r="M33" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="N33" s="24"/>
+    </row>
+    <row r="34" spans="1:15" ht="87.75" customHeight="1">
+      <c r="A34" s="10">
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="1"/>
+      <c r="E34" s="2">
+        <v>400000000</v>
+      </c>
       <c r="F34" s="2">
-        <v>3500000000</v>
-      </c>
-      <c r="G34" s="55">
-        <v>0.25</v>
-      </c>
-      <c r="H34" s="54" t="s">
-        <v>46</v>
+        <v>3000000000</v>
+      </c>
+      <c r="G34" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>110</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="K34" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L34" s="96" t="s">
+        <v>0.6</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M34" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="N34" s="24"/>
+    </row>
+    <row r="35" spans="1:15" ht="39.75" customHeight="1">
+      <c r="A35" s="10">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B35" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="77" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="E35" s="2">
+        <v>400000000</v>
+      </c>
+      <c r="F35" s="78">
+        <v>500000000</v>
+      </c>
+      <c r="G35" s="79">
+        <v>0.2</v>
+      </c>
+      <c r="H35" s="80" t="s">
         <v>110</v>
       </c>
-      <c r="M34" s="35"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-    </row>
-    <row r="35" spans="1:15" ht="131.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>3</v>
-      </c>
-      <c r="B35" s="4" t="s">
+      <c r="I35" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="K35" s="79">
+        <v>0.6</v>
+      </c>
+      <c r="L35" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="M35" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="N35" s="24"/>
+    </row>
+    <row r="36" spans="1:15" ht="30" customHeight="1">
+      <c r="A36" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" s="2">
-        <v>2400000000</v>
-      </c>
-      <c r="G35" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H35" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K35" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L35" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="M35" s="35"/>
-      <c r="N35" s="26"/>
-      <c r="O35" s="26"/>
-    </row>
-    <row r="36" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
-        <v>4</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" s="1"/>
-      <c r="F36" s="2">
-        <v>1300000000</v>
-      </c>
-      <c r="G36" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H36" s="95">
-        <v>46209</v>
-      </c>
-      <c r="I36" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K36" s="12">
-        <v>0.9</v>
-      </c>
-      <c r="L36" s="41" t="s">
-        <v>115</v>
-      </c>
-      <c r="M36" s="35"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-    </row>
-    <row r="37" spans="1:15" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C36" s="50"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="85">
+        <f>+SUBTOTAL(9,F37:F44)</f>
+        <v>20500000000</v>
+      </c>
+      <c r="G36" s="87"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="34"/>
+    </row>
+    <row r="37" spans="1:15" ht="94.5" customHeight="1">
       <c r="A37" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="51" t="s">
+      <c r="C37" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" s="82">
+        <v>3500000000</v>
+      </c>
+      <c r="G37" s="54">
+        <v>0.2</v>
+      </c>
+      <c r="H37" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K37" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L37" s="84" t="s">
         <v>116</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="2">
-        <v>2600000000</v>
-      </c>
-      <c r="G37" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I37" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="K37" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L37" s="41" t="s">
-        <v>118</v>
       </c>
       <c r="M37" s="35"/>
       <c r="N37" s="26"/>
       <c r="O37" s="26"/>
     </row>
-    <row r="38" spans="1:15" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" ht="131.25" customHeight="1">
       <c r="A38" s="3">
-        <v>6</v>
+        <f>+A37+1</f>
+        <v>2</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>11</v>
@@ -4673,37 +4645,40 @@
         <v>12</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F38" s="2">
+        <v>2400000000</v>
+      </c>
+      <c r="G38" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I38" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K38" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L38" s="41" t="s">
         <v>119</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="2">
-        <v>2900000000</v>
-      </c>
-      <c r="G38" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H38" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="K38" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="M38" s="35"/>
       <c r="N38" s="26"/>
       <c r="O38" s="26"/>
     </row>
-    <row r="39" spans="1:15" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:15" ht="66" customHeight="1">
       <c r="A39" s="3">
-        <v>9</v>
+        <f t="shared" ref="A39:A44" si="1">+A38+1</f>
+        <v>3</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>11</v>
@@ -4712,433 +4687,443 @@
         <v>12</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="2">
-        <v>5000000000</v>
+        <v>400000000</v>
       </c>
       <c r="G39" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>46</v>
+        <v>0.2</v>
+      </c>
+      <c r="H39" s="83" t="s">
+        <v>47</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K39" s="12">
         <v>0.9</v>
       </c>
-      <c r="L39" s="49" t="s">
-        <v>122</v>
+      <c r="L39" s="41" t="s">
+        <v>121</v>
       </c>
       <c r="M39" s="35"/>
-    </row>
-    <row r="40" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+    </row>
+    <row r="40" spans="1:15" ht="108.75" customHeight="1">
       <c r="A40" s="3">
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="48" t="s">
+      <c r="C40" s="51" t="s">
         <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="2">
-        <v>200000000</v>
+        <v>3000000000</v>
       </c>
       <c r="G40" s="12">
         <v>0.2</v>
       </c>
-      <c r="H40" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I40" s="52" t="s">
+      <c r="H40" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K40" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L40" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="M40" s="35"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+    </row>
+    <row r="41" spans="1:15" ht="50.25" customHeight="1">
+      <c r="A41" s="3">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="2">
+        <v>2900000000</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.2</v>
+      </c>
+      <c r="H41" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J40" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K40" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M40" s="35"/>
-    </row>
-    <row r="41" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="50"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8">
-        <f>+SUBTOTAL(9,F42:F53)</f>
-        <v>222325000000</v>
-      </c>
-      <c r="G41" s="46"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="34"/>
-    </row>
-    <row r="42" spans="1:15" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J41" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K41" s="12">
+        <v>0.6</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M41" s="35"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+    </row>
+    <row r="42" spans="1:15" ht="70.5" customHeight="1">
       <c r="A42" s="3">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="51" t="s">
-        <v>4</v>
+        <v>11</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>12</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="2">
-        <v>80000000</v>
+        <v>6000000000</v>
       </c>
       <c r="G42" s="12">
         <v>0.2</v>
       </c>
       <c r="H42" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="K42" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L42" s="1" t="s">
+        <v>0.9</v>
+      </c>
+      <c r="L42" s="49" t="s">
         <v>128</v>
       </c>
       <c r="M42" s="35"/>
     </row>
-    <row r="43" spans="1:15" s="26" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:15" ht="70.5" customHeight="1">
       <c r="A43" s="3">
-        <f>A42+1</f>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C43" s="48" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>129</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="2">
-        <v>30000000000</v>
+        <v>2100000000</v>
       </c>
       <c r="G43" s="12">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H43" s="39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K43" s="12">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>130</v>
       </c>
       <c r="M43" s="35"/>
     </row>
-    <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" ht="33" customHeight="1">
       <c r="A44" s="3">
-        <f>A43+1</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E44" s="42"/>
+      <c r="E44" s="1"/>
       <c r="F44" s="2">
-        <v>95000000</v>
+        <v>200000000</v>
       </c>
       <c r="G44" s="12">
-        <v>0.23</v>
-      </c>
-      <c r="H44" s="43" t="s">
-        <v>133</v>
+        <v>0.2</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>47</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K44" s="12">
-        <v>0.85</v>
-      </c>
-      <c r="L44" s="41" t="s">
-        <v>134</v>
+        <v>0.5</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="M44" s="35"/>
     </row>
-    <row r="45" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <f>A44+1</f>
-        <v>4</v>
-      </c>
-      <c r="B45" s="4" t="s">
+    <row r="45" spans="1:15" ht="27.75" customHeight="1">
+      <c r="A45" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="42"/>
-      <c r="F45" s="2">
-        <v>1100000000</v>
-      </c>
-      <c r="G45" s="12">
-        <v>0.23</v>
-      </c>
-      <c r="H45" s="43">
-        <v>46213</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K45" s="12">
-        <v>0.7</v>
-      </c>
-      <c r="L45" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="M45" s="35"/>
-    </row>
-    <row r="46" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C45" s="50"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="8">
+        <f>+SUBTOTAL(9,F46:F56)</f>
+        <v>192325000000</v>
+      </c>
+      <c r="G45" s="46"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="34"/>
+    </row>
+    <row r="46" spans="1:15" ht="37.5" customHeight="1">
       <c r="A46" s="3">
-        <f t="shared" ref="A46" si="0">A45+1</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E46" s="42"/>
+        <v>134</v>
+      </c>
+      <c r="E46" s="1"/>
       <c r="F46" s="2">
-        <v>110000000</v>
+        <v>80000000</v>
       </c>
       <c r="G46" s="12">
         <v>0.2</v>
       </c>
-      <c r="H46" s="43">
-        <v>46213</v>
+      <c r="H46" s="39" t="s">
+        <v>51</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="K46" s="12">
         <v>0.7</v>
       </c>
-      <c r="L46" s="41" t="s">
-        <v>138</v>
+      <c r="L46" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="M46" s="35"/>
     </row>
-    <row r="47" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
+    <row r="47" spans="1:15" ht="42" customHeight="1">
+      <c r="A47" s="3">
+        <f>+A46+1</f>
+        <v>2</v>
+      </c>
       <c r="B47" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E47" s="42"/>
       <c r="F47" s="2">
-        <v>140000000</v>
+        <v>95000000</v>
       </c>
       <c r="G47" s="12">
-        <v>0.2</v>
-      </c>
-      <c r="H47" s="43" t="s">
-        <v>66</v>
+        <v>0.23</v>
+      </c>
+      <c r="H47" s="43">
+        <v>46220</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" s="12">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L47" s="41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M47" s="35"/>
     </row>
-    <row r="48" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" ht="42" customHeight="1">
       <c r="A48" s="3">
-        <f>A46+1</f>
-        <v>6</v>
+        <f t="shared" ref="A48:A56" si="2">+A47+1</f>
+        <v>3</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C48" s="51" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E48" s="42"/>
       <c r="F48" s="2">
-        <v>60000000000</v>
+        <v>1100000000</v>
       </c>
       <c r="G48" s="12">
-        <v>0.08</v>
-      </c>
-      <c r="H48" s="39" t="s">
-        <v>66</v>
+        <v>0.23</v>
+      </c>
+      <c r="H48" s="43">
+        <v>46223</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="K48" s="12">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L48" s="41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M48" s="35"/>
     </row>
-    <row r="49" spans="1:13" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" ht="39" customHeight="1">
       <c r="A49" s="3">
-        <f>A48+1</f>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C49" s="51" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E49" s="42"/>
       <c r="F49" s="2">
-        <v>60000000000</v>
+        <v>110000000</v>
       </c>
       <c r="G49" s="12">
-        <v>0.15</v>
-      </c>
-      <c r="H49" s="39" t="s">
-        <v>144</v>
+        <v>0.2</v>
+      </c>
+      <c r="H49" s="43">
+        <v>46219</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>145</v>
+        <v>48</v>
       </c>
       <c r="K49" s="12">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L49" s="41" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M49" s="35"/>
     </row>
-    <row r="50" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" ht="39" customHeight="1">
       <c r="A50" s="3">
-        <f>A49+1</f>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>5</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C50" s="51" t="s">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E50" s="42"/>
       <c r="F50" s="2">
-        <v>800000000</v>
+        <v>140000000</v>
       </c>
       <c r="G50" s="12">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="H50" s="43" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K50" s="12">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L50" s="41" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="M50" s="35"/>
     </row>
-    <row r="51" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" ht="39" customHeight="1">
       <c r="A51" s="3">
-        <f>A50+1</f>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>3</v>
@@ -5147,36 +5132,36 @@
         <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E51" s="42"/>
       <c r="F51" s="2">
         <v>60000000000</v>
       </c>
       <c r="G51" s="12">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H51" s="39" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>33</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>145</v>
+        <v>105</v>
       </c>
       <c r="K51" s="12">
         <v>0.8</v>
       </c>
       <c r="L51" s="41" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M51" s="35"/>
     </row>
-    <row r="52" spans="1:13" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" ht="48.75" customHeight="1">
       <c r="A52" s="3">
-        <f>A51+1</f>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>3</v>
@@ -5185,97 +5170,211 @@
         <v>4</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E52" s="42"/>
-      <c r="F52" s="47">
-        <v>4000000000</v>
+      <c r="F52" s="2">
+        <v>60000000000</v>
       </c>
       <c r="G52" s="12">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="H52" s="39" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="K52" s="12">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L52" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M52" s="35"/>
     </row>
-    <row r="53" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" ht="36.75" customHeight="1">
       <c r="A53" s="3">
-        <f>A52+1</f>
-        <v>11</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C53" s="51" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E53" s="42"/>
       <c r="F53" s="2">
+        <v>800000000</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0.23</v>
+      </c>
+      <c r="H53" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K53" s="12">
+        <v>0.7</v>
+      </c>
+      <c r="L53" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="M53" s="35"/>
+    </row>
+    <row r="54" spans="1:13" ht="44.25" customHeight="1">
+      <c r="A54" s="3">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E54" s="42"/>
+      <c r="F54" s="2">
+        <v>60000000000</v>
+      </c>
+      <c r="G54" s="12">
+        <v>0.15</v>
+      </c>
+      <c r="H54" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="K54" s="12">
+        <v>0.8</v>
+      </c>
+      <c r="L54" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="M54" s="35"/>
+    </row>
+    <row r="55" spans="1:13" ht="44.25" customHeight="1">
+      <c r="A55" s="3">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E55" s="42"/>
+      <c r="F55" s="47">
+        <v>4000000000</v>
+      </c>
+      <c r="G55" s="12">
+        <v>0.08</v>
+      </c>
+      <c r="H55" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="12">
+        <v>0.9</v>
+      </c>
+      <c r="L55" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="M55" s="35"/>
+    </row>
+    <row r="56" spans="1:13" ht="32.25" customHeight="1">
+      <c r="A56" s="3">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" s="42"/>
+      <c r="F56" s="2">
         <v>6000000000</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G56" s="12">
         <v>0.08</v>
       </c>
-      <c r="H53" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="I53" s="4" t="s">
+      <c r="H56" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="I56" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J53" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="K53" s="12">
+      <c r="J56" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K56" s="12">
         <v>0.8</v>
       </c>
-      <c r="L53" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="M53" s="35"/>
-    </row>
-    <row r="54" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="28"/>
-      <c r="B54" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="C54" s="30"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="32">
-        <f>SUBTOTAL(9,F4:F53)</f>
-        <v>274738000000</v>
-      </c>
-      <c r="G54" s="58"/>
-      <c r="H54" s="60"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="60"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="31"/>
-      <c r="M54" s="36"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="F55" s="24"/>
-      <c r="H55" s="61"/>
-    </row>
-    <row r="56" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="L56" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="M56" s="35"/>
+    </row>
+    <row r="57" spans="1:13" ht="22.5" customHeight="1">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="30"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="32">
+        <f>SUBTOTAL(9,F4:F56)</f>
+        <v>244358000000</v>
+      </c>
+      <c r="G57" s="56"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="58"/>
+      <c r="K57" s="33"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="36"/>
+    </row>
+    <row r="58" spans="1:13">
+      <c r="F58" s="24"/>
+      <c r="H58" s="59"/>
+    </row>
+    <row r="59" spans="1:13" ht="46.5" customHeight="1"/>
+    <row r="60" spans="1:13" ht="46.5" customHeight="1"/>
+    <row r="61" spans="1:13" ht="25.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:M1"/>
